--- a/XRD_Results/CuS B2_CuS_XRD_Analysis.xlsx
+++ b/XRD_Results/CuS B2_CuS_XRD_Analysis.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F8"/>
+  <dimension ref="A1:F35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -460,19 +460,19 @@
         <v>1</v>
       </c>
       <c r="B2" t="n">
-        <v>27.905</v>
+        <v>19.945</v>
       </c>
       <c r="C2" t="n">
-        <v>3.19472</v>
+        <v>4.44811</v>
       </c>
       <c r="D2" t="n">
-        <v>758.143</v>
+        <v>365.952</v>
       </c>
       <c r="E2" t="n">
-        <v>166.9528251748255</v>
+        <v>33.78655944055953</v>
       </c>
       <c r="F2" t="n">
-        <v>35.80013316270878</v>
+        <v>17.28055305022878</v>
       </c>
     </row>
     <row r="3">
@@ -480,19 +480,19 @@
         <v>2</v>
       </c>
       <c r="B3" t="n">
-        <v>29.501</v>
+        <v>24.242</v>
       </c>
       <c r="C3" t="n">
-        <v>3.02541</v>
+        <v>3.66849</v>
       </c>
       <c r="D3" t="n">
-        <v>1238.62</v>
+        <v>461.619</v>
       </c>
       <c r="E3" t="n">
-        <v>617.4257156177173</v>
+        <v>39.38721445221461</v>
       </c>
       <c r="F3" t="n">
-        <v>58.48865047622195</v>
+        <v>21.79802711419411</v>
       </c>
     </row>
     <row r="4">
@@ -500,19 +500,19 @@
         <v>3</v>
       </c>
       <c r="B4" t="n">
-        <v>32.018</v>
+        <v>26.186</v>
       </c>
       <c r="C4" t="n">
-        <v>2.7931</v>
+        <v>3.4004</v>
       </c>
       <c r="D4" t="n">
-        <v>1335.95</v>
+        <v>498.571</v>
       </c>
       <c r="E4" t="n">
-        <v>734.5982634032654</v>
+        <v>31.97189976689981</v>
       </c>
       <c r="F4" t="n">
-        <v>63.08465276170958</v>
+        <v>23.54293080733434</v>
       </c>
     </row>
     <row r="5">
@@ -520,19 +520,19 @@
         <v>4</v>
       </c>
       <c r="B5" t="n">
-        <v>48.224</v>
+        <v>27.905</v>
       </c>
       <c r="C5" t="n">
-        <v>1.88557</v>
+        <v>3.19472</v>
       </c>
       <c r="D5" t="n">
-        <v>2117.71</v>
+        <v>758.143</v>
       </c>
       <c r="E5" t="n">
-        <v>1461.322503496507</v>
+        <v>166.9528251748255</v>
       </c>
       <c r="F5" t="n">
-        <v>100</v>
+        <v>35.80013316270878</v>
       </c>
     </row>
     <row r="6">
@@ -540,19 +540,19 @@
         <v>5</v>
       </c>
       <c r="B6" t="n">
-        <v>53.012</v>
+        <v>29.501</v>
       </c>
       <c r="C6" t="n">
-        <v>1.72599</v>
+        <v>3.02541</v>
       </c>
       <c r="D6" t="n">
-        <v>1007.48</v>
+        <v>1238.62</v>
       </c>
       <c r="E6" t="n">
-        <v>293.7466153846162</v>
+        <v>617.4257156177173</v>
       </c>
       <c r="F6" t="n">
-        <v>47.57403043853974</v>
+        <v>58.48865047622195</v>
       </c>
     </row>
     <row r="7">
@@ -560,19 +560,19 @@
         <v>6</v>
       </c>
       <c r="B7" t="n">
-        <v>59.376</v>
+        <v>32.018</v>
       </c>
       <c r="C7" t="n">
-        <v>1.55528</v>
+        <v>2.7931</v>
       </c>
       <c r="D7" t="n">
-        <v>1194.52</v>
+        <v>1335.95</v>
       </c>
       <c r="E7" t="n">
-        <v>490.9883613053626</v>
+        <v>734.5982634032654</v>
       </c>
       <c r="F7" t="n">
-        <v>56.40621237091008</v>
+        <v>63.08465276170958</v>
       </c>
     </row>
     <row r="8">
@@ -580,19 +580,559 @@
         <v>7</v>
       </c>
       <c r="B8" t="n">
+        <v>32.304</v>
+      </c>
+      <c r="C8" t="n">
+        <v>2.76898</v>
+      </c>
+      <c r="D8" t="n">
+        <v>1318.29</v>
+      </c>
+      <c r="E8" t="n">
+        <v>69.00004662004676</v>
+      </c>
+      <c r="F8" t="n">
+        <v>62.25073310321054</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" t="n">
+        <v>34.903</v>
+      </c>
+      <c r="C9" t="n">
+        <v>2.56853</v>
+      </c>
+      <c r="D9" t="n">
+        <v>635.429</v>
+      </c>
+      <c r="E9" t="n">
+        <v>36.50466200466212</v>
+      </c>
+      <c r="F9" t="n">
+        <v>30.00547761497089</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" t="n">
+        <v>38.73</v>
+      </c>
+      <c r="C10" t="n">
+        <v>2.32311</v>
+      </c>
+      <c r="D10" t="n">
+        <v>692.952</v>
+      </c>
+      <c r="E10" t="n">
+        <v>80.02541258741269</v>
+      </c>
+      <c r="F10" t="n">
+        <v>32.72176076988823</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" t="n">
+        <v>39.957</v>
+      </c>
+      <c r="C11" t="n">
+        <v>2.25451</v>
+      </c>
+      <c r="D11" t="n">
+        <v>660.952</v>
+      </c>
+      <c r="E11" t="n">
+        <v>35.10022377622386</v>
+      </c>
+      <c r="F11" t="n">
+        <v>31.21069457102247</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" t="n">
+        <v>44.05</v>
+      </c>
+      <c r="C12" t="n">
+        <v>2.05408</v>
+      </c>
+      <c r="D12" t="n">
+        <v>703.952</v>
+      </c>
+      <c r="E12" t="n">
+        <v>33.17082750582745</v>
+      </c>
+      <c r="F12" t="n">
+        <v>33.24118977574833</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" t="n">
+        <v>44.582</v>
+      </c>
+      <c r="C13" t="n">
+        <v>2.03079</v>
+      </c>
+      <c r="D13" t="n">
+        <v>704</v>
+      </c>
+      <c r="E13" t="n">
+        <v>48.19276923076939</v>
+      </c>
+      <c r="F13" t="n">
+        <v>33.24345637504663</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>13</v>
+      </c>
+      <c r="B14" t="n">
+        <v>48.224</v>
+      </c>
+      <c r="C14" t="n">
+        <v>1.88557</v>
+      </c>
+      <c r="D14" t="n">
+        <v>2117.71</v>
+      </c>
+      <c r="E14" t="n">
+        <v>1461.322503496507</v>
+      </c>
+      <c r="F14" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>14</v>
+      </c>
+      <c r="B15" t="n">
+        <v>53.012</v>
+      </c>
+      <c r="C15" t="n">
+        <v>1.72599</v>
+      </c>
+      <c r="D15" t="n">
+        <v>1007.48</v>
+      </c>
+      <c r="E15" t="n">
+        <v>293.7466153846162</v>
+      </c>
+      <c r="F15" t="n">
+        <v>47.57403043853974</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>15</v>
+      </c>
+      <c r="B16" t="n">
+        <v>55.407</v>
+      </c>
+      <c r="C16" t="n">
+        <v>1.65694</v>
+      </c>
+      <c r="D16" t="n">
+        <v>756.476</v>
+      </c>
+      <c r="E16" t="n">
+        <v>41.34393240093232</v>
+      </c>
+      <c r="F16" t="n">
+        <v>35.72141605791161</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>16</v>
+      </c>
+      <c r="B17" t="n">
+        <v>55.754</v>
+      </c>
+      <c r="C17" t="n">
+        <v>1.64742</v>
+      </c>
+      <c r="D17" t="n">
+        <v>740.2859999999999</v>
+      </c>
+      <c r="E17" t="n">
+        <v>35.75706293706298</v>
+      </c>
+      <c r="F17" t="n">
+        <v>34.95691100292296</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>17</v>
+      </c>
+      <c r="B18" t="n">
+        <v>57.453</v>
+      </c>
+      <c r="C18" t="n">
+        <v>1.6027</v>
+      </c>
+      <c r="D18" t="n">
+        <v>842.619</v>
+      </c>
+      <c r="E18" t="n">
+        <v>55.18450582750586</v>
+      </c>
+      <c r="F18" t="n">
+        <v>39.78915904443951</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>18</v>
+      </c>
+      <c r="B19" t="n">
+        <v>59.376</v>
+      </c>
+      <c r="C19" t="n">
+        <v>1.55528</v>
+      </c>
+      <c r="D19" t="n">
+        <v>1194.52</v>
+      </c>
+      <c r="E19" t="n">
+        <v>490.9883613053626</v>
+      </c>
+      <c r="F19" t="n">
+        <v>56.40621237091008</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>19</v>
+      </c>
+      <c r="B20" t="n">
+        <v>61.75</v>
+      </c>
+      <c r="C20" t="n">
+        <v>1.50107</v>
+      </c>
+      <c r="D20" t="n">
+        <v>771</v>
+      </c>
+      <c r="E20" t="n">
+        <v>42.54748484848494</v>
+      </c>
+      <c r="F20" t="n">
+        <v>36.40725122892181</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>20</v>
+      </c>
+      <c r="B21" t="n">
+        <v>62.118</v>
+      </c>
+      <c r="C21" t="n">
+        <v>1.49305</v>
+      </c>
+      <c r="D21" t="n">
+        <v>773.571</v>
+      </c>
+      <c r="E21" t="n">
+        <v>50.34564801864815</v>
+      </c>
+      <c r="F21" t="n">
+        <v>36.52865595383693</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>21</v>
+      </c>
+      <c r="B22" t="n">
+        <v>62.446</v>
+      </c>
+      <c r="C22" t="n">
+        <v>1.48601</v>
+      </c>
+      <c r="D22" t="n">
+        <v>769.143</v>
+      </c>
+      <c r="E22" t="n">
+        <v>32.00741724941736</v>
+      </c>
+      <c r="F22" t="n">
+        <v>36.31956216856888</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>22</v>
+      </c>
+      <c r="B23" t="n">
+        <v>63.489</v>
+      </c>
+      <c r="C23" t="n">
+        <v>1.46407</v>
+      </c>
+      <c r="D23" t="n">
+        <v>766.095</v>
+      </c>
+      <c r="E23" t="n">
+        <v>40.76573659673682</v>
+      </c>
+      <c r="F23" t="n">
+        <v>36.17563311312691</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>23</v>
+      </c>
+      <c r="B24" t="n">
+        <v>67.13200000000001</v>
+      </c>
+      <c r="C24" t="n">
+        <v>1.39321</v>
+      </c>
+      <c r="D24" t="n">
+        <v>738.2380000000001</v>
+      </c>
+      <c r="E24" t="n">
+        <v>61.30725641025651</v>
+      </c>
+      <c r="F24" t="n">
+        <v>34.86020276619556</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>24</v>
+      </c>
+      <c r="B25" t="n">
+        <v>69.116</v>
+      </c>
+      <c r="C25" t="n">
+        <v>1.35797</v>
+      </c>
+      <c r="D25" t="n">
+        <v>739.095</v>
+      </c>
+      <c r="E25" t="n">
+        <v>32.23910489510502</v>
+      </c>
+      <c r="F25" t="n">
+        <v>34.90067100783394</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>25</v>
+      </c>
+      <c r="B26" t="n">
+        <v>70.03700000000001</v>
+      </c>
+      <c r="C26" t="n">
+        <v>1.34235</v>
+      </c>
+      <c r="D26" t="n">
+        <v>739.048</v>
+      </c>
+      <c r="E26" t="n">
+        <v>39.71216317016319</v>
+      </c>
+      <c r="F26" t="n">
+        <v>34.89845162935435</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>26</v>
+      </c>
+      <c r="B27" t="n">
+        <v>70.85599999999999</v>
+      </c>
+      <c r="C27" t="n">
+        <v>1.32884</v>
+      </c>
+      <c r="D27" t="n">
+        <v>722.619</v>
+      </c>
+      <c r="E27" t="n">
+        <v>36.57724941724939</v>
+      </c>
+      <c r="F27" t="n">
+        <v>34.12266079869293</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>27</v>
+      </c>
+      <c r="B28" t="n">
+        <v>71.101</v>
+      </c>
+      <c r="C28" t="n">
+        <v>1.32485</v>
+      </c>
+      <c r="D28" t="n">
+        <v>711.048</v>
+      </c>
+      <c r="E28" t="n">
+        <v>36.80347086247093</v>
+      </c>
+      <c r="F28" t="n">
+        <v>33.57626870534681</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>28</v>
+      </c>
+      <c r="B29" t="n">
+        <v>71.69499999999999</v>
+      </c>
+      <c r="C29" t="n">
+        <v>1.31534</v>
+      </c>
+      <c r="D29" t="n">
+        <v>715.381</v>
+      </c>
+      <c r="E29" t="n">
+        <v>36.67449650349658</v>
+      </c>
+      <c r="F29" t="n">
+        <v>33.78087651283698</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>29</v>
+      </c>
+      <c r="B30" t="n">
+        <v>71.98099999999999</v>
+      </c>
+      <c r="C30" t="n">
+        <v>1.31081</v>
+      </c>
+      <c r="D30" t="n">
+        <v>700.571</v>
+      </c>
+      <c r="E30" t="n">
+        <v>43.91138927738939</v>
+      </c>
+      <c r="F30" t="n">
+        <v>33.08153618767442</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>30</v>
+      </c>
+      <c r="B31" t="n">
+        <v>73.004</v>
+      </c>
+      <c r="C31" t="n">
+        <v>1.29494</v>
+      </c>
+      <c r="D31" t="n">
+        <v>708.2859999999999</v>
+      </c>
+      <c r="E31" t="n">
+        <v>35.13585314685326</v>
+      </c>
+      <c r="F31" t="n">
+        <v>33.44584480405721</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>31</v>
+      </c>
+      <c r="B32" t="n">
         <v>74.31399999999999</v>
       </c>
-      <c r="C8" t="n">
+      <c r="C32" t="n">
         <v>1.27533</v>
       </c>
-      <c r="D8" t="n">
+      <c r="D32" t="n">
         <v>765.905</v>
       </c>
-      <c r="E8" t="n">
+      <c r="E32" t="n">
         <v>105.9533706293707</v>
       </c>
-      <c r="F8" t="n">
+      <c r="F32" t="n">
         <v>36.16666115757115</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>32</v>
+      </c>
+      <c r="B33" t="n">
+        <v>75.64400000000001</v>
+      </c>
+      <c r="C33" t="n">
+        <v>1.25617</v>
+      </c>
+      <c r="D33" t="n">
+        <v>693.381</v>
+      </c>
+      <c r="E33" t="n">
+        <v>38.79579720279753</v>
+      </c>
+      <c r="F33" t="n">
+        <v>32.74201850111677</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>33</v>
+      </c>
+      <c r="B34" t="n">
+        <v>77.813</v>
+      </c>
+      <c r="C34" t="n">
+        <v>1.22649</v>
+      </c>
+      <c r="D34" t="n">
+        <v>742.8099999999999</v>
+      </c>
+      <c r="E34" t="n">
+        <v>58.98606993007002</v>
+      </c>
+      <c r="F34" t="n">
+        <v>35.0760963493585</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>34</v>
+      </c>
+      <c r="B35" t="n">
+        <v>79</v>
+      </c>
+      <c r="C35" t="n">
+        <v>1.21102</v>
+      </c>
+      <c r="D35" t="n">
+        <v>738</v>
+      </c>
+      <c r="E35" t="n">
+        <v>42.10203496503505</v>
+      </c>
+      <c r="F35" t="n">
+        <v>34.8489642113415</v>
       </c>
     </row>
   </sheetData>
@@ -20706,7 +21246,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q24"/>
+  <dimension ref="A1:Q49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -20798,58 +21338,58 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B2" t="n">
-        <v>27.905</v>
+        <v>26.186</v>
       </c>
       <c r="C2" t="n">
-        <v>3.19472</v>
+        <v>3.4004</v>
       </c>
       <c r="D2" t="n">
-        <v>758.143</v>
+        <v>498.571</v>
       </c>
       <c r="E2" t="n">
-        <v>35.80013316270878</v>
+        <v>23.54293080733434</v>
       </c>
       <c r="F2" t="n">
-        <v>27.8619</v>
+        <v>26.2118</v>
       </c>
       <c r="G2" t="n">
-        <v>3.1995</v>
+        <v>3.397</v>
       </c>
       <c r="H2" t="n">
-        <v>261</v>
+        <v>43</v>
       </c>
       <c r="I2" t="n">
-        <v>26.12612612612612</v>
+        <v>43</v>
       </c>
       <c r="J2" t="n">
-        <v>0.04310000000000258</v>
+        <v>0.02580000000000027</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>1 0 1</t>
+          <t>4 4 0</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>CuS</t>
+          <t>Cu1.9375S</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>Covellite</t>
+          <t>Djurleite</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>CuS</t>
+          <t>Cu1.9375S</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>000752233</t>
+          <t>000711383</t>
         </is>
       </c>
       <c r="P2" t="n">
@@ -20863,38 +21403,38 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B3" t="n">
-        <v>27.905</v>
+        <v>26.186</v>
       </c>
       <c r="C3" t="n">
-        <v>3.19472</v>
+        <v>3.4004</v>
       </c>
       <c r="D3" t="n">
-        <v>758.143</v>
+        <v>498.571</v>
       </c>
       <c r="E3" t="n">
-        <v>35.80013316270878</v>
+        <v>23.54293080733434</v>
       </c>
       <c r="F3" t="n">
-        <v>27.8408</v>
+        <v>26.2118</v>
       </c>
       <c r="G3" t="n">
-        <v>3.2018</v>
+        <v>3.397</v>
       </c>
       <c r="H3" t="n">
-        <v>21</v>
+        <v>43</v>
       </c>
       <c r="I3" t="n">
-        <v>21</v>
+        <v>43</v>
       </c>
       <c r="J3" t="n">
-        <v>0.06419999999999959</v>
+        <v>0.02580000000000027</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>-3 3 3</t>
+          <t>-4 2 3</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -20928,58 +21468,58 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B4" t="n">
-        <v>27.905</v>
+        <v>26.186</v>
       </c>
       <c r="C4" t="n">
-        <v>3.19472</v>
+        <v>3.4004</v>
       </c>
       <c r="D4" t="n">
-        <v>758.143</v>
+        <v>498.571</v>
       </c>
       <c r="E4" t="n">
-        <v>35.80013316270878</v>
+        <v>23.54293080733434</v>
       </c>
       <c r="F4" t="n">
-        <v>27.8408</v>
+        <v>26.1259</v>
       </c>
       <c r="G4" t="n">
-        <v>3.2018</v>
+        <v>3.408</v>
       </c>
       <c r="H4" t="n">
-        <v>21</v>
+        <v>8</v>
       </c>
       <c r="I4" t="n">
-        <v>21</v>
+        <v>8</v>
       </c>
       <c r="J4" t="n">
-        <v>0.06419999999999959</v>
+        <v>0.06009999999999849</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>3 3 3</t>
+          <t>1 0 12</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>Cu1.9375S</t>
+          <t>Cu39S28</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>Djurleite</t>
+          <t>Spionkopite</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>Cu1.9375S</t>
+          <t>Cu39S28</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>000711383</t>
+          <t>000360380</t>
         </is>
       </c>
       <c r="P4" t="n">
@@ -20993,7 +21533,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="B5" t="n">
         <v>27.905</v>
@@ -21008,47 +21548,47 @@
         <v>35.80013316270878</v>
       </c>
       <c r="F5" t="n">
-        <v>27.6544</v>
+        <v>27.8619</v>
       </c>
       <c r="G5" t="n">
-        <v>3.223</v>
+        <v>3.1995</v>
       </c>
       <c r="H5" t="n">
-        <v>5</v>
+        <v>261</v>
       </c>
       <c r="I5" t="n">
-        <v>5</v>
+        <v>26.12612612612612</v>
       </c>
       <c r="J5" t="n">
-        <v>0.2506000000000022</v>
+        <v>0.04310000000000258</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>6 0 3</t>
+          <t>1 0 1</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>Cu39S28</t>
+          <t>CuS</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>Spionkopite</t>
+          <t>Covellite</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>Cu39S28</t>
+          <t>CuS</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>000360380</t>
+          <t>000752233</t>
         </is>
       </c>
       <c r="P5" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
@@ -21058,62 +21598,62 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
+        <v>4</v>
+      </c>
+      <c r="B6" t="n">
+        <v>27.905</v>
+      </c>
+      <c r="C6" t="n">
+        <v>3.19472</v>
+      </c>
+      <c r="D6" t="n">
+        <v>758.143</v>
+      </c>
+      <c r="E6" t="n">
+        <v>35.80013316270878</v>
+      </c>
+      <c r="F6" t="n">
+        <v>27.8408</v>
+      </c>
+      <c r="G6" t="n">
+        <v>3.2018</v>
+      </c>
+      <c r="H6" t="n">
+        <v>21</v>
+      </c>
+      <c r="I6" t="n">
+        <v>21</v>
+      </c>
+      <c r="J6" t="n">
+        <v>0.06419999999999959</v>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>-3 3 3</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>Cu1.9375S</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>Djurleite</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>Cu1.9375S</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>000711383</t>
+        </is>
+      </c>
+      <c r="P6" t="n">
         <v>2</v>
-      </c>
-      <c r="B6" t="n">
-        <v>29.501</v>
-      </c>
-      <c r="C6" t="n">
-        <v>3.02541</v>
-      </c>
-      <c r="D6" t="n">
-        <v>1238.62</v>
-      </c>
-      <c r="E6" t="n">
-        <v>58.48865047622195</v>
-      </c>
-      <c r="F6" t="n">
-        <v>29.4683</v>
-      </c>
-      <c r="G6" t="n">
-        <v>3.0286</v>
-      </c>
-      <c r="H6" t="n">
-        <v>572</v>
-      </c>
-      <c r="I6" t="n">
-        <v>57.25725725725725</v>
-      </c>
-      <c r="J6" t="n">
-        <v>0.03270000000000195</v>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>1 0 2</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>CuS</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>Covellite</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>CuS</t>
-        </is>
-      </c>
-      <c r="O6" t="inlineStr">
-        <is>
-          <t>000752233</t>
-        </is>
-      </c>
-      <c r="P6" t="n">
-        <v>1</v>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
@@ -21123,38 +21663,38 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="B7" t="n">
-        <v>29.501</v>
+        <v>27.905</v>
       </c>
       <c r="C7" t="n">
-        <v>3.02541</v>
+        <v>3.19472</v>
       </c>
       <c r="D7" t="n">
-        <v>1238.62</v>
+        <v>758.143</v>
       </c>
       <c r="E7" t="n">
-        <v>58.48865047622195</v>
+        <v>35.80013316270878</v>
       </c>
       <c r="F7" t="n">
-        <v>29.5944</v>
+        <v>27.8408</v>
       </c>
       <c r="G7" t="n">
-        <v>3.016</v>
+        <v>3.2018</v>
       </c>
       <c r="H7" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="I7" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="J7" t="n">
-        <v>0.09339999999999904</v>
+        <v>0.06419999999999959</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>-8 2 1</t>
+          <t>3 3 3</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -21178,7 +21718,7 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
@@ -21188,62 +21728,62 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="B8" t="n">
-        <v>29.501</v>
+        <v>27.905</v>
       </c>
       <c r="C8" t="n">
-        <v>3.02541</v>
+        <v>3.19472</v>
       </c>
       <c r="D8" t="n">
-        <v>1238.62</v>
+        <v>758.143</v>
       </c>
       <c r="E8" t="n">
-        <v>58.48865047622195</v>
+        <v>35.80013316270878</v>
       </c>
       <c r="F8" t="n">
-        <v>29.5944</v>
+        <v>27.6544</v>
       </c>
       <c r="G8" t="n">
-        <v>3.016</v>
+        <v>3.223</v>
       </c>
       <c r="H8" t="n">
-        <v>23</v>
+        <v>5</v>
       </c>
       <c r="I8" t="n">
-        <v>23</v>
+        <v>5</v>
       </c>
       <c r="J8" t="n">
-        <v>0.09339999999999904</v>
+        <v>0.2506000000000022</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>-8 0 2</t>
+          <t>6 0 3</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>Cu1.9375S</t>
+          <t>Cu39S28</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>Djurleite</t>
+          <t>Spionkopite</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>Cu1.9375S</t>
+          <t>Cu39S28</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>000711383</t>
+          <t>000360380</t>
         </is>
       </c>
       <c r="P8" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
@@ -21253,7 +21793,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="B9" t="n">
         <v>29.501</v>
@@ -21268,47 +21808,47 @@
         <v>58.48865047622195</v>
       </c>
       <c r="F9" t="n">
-        <v>29.3679</v>
+        <v>29.4683</v>
       </c>
       <c r="G9" t="n">
-        <v>3.0387</v>
+        <v>3.0286</v>
       </c>
       <c r="H9" t="n">
-        <v>16</v>
+        <v>572</v>
       </c>
       <c r="I9" t="n">
-        <v>16</v>
+        <v>57.25725725725725</v>
       </c>
       <c r="J9" t="n">
-        <v>0.1331000000000024</v>
+        <v>0.03270000000000195</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>-4 4 2</t>
+          <t>1 0 2</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>Cu1.9375S</t>
+          <t>CuS</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>Djurleite</t>
+          <t>Covellite</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>Cu1.9375S</t>
+          <t>CuS</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>000711383</t>
+          <t>000752233</t>
         </is>
       </c>
       <c r="P9" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
@@ -21318,7 +21858,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="B10" t="n">
         <v>29.501</v>
@@ -21333,23 +21873,23 @@
         <v>58.48865047622195</v>
       </c>
       <c r="F10" t="n">
-        <v>29.3679</v>
+        <v>29.5944</v>
       </c>
       <c r="G10" t="n">
-        <v>3.0387</v>
+        <v>3.016</v>
       </c>
       <c r="H10" t="n">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="I10" t="n">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="J10" t="n">
-        <v>0.1331000000000024</v>
+        <v>0.09339999999999904</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>4 4 2</t>
+          <t>-8 2 1</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
@@ -21373,7 +21913,7 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
@@ -21383,7 +21923,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="B11" t="n">
         <v>29.501</v>
@@ -21398,23 +21938,23 @@
         <v>58.48865047622195</v>
       </c>
       <c r="F11" t="n">
-        <v>29.6586</v>
+        <v>29.5944</v>
       </c>
       <c r="G11" t="n">
-        <v>3.0096</v>
+        <v>3.016</v>
       </c>
       <c r="H11" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="I11" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="J11" t="n">
-        <v>0.1575999999999986</v>
+        <v>0.09339999999999904</v>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>8 0 2</t>
+          <t>-8 0 2</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
@@ -21438,7 +21978,7 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
@@ -21448,7 +21988,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="B12" t="n">
         <v>29.501</v>
@@ -21463,23 +22003,23 @@
         <v>58.48865047622195</v>
       </c>
       <c r="F12" t="n">
-        <v>29.2781</v>
+        <v>29.3679</v>
       </c>
       <c r="G12" t="n">
-        <v>3.0478</v>
+        <v>3.0387</v>
       </c>
       <c r="H12" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I12" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="J12" t="n">
-        <v>0.2229000000000028</v>
+        <v>0.1331000000000024</v>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>4 3 3</t>
+          <t>-4 4 2</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
@@ -21503,7 +22043,7 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
@@ -21513,7 +22053,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="B13" t="n">
         <v>29.501</v>
@@ -21528,23 +22068,23 @@
         <v>58.48865047622195</v>
       </c>
       <c r="F13" t="n">
-        <v>29.2781</v>
+        <v>29.3679</v>
       </c>
       <c r="G13" t="n">
-        <v>3.0478</v>
+        <v>3.0387</v>
       </c>
       <c r="H13" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I13" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="J13" t="n">
-        <v>0.2229000000000028</v>
+        <v>0.1331000000000024</v>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>-1 5 1</t>
+          <t>4 4 2</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
@@ -21568,7 +22108,7 @@
         </is>
       </c>
       <c r="P13" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
@@ -21578,62 +22118,62 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="B14" t="n">
-        <v>32.018</v>
+        <v>29.501</v>
       </c>
       <c r="C14" t="n">
-        <v>2.7931</v>
+        <v>3.02541</v>
       </c>
       <c r="D14" t="n">
-        <v>1335.95</v>
+        <v>1238.62</v>
       </c>
       <c r="E14" t="n">
-        <v>63.08465276170958</v>
+        <v>58.48865047622195</v>
       </c>
       <c r="F14" t="n">
-        <v>32.0508</v>
+        <v>29.6586</v>
       </c>
       <c r="G14" t="n">
-        <v>2.7902</v>
+        <v>3.0096</v>
       </c>
       <c r="H14" t="n">
+        <v>21</v>
+      </c>
+      <c r="I14" t="n">
+        <v>21</v>
+      </c>
+      <c r="J14" t="n">
+        <v>0.1575999999999986</v>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>8 0 2</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>Cu1.9375S</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>Djurleite</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>Cu1.9375S</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>000711383</t>
+        </is>
+      </c>
+      <c r="P14" t="n">
         <v>6</v>
-      </c>
-      <c r="I14" t="n">
-        <v>6</v>
-      </c>
-      <c r="J14" t="n">
-        <v>0.03280000000000172</v>
-      </c>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>2 5 2</t>
-        </is>
-      </c>
-      <c r="L14" t="inlineStr">
-        <is>
-          <t>Cu1.9375S</t>
-        </is>
-      </c>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>Djurleite</t>
-        </is>
-      </c>
-      <c r="N14" t="inlineStr">
-        <is>
-          <t>Cu1.9375S</t>
-        </is>
-      </c>
-      <c r="O14" t="inlineStr">
-        <is>
-          <t>000711383</t>
-        </is>
-      </c>
-      <c r="P14" t="n">
-        <v>1</v>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
@@ -21643,38 +22183,38 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="B15" t="n">
-        <v>32.018</v>
+        <v>29.501</v>
       </c>
       <c r="C15" t="n">
-        <v>2.7931</v>
+        <v>3.02541</v>
       </c>
       <c r="D15" t="n">
-        <v>1335.95</v>
+        <v>1238.62</v>
       </c>
       <c r="E15" t="n">
-        <v>63.08465276170958</v>
+        <v>58.48865047622195</v>
       </c>
       <c r="F15" t="n">
-        <v>32.0508</v>
+        <v>29.2781</v>
       </c>
       <c r="G15" t="n">
-        <v>2.7902</v>
+        <v>3.0478</v>
       </c>
       <c r="H15" t="n">
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="I15" t="n">
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="J15" t="n">
-        <v>0.03280000000000172</v>
+        <v>0.2229000000000028</v>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>4 5 1</t>
+          <t>4 3 3</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
@@ -21698,7 +22238,7 @@
         </is>
       </c>
       <c r="P15" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
@@ -21708,62 +22248,62 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="B16" t="n">
-        <v>32.018</v>
+        <v>29.501</v>
       </c>
       <c r="C16" t="n">
-        <v>2.7931</v>
+        <v>3.02541</v>
       </c>
       <c r="D16" t="n">
-        <v>1335.95</v>
+        <v>1238.62</v>
       </c>
       <c r="E16" t="n">
-        <v>63.08465276170958</v>
+        <v>58.48865047622195</v>
       </c>
       <c r="F16" t="n">
-        <v>31.982</v>
+        <v>29.2781</v>
       </c>
       <c r="G16" t="n">
-        <v>2.7961</v>
+        <v>3.0478</v>
       </c>
       <c r="H16" t="n">
-        <v>999</v>
+        <v>17</v>
       </c>
       <c r="I16" t="n">
-        <v>100</v>
+        <v>17</v>
       </c>
       <c r="J16" t="n">
-        <v>0.03600000000000136</v>
+        <v>0.2229000000000028</v>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>1 0 3</t>
+          <t>-1 5 1</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>CuS</t>
+          <t>Cu1.9375S</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>Covellite</t>
+          <t>Djurleite</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>CuS</t>
+          <t>Cu1.9375S</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>000752233</t>
+          <t>000711383</t>
         </is>
       </c>
       <c r="P16" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
@@ -21773,7 +22313,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="B17" t="n">
         <v>32.018</v>
@@ -21788,47 +22328,47 @@
         <v>63.08465276170958</v>
       </c>
       <c r="F17" t="n">
-        <v>32.2076</v>
+        <v>32.0508</v>
       </c>
       <c r="G17" t="n">
-        <v>2.777</v>
+        <v>2.7902</v>
       </c>
       <c r="H17" t="n">
-        <v>30</v>
+        <v>6</v>
       </c>
       <c r="I17" t="n">
-        <v>30</v>
+        <v>6</v>
       </c>
       <c r="J17" t="n">
-        <v>0.1895999999999987</v>
+        <v>0.03280000000000172</v>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>6 0 8</t>
+          <t>2 5 2</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>Cu39S28</t>
+          <t>Cu1.9375S</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>Spionkopite</t>
+          <t>Djurleite</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>Cu39S28</t>
+          <t>Cu1.9375S</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>000360380</t>
+          <t>000711383</t>
         </is>
       </c>
       <c r="P17" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
@@ -21838,7 +22378,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="B18" t="n">
         <v>32.018</v>
@@ -21853,23 +22393,23 @@
         <v>63.08465276170958</v>
       </c>
       <c r="F18" t="n">
-        <v>31.7366</v>
+        <v>32.0508</v>
       </c>
       <c r="G18" t="n">
-        <v>2.8171</v>
+        <v>2.7902</v>
       </c>
       <c r="H18" t="n">
-        <v>17</v>
+        <v>6</v>
       </c>
       <c r="I18" t="n">
-        <v>17</v>
+        <v>6</v>
       </c>
       <c r="J18" t="n">
-        <v>0.2814000000000014</v>
+        <v>0.03280000000000172</v>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>-3 4 3</t>
+          <t>4 5 1</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
@@ -21893,7 +22433,7 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
@@ -21903,7 +22443,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="B19" t="n">
         <v>32.018</v>
@@ -21918,47 +22458,47 @@
         <v>63.08465276170958</v>
       </c>
       <c r="F19" t="n">
-        <v>31.7366</v>
+        <v>31.982</v>
       </c>
       <c r="G19" t="n">
-        <v>2.8171</v>
+        <v>2.7961</v>
       </c>
       <c r="H19" t="n">
-        <v>17</v>
+        <v>999</v>
       </c>
       <c r="I19" t="n">
-        <v>17</v>
+        <v>100</v>
       </c>
       <c r="J19" t="n">
-        <v>0.2814000000000014</v>
+        <v>0.03600000000000136</v>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>3 4 3</t>
+          <t>1 0 3</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>Cu1.9375S</t>
+          <t>CuS</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>Djurleite</t>
+          <t>Covellite</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>Cu1.9375S</t>
+          <t>CuS</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>000711383</t>
+          <t>000752233</t>
         </is>
       </c>
       <c r="P19" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
@@ -21968,62 +22508,62 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
+        <v>6</v>
+      </c>
+      <c r="B20" t="n">
+        <v>32.018</v>
+      </c>
+      <c r="C20" t="n">
+        <v>2.7931</v>
+      </c>
+      <c r="D20" t="n">
+        <v>1335.95</v>
+      </c>
+      <c r="E20" t="n">
+        <v>63.08465276170958</v>
+      </c>
+      <c r="F20" t="n">
+        <v>32.2076</v>
+      </c>
+      <c r="G20" t="n">
+        <v>2.777</v>
+      </c>
+      <c r="H20" t="n">
+        <v>30</v>
+      </c>
+      <c r="I20" t="n">
+        <v>30</v>
+      </c>
+      <c r="J20" t="n">
+        <v>0.1895999999999987</v>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>6 0 8</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>Cu39S28</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>Spionkopite</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>Cu39S28</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>000360380</t>
+        </is>
+      </c>
+      <c r="P20" t="n">
         <v>4</v>
-      </c>
-      <c r="B20" t="n">
-        <v>48.224</v>
-      </c>
-      <c r="C20" t="n">
-        <v>1.88557</v>
-      </c>
-      <c r="D20" t="n">
-        <v>2117.71</v>
-      </c>
-      <c r="E20" t="n">
-        <v>100</v>
-      </c>
-      <c r="F20" t="n">
-        <v>48.2657</v>
-      </c>
-      <c r="G20" t="n">
-        <v>1.884</v>
-      </c>
-      <c r="H20" t="n">
-        <v>618</v>
-      </c>
-      <c r="I20" t="n">
-        <v>61.86186186186187</v>
-      </c>
-      <c r="J20" t="n">
-        <v>0.04170000000000584</v>
-      </c>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>1 1 0</t>
-        </is>
-      </c>
-      <c r="L20" t="inlineStr">
-        <is>
-          <t>CuS</t>
-        </is>
-      </c>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>Covellite</t>
-        </is>
-      </c>
-      <c r="N20" t="inlineStr">
-        <is>
-          <t>CuS</t>
-        </is>
-      </c>
-      <c r="O20" t="inlineStr">
-        <is>
-          <t>000752233</t>
-        </is>
-      </c>
-      <c r="P20" t="n">
-        <v>1</v>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
@@ -22033,62 +22573,62 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="B21" t="n">
-        <v>48.224</v>
+        <v>32.018</v>
       </c>
       <c r="C21" t="n">
-        <v>1.88557</v>
+        <v>2.7931</v>
       </c>
       <c r="D21" t="n">
-        <v>2117.71</v>
+        <v>1335.95</v>
       </c>
       <c r="E21" t="n">
-        <v>100</v>
+        <v>63.08465276170958</v>
       </c>
       <c r="F21" t="n">
-        <v>48.0177</v>
+        <v>31.7366</v>
       </c>
       <c r="G21" t="n">
-        <v>1.8931</v>
+        <v>2.8171</v>
       </c>
       <c r="H21" t="n">
-        <v>165</v>
+        <v>17</v>
       </c>
       <c r="I21" t="n">
-        <v>16.51651651651652</v>
+        <v>17</v>
       </c>
       <c r="J21" t="n">
-        <v>0.2062999999999988</v>
+        <v>0.2814000000000014</v>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>1 0 7</t>
+          <t>-3 4 3</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>CuS</t>
+          <t>Cu1.9375S</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>Covellite</t>
+          <t>Djurleite</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>CuS</t>
+          <t>Cu1.9375S</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>000752233</t>
+          <t>000711383</t>
         </is>
       </c>
       <c r="P21" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
@@ -22098,62 +22638,62 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B22" t="n">
-        <v>53.012</v>
+        <v>32.018</v>
       </c>
       <c r="C22" t="n">
-        <v>1.72599</v>
+        <v>2.7931</v>
       </c>
       <c r="D22" t="n">
-        <v>1007.48</v>
+        <v>1335.95</v>
       </c>
       <c r="E22" t="n">
-        <v>47.57403043853974</v>
+        <v>63.08465276170958</v>
       </c>
       <c r="F22" t="n">
-        <v>53.0112</v>
+        <v>31.7366</v>
       </c>
       <c r="G22" t="n">
-        <v>1.726</v>
+        <v>2.8171</v>
       </c>
       <c r="H22" t="n">
-        <v>256</v>
+        <v>17</v>
       </c>
       <c r="I22" t="n">
-        <v>25.62562562562562</v>
+        <v>17</v>
       </c>
       <c r="J22" t="n">
-        <v>0.0007999999999981355</v>
+        <v>0.2814000000000014</v>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>1 0 8</t>
+          <t>3 4 3</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>CuS</t>
+          <t>Cu1.9375S</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>Covellite</t>
+          <t>Djurleite</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>CuS</t>
+          <t>Cu1.9375S</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>000752233</t>
+          <t>000711383</t>
         </is>
       </c>
       <c r="P22" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
@@ -22163,58 +22703,58 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B23" t="n">
-        <v>59.376</v>
+        <v>32.304</v>
       </c>
       <c r="C23" t="n">
-        <v>1.55528</v>
+        <v>2.76898</v>
       </c>
       <c r="D23" t="n">
-        <v>1194.52</v>
+        <v>1318.29</v>
       </c>
       <c r="E23" t="n">
-        <v>56.40621237091008</v>
+        <v>62.25073310321054</v>
       </c>
       <c r="F23" t="n">
-        <v>59.0765</v>
+        <v>32.2076</v>
       </c>
       <c r="G23" t="n">
-        <v>1.5624</v>
+        <v>2.777</v>
       </c>
       <c r="H23" t="n">
-        <v>104</v>
+        <v>30</v>
       </c>
       <c r="I23" t="n">
-        <v>10.41041041041041</v>
+        <v>30</v>
       </c>
       <c r="J23" t="n">
-        <v>0.2994999999999948</v>
+        <v>0.09640000000000271</v>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>2 0 3</t>
+          <t>6 0 8</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>CuS</t>
+          <t>Cu39S28</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>Covellite</t>
+          <t>Spionkopite</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>CuS</t>
+          <t>Cu39S28</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>000752233</t>
+          <t>000360380</t>
         </is>
       </c>
       <c r="P23" t="n">
@@ -22231,61 +22771,1686 @@
         <v>7</v>
       </c>
       <c r="B24" t="n">
+        <v>32.304</v>
+      </c>
+      <c r="C24" t="n">
+        <v>2.76898</v>
+      </c>
+      <c r="D24" t="n">
+        <v>1318.29</v>
+      </c>
+      <c r="E24" t="n">
+        <v>62.25073310321054</v>
+      </c>
+      <c r="F24" t="n">
+        <v>32.0508</v>
+      </c>
+      <c r="G24" t="n">
+        <v>2.7902</v>
+      </c>
+      <c r="H24" t="n">
+        <v>6</v>
+      </c>
+      <c r="I24" t="n">
+        <v>6</v>
+      </c>
+      <c r="J24" t="n">
+        <v>0.2531999999999996</v>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>2 5 2</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>Cu1.9375S</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>Djurleite</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>Cu1.9375S</t>
+        </is>
+      </c>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>000711383</t>
+        </is>
+      </c>
+      <c r="P24" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q24" t="inlineStr">
+        <is>
+          <t>MATCH</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>7</v>
+      </c>
+      <c r="B25" t="n">
+        <v>32.304</v>
+      </c>
+      <c r="C25" t="n">
+        <v>2.76898</v>
+      </c>
+      <c r="D25" t="n">
+        <v>1318.29</v>
+      </c>
+      <c r="E25" t="n">
+        <v>62.25073310321054</v>
+      </c>
+      <c r="F25" t="n">
+        <v>32.0508</v>
+      </c>
+      <c r="G25" t="n">
+        <v>2.7902</v>
+      </c>
+      <c r="H25" t="n">
+        <v>6</v>
+      </c>
+      <c r="I25" t="n">
+        <v>6</v>
+      </c>
+      <c r="J25" t="n">
+        <v>0.2531999999999996</v>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>4 5 1</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>Cu1.9375S</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>Djurleite</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>Cu1.9375S</t>
+        </is>
+      </c>
+      <c r="O25" t="inlineStr">
+        <is>
+          <t>000711383</t>
+        </is>
+      </c>
+      <c r="P25" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q25" t="inlineStr">
+        <is>
+          <t>MATCH</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>8</v>
+      </c>
+      <c r="B26" t="n">
+        <v>34.903</v>
+      </c>
+      <c r="C26" t="n">
+        <v>2.56853</v>
+      </c>
+      <c r="D26" t="n">
+        <v>635.429</v>
+      </c>
+      <c r="E26" t="n">
+        <v>30.00547761497089</v>
+      </c>
+      <c r="F26" t="n">
+        <v>34.8545</v>
+      </c>
+      <c r="G26" t="n">
+        <v>2.5719</v>
+      </c>
+      <c r="H26" t="n">
+        <v>16</v>
+      </c>
+      <c r="I26" t="n">
+        <v>16</v>
+      </c>
+      <c r="J26" t="n">
+        <v>0.0484999999999971</v>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>-1 5 3</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>Cu1.9375S</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>Djurleite</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>Cu1.9375S</t>
+        </is>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>000711383</t>
+        </is>
+      </c>
+      <c r="P26" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q26" t="inlineStr">
+        <is>
+          <t>MATCH</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>8</v>
+      </c>
+      <c r="B27" t="n">
+        <v>34.903</v>
+      </c>
+      <c r="C27" t="n">
+        <v>2.56853</v>
+      </c>
+      <c r="D27" t="n">
+        <v>635.429</v>
+      </c>
+      <c r="E27" t="n">
+        <v>30.00547761497089</v>
+      </c>
+      <c r="F27" t="n">
+        <v>34.8545</v>
+      </c>
+      <c r="G27" t="n">
+        <v>2.5719</v>
+      </c>
+      <c r="H27" t="n">
+        <v>16</v>
+      </c>
+      <c r="I27" t="n">
+        <v>16</v>
+      </c>
+      <c r="J27" t="n">
+        <v>0.0484999999999971</v>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>1 5 3</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>Cu1.9375S</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>Djurleite</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>Cu1.9375S</t>
+        </is>
+      </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>000711383</t>
+        </is>
+      </c>
+      <c r="P27" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q27" t="inlineStr">
+        <is>
+          <t>MATCH</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>8</v>
+      </c>
+      <c r="B28" t="n">
+        <v>34.903</v>
+      </c>
+      <c r="C28" t="n">
+        <v>2.56853</v>
+      </c>
+      <c r="D28" t="n">
+        <v>635.429</v>
+      </c>
+      <c r="E28" t="n">
+        <v>30.00547761497089</v>
+      </c>
+      <c r="F28" t="n">
+        <v>34.9523</v>
+      </c>
+      <c r="G28" t="n">
+        <v>2.565</v>
+      </c>
+      <c r="H28" t="n">
+        <v>17</v>
+      </c>
+      <c r="I28" t="n">
+        <v>17</v>
+      </c>
+      <c r="J28" t="n">
+        <v>0.04930000000000234</v>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>0 2 5</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>Cu1.9375S</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>Djurleite</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>Cu1.9375S</t>
+        </is>
+      </c>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>000711383</t>
+        </is>
+      </c>
+      <c r="P28" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q28" t="inlineStr">
+        <is>
+          <t>MATCH</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>8</v>
+      </c>
+      <c r="B29" t="n">
+        <v>34.903</v>
+      </c>
+      <c r="C29" t="n">
+        <v>2.56853</v>
+      </c>
+      <c r="D29" t="n">
+        <v>635.429</v>
+      </c>
+      <c r="E29" t="n">
+        <v>30.00547761497089</v>
+      </c>
+      <c r="F29" t="n">
+        <v>34.9523</v>
+      </c>
+      <c r="G29" t="n">
+        <v>2.565</v>
+      </c>
+      <c r="H29" t="n">
+        <v>17</v>
+      </c>
+      <c r="I29" t="n">
+        <v>17</v>
+      </c>
+      <c r="J29" t="n">
+        <v>0.04930000000000234</v>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>-1 6 1</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>Cu1.9375S</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>Djurleite</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>Cu1.9375S</t>
+        </is>
+      </c>
+      <c r="O29" t="inlineStr">
+        <is>
+          <t>000711383</t>
+        </is>
+      </c>
+      <c r="P29" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q29" t="inlineStr">
+        <is>
+          <t>MATCH</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>8</v>
+      </c>
+      <c r="B30" t="n">
+        <v>34.903</v>
+      </c>
+      <c r="C30" t="n">
+        <v>2.56853</v>
+      </c>
+      <c r="D30" t="n">
+        <v>635.429</v>
+      </c>
+      <c r="E30" t="n">
+        <v>30.00547761497089</v>
+      </c>
+      <c r="F30" t="n">
+        <v>35.0147</v>
+      </c>
+      <c r="G30" t="n">
+        <v>2.5605</v>
+      </c>
+      <c r="H30" t="n">
+        <v>18</v>
+      </c>
+      <c r="I30" t="n">
+        <v>18</v>
+      </c>
+      <c r="J30" t="n">
+        <v>0.111699999999999</v>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>3 1 5</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>Cu1.9375S</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>Djurleite</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>Cu1.9375S</t>
+        </is>
+      </c>
+      <c r="O30" t="inlineStr">
+        <is>
+          <t>000711383</t>
+        </is>
+      </c>
+      <c r="P30" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q30" t="inlineStr">
+        <is>
+          <t>MATCH</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>8</v>
+      </c>
+      <c r="B31" t="n">
+        <v>34.903</v>
+      </c>
+      <c r="C31" t="n">
+        <v>2.56853</v>
+      </c>
+      <c r="D31" t="n">
+        <v>635.429</v>
+      </c>
+      <c r="E31" t="n">
+        <v>30.00547761497089</v>
+      </c>
+      <c r="F31" t="n">
+        <v>35.0147</v>
+      </c>
+      <c r="G31" t="n">
+        <v>2.5605</v>
+      </c>
+      <c r="H31" t="n">
+        <v>18</v>
+      </c>
+      <c r="I31" t="n">
+        <v>18</v>
+      </c>
+      <c r="J31" t="n">
+        <v>0.111699999999999</v>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>-6 2 4</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>Cu1.9375S</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>Djurleite</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>Cu1.9375S</t>
+        </is>
+      </c>
+      <c r="O31" t="inlineStr">
+        <is>
+          <t>000711383</t>
+        </is>
+      </c>
+      <c r="P31" t="n">
+        <v>6</v>
+      </c>
+      <c r="Q31" t="inlineStr">
+        <is>
+          <t>MATCH</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>8</v>
+      </c>
+      <c r="B32" t="n">
+        <v>34.903</v>
+      </c>
+      <c r="C32" t="n">
+        <v>2.56853</v>
+      </c>
+      <c r="D32" t="n">
+        <v>635.429</v>
+      </c>
+      <c r="E32" t="n">
+        <v>30.00547761497089</v>
+      </c>
+      <c r="F32" t="n">
+        <v>35.0955</v>
+      </c>
+      <c r="G32" t="n">
+        <v>2.5548</v>
+      </c>
+      <c r="H32" t="n">
+        <v>14</v>
+      </c>
+      <c r="I32" t="n">
+        <v>14</v>
+      </c>
+      <c r="J32" t="n">
+        <v>0.1925000000000026</v>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>7 3 3</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>Cu1.9375S</t>
+        </is>
+      </c>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>Djurleite</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>Cu1.9375S</t>
+        </is>
+      </c>
+      <c r="O32" t="inlineStr">
+        <is>
+          <t>000711383</t>
+        </is>
+      </c>
+      <c r="P32" t="n">
+        <v>7</v>
+      </c>
+      <c r="Q32" t="inlineStr">
+        <is>
+          <t>MATCH</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>8</v>
+      </c>
+      <c r="B33" t="n">
+        <v>34.903</v>
+      </c>
+      <c r="C33" t="n">
+        <v>2.56853</v>
+      </c>
+      <c r="D33" t="n">
+        <v>635.429</v>
+      </c>
+      <c r="E33" t="n">
+        <v>30.00547761497089</v>
+      </c>
+      <c r="F33" t="n">
+        <v>35.0955</v>
+      </c>
+      <c r="G33" t="n">
+        <v>2.5548</v>
+      </c>
+      <c r="H33" t="n">
+        <v>14</v>
+      </c>
+      <c r="I33" t="n">
+        <v>14</v>
+      </c>
+      <c r="J33" t="n">
+        <v>0.1925000000000026</v>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>-8 2 3</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>Cu1.9375S</t>
+        </is>
+      </c>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>Djurleite</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>Cu1.9375S</t>
+        </is>
+      </c>
+      <c r="O33" t="inlineStr">
+        <is>
+          <t>000711383</t>
+        </is>
+      </c>
+      <c r="P33" t="n">
+        <v>8</v>
+      </c>
+      <c r="Q33" t="inlineStr">
+        <is>
+          <t>MATCH</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>9</v>
+      </c>
+      <c r="B34" t="n">
+        <v>38.73</v>
+      </c>
+      <c r="C34" t="n">
+        <v>2.32311</v>
+      </c>
+      <c r="D34" t="n">
+        <v>692.952</v>
+      </c>
+      <c r="E34" t="n">
+        <v>32.72176076988823</v>
+      </c>
+      <c r="F34" t="n">
+        <v>38.7261</v>
+      </c>
+      <c r="G34" t="n">
+        <v>2.3233</v>
+      </c>
+      <c r="H34" t="n">
+        <v>8</v>
+      </c>
+      <c r="I34" t="n">
+        <v>8</v>
+      </c>
+      <c r="J34" t="n">
+        <v>0.003899999999994463</v>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>-5 6 1</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>Cu1.9375S</t>
+        </is>
+      </c>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>Djurleite</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>Cu1.9375S</t>
+        </is>
+      </c>
+      <c r="O34" t="inlineStr">
+        <is>
+          <t>000711383</t>
+        </is>
+      </c>
+      <c r="P34" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q34" t="inlineStr">
+        <is>
+          <t>MATCH</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>9</v>
+      </c>
+      <c r="B35" t="n">
+        <v>38.73</v>
+      </c>
+      <c r="C35" t="n">
+        <v>2.32311</v>
+      </c>
+      <c r="D35" t="n">
+        <v>692.952</v>
+      </c>
+      <c r="E35" t="n">
+        <v>32.72176076988823</v>
+      </c>
+      <c r="F35" t="n">
+        <v>38.7261</v>
+      </c>
+      <c r="G35" t="n">
+        <v>2.3233</v>
+      </c>
+      <c r="H35" t="n">
+        <v>8</v>
+      </c>
+      <c r="I35" t="n">
+        <v>8</v>
+      </c>
+      <c r="J35" t="n">
+        <v>0.003899999999994463</v>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>5 6 1</t>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>Cu1.9375S</t>
+        </is>
+      </c>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>Djurleite</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>Cu1.9375S</t>
+        </is>
+      </c>
+      <c r="O35" t="inlineStr">
+        <is>
+          <t>000711383</t>
+        </is>
+      </c>
+      <c r="P35" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q35" t="inlineStr">
+        <is>
+          <t>MATCH</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>9</v>
+      </c>
+      <c r="B36" t="n">
+        <v>38.73</v>
+      </c>
+      <c r="C36" t="n">
+        <v>2.32311</v>
+      </c>
+      <c r="D36" t="n">
+        <v>692.952</v>
+      </c>
+      <c r="E36" t="n">
+        <v>32.72176076988823</v>
+      </c>
+      <c r="F36" t="n">
+        <v>38.642</v>
+      </c>
+      <c r="G36" t="n">
+        <v>2.3281</v>
+      </c>
+      <c r="H36" t="n">
+        <v>6</v>
+      </c>
+      <c r="I36" t="n">
+        <v>6</v>
+      </c>
+      <c r="J36" t="n">
+        <v>0.08799999999999386</v>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>-3 3 5</t>
+        </is>
+      </c>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>Cu1.9375S</t>
+        </is>
+      </c>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>Djurleite</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t>Cu1.9375S</t>
+        </is>
+      </c>
+      <c r="O36" t="inlineStr">
+        <is>
+          <t>000711383</t>
+        </is>
+      </c>
+      <c r="P36" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q36" t="inlineStr">
+        <is>
+          <t>MATCH</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>9</v>
+      </c>
+      <c r="B37" t="n">
+        <v>38.73</v>
+      </c>
+      <c r="C37" t="n">
+        <v>2.32311</v>
+      </c>
+      <c r="D37" t="n">
+        <v>692.952</v>
+      </c>
+      <c r="E37" t="n">
+        <v>32.72176076988823</v>
+      </c>
+      <c r="F37" t="n">
+        <v>38.642</v>
+      </c>
+      <c r="G37" t="n">
+        <v>2.3281</v>
+      </c>
+      <c r="H37" t="n">
+        <v>6</v>
+      </c>
+      <c r="I37" t="n">
+        <v>6</v>
+      </c>
+      <c r="J37" t="n">
+        <v>0.08799999999999386</v>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>5 5 3</t>
+        </is>
+      </c>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>Cu1.9375S</t>
+        </is>
+      </c>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>Djurleite</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr">
+        <is>
+          <t>Cu1.9375S</t>
+        </is>
+      </c>
+      <c r="O37" t="inlineStr">
+        <is>
+          <t>000711383</t>
+        </is>
+      </c>
+      <c r="P37" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q37" t="inlineStr">
+        <is>
+          <t>MATCH</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>9</v>
+      </c>
+      <c r="B38" t="n">
+        <v>38.73</v>
+      </c>
+      <c r="C38" t="n">
+        <v>2.32311</v>
+      </c>
+      <c r="D38" t="n">
+        <v>692.952</v>
+      </c>
+      <c r="E38" t="n">
+        <v>32.72176076988823</v>
+      </c>
+      <c r="F38" t="n">
+        <v>38.8318</v>
+      </c>
+      <c r="G38" t="n">
+        <v>2.3172</v>
+      </c>
+      <c r="H38" t="n">
+        <v>6</v>
+      </c>
+      <c r="I38" t="n">
+        <v>6</v>
+      </c>
+      <c r="J38" t="n">
+        <v>0.1018000000000043</v>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>-5 2 5</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>Cu1.9375S</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>Djurleite</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>Cu1.9375S</t>
+        </is>
+      </c>
+      <c r="O38" t="inlineStr">
+        <is>
+          <t>000711383</t>
+        </is>
+      </c>
+      <c r="P38" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q38" t="inlineStr">
+        <is>
+          <t>MATCH</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>9</v>
+      </c>
+      <c r="B39" t="n">
+        <v>38.73</v>
+      </c>
+      <c r="C39" t="n">
+        <v>2.32311</v>
+      </c>
+      <c r="D39" t="n">
+        <v>692.952</v>
+      </c>
+      <c r="E39" t="n">
+        <v>32.72176076988823</v>
+      </c>
+      <c r="F39" t="n">
+        <v>38.8318</v>
+      </c>
+      <c r="G39" t="n">
+        <v>2.3172</v>
+      </c>
+      <c r="H39" t="n">
+        <v>6</v>
+      </c>
+      <c r="I39" t="n">
+        <v>6</v>
+      </c>
+      <c r="J39" t="n">
+        <v>0.1018000000000043</v>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>5 4 4</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>Cu1.9375S</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>Djurleite</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>Cu1.9375S</t>
+        </is>
+      </c>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>000711383</t>
+        </is>
+      </c>
+      <c r="P39" t="n">
+        <v>6</v>
+      </c>
+      <c r="Q39" t="inlineStr">
+        <is>
+          <t>MATCH</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>9</v>
+      </c>
+      <c r="B40" t="n">
+        <v>38.73</v>
+      </c>
+      <c r="C40" t="n">
+        <v>2.32311</v>
+      </c>
+      <c r="D40" t="n">
+        <v>692.952</v>
+      </c>
+      <c r="E40" t="n">
+        <v>32.72176076988823</v>
+      </c>
+      <c r="F40" t="n">
+        <v>38.5213</v>
+      </c>
+      <c r="G40" t="n">
+        <v>2.3351</v>
+      </c>
+      <c r="H40" t="n">
+        <v>5</v>
+      </c>
+      <c r="I40" t="n">
+        <v>5</v>
+      </c>
+      <c r="J40" t="n">
+        <v>0.2087000000000003</v>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>11 2 0</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>Cu1.9375S</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>Djurleite</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>Cu1.9375S</t>
+        </is>
+      </c>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>000711383</t>
+        </is>
+      </c>
+      <c r="P40" t="n">
+        <v>7</v>
+      </c>
+      <c r="Q40" t="inlineStr">
+        <is>
+          <t>MATCH</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>11</v>
+      </c>
+      <c r="B41" t="n">
+        <v>44.05</v>
+      </c>
+      <c r="C41" t="n">
+        <v>2.05408</v>
+      </c>
+      <c r="D41" t="n">
+        <v>703.952</v>
+      </c>
+      <c r="E41" t="n">
+        <v>33.24118977574833</v>
+      </c>
+      <c r="F41" t="n">
+        <v>43.9154</v>
+      </c>
+      <c r="G41" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="H41" t="n">
+        <v>8</v>
+      </c>
+      <c r="I41" t="n">
+        <v>8</v>
+      </c>
+      <c r="J41" t="n">
+        <v>0.1345999999999989</v>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>1 0 20</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>Cu39S28</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>Spionkopite</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>Cu39S28</t>
+        </is>
+      </c>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>000360380</t>
+        </is>
+      </c>
+      <c r="P41" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q41" t="inlineStr">
+        <is>
+          <t>MATCH</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>13</v>
+      </c>
+      <c r="B42" t="n">
+        <v>48.224</v>
+      </c>
+      <c r="C42" t="n">
+        <v>1.88557</v>
+      </c>
+      <c r="D42" t="n">
+        <v>2117.71</v>
+      </c>
+      <c r="E42" t="n">
+        <v>100</v>
+      </c>
+      <c r="F42" t="n">
+        <v>48.2657</v>
+      </c>
+      <c r="G42" t="n">
+        <v>1.884</v>
+      </c>
+      <c r="H42" t="n">
+        <v>618</v>
+      </c>
+      <c r="I42" t="n">
+        <v>61.86186186186187</v>
+      </c>
+      <c r="J42" t="n">
+        <v>0.04170000000000584</v>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>1 1 0</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>CuS</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>Covellite</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>CuS</t>
+        </is>
+      </c>
+      <c r="O42" t="inlineStr">
+        <is>
+          <t>000752233</t>
+        </is>
+      </c>
+      <c r="P42" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q42" t="inlineStr">
+        <is>
+          <t>MATCH</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>13</v>
+      </c>
+      <c r="B43" t="n">
+        <v>48.224</v>
+      </c>
+      <c r="C43" t="n">
+        <v>1.88557</v>
+      </c>
+      <c r="D43" t="n">
+        <v>2117.71</v>
+      </c>
+      <c r="E43" t="n">
+        <v>100</v>
+      </c>
+      <c r="F43" t="n">
+        <v>48.0177</v>
+      </c>
+      <c r="G43" t="n">
+        <v>1.8931</v>
+      </c>
+      <c r="H43" t="n">
+        <v>165</v>
+      </c>
+      <c r="I43" t="n">
+        <v>16.51651651651652</v>
+      </c>
+      <c r="J43" t="n">
+        <v>0.2062999999999988</v>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>1 0 7</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>CuS</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>Covellite</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>CuS</t>
+        </is>
+      </c>
+      <c r="O43" t="inlineStr">
+        <is>
+          <t>000752233</t>
+        </is>
+      </c>
+      <c r="P43" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q43" t="inlineStr">
+        <is>
+          <t>MATCH</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>14</v>
+      </c>
+      <c r="B44" t="n">
+        <v>53.012</v>
+      </c>
+      <c r="C44" t="n">
+        <v>1.72599</v>
+      </c>
+      <c r="D44" t="n">
+        <v>1007.48</v>
+      </c>
+      <c r="E44" t="n">
+        <v>47.57403043853974</v>
+      </c>
+      <c r="F44" t="n">
+        <v>53.0112</v>
+      </c>
+      <c r="G44" t="n">
+        <v>1.726</v>
+      </c>
+      <c r="H44" t="n">
+        <v>256</v>
+      </c>
+      <c r="I44" t="n">
+        <v>25.62562562562562</v>
+      </c>
+      <c r="J44" t="n">
+        <v>0.0007999999999981355</v>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>1 0 8</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>CuS</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>Covellite</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>CuS</t>
+        </is>
+      </c>
+      <c r="O44" t="inlineStr">
+        <is>
+          <t>000752233</t>
+        </is>
+      </c>
+      <c r="P44" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q44" t="inlineStr">
+        <is>
+          <t>MATCH</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>18</v>
+      </c>
+      <c r="B45" t="n">
+        <v>59.376</v>
+      </c>
+      <c r="C45" t="n">
+        <v>1.55528</v>
+      </c>
+      <c r="D45" t="n">
+        <v>1194.52</v>
+      </c>
+      <c r="E45" t="n">
+        <v>56.40621237091008</v>
+      </c>
+      <c r="F45" t="n">
+        <v>59.0765</v>
+      </c>
+      <c r="G45" t="n">
+        <v>1.5624</v>
+      </c>
+      <c r="H45" t="n">
+        <v>104</v>
+      </c>
+      <c r="I45" t="n">
+        <v>10.41041041041041</v>
+      </c>
+      <c r="J45" t="n">
+        <v>0.2994999999999948</v>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>2 0 3</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>CuS</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>Covellite</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>CuS</t>
+        </is>
+      </c>
+      <c r="O45" t="inlineStr">
+        <is>
+          <t>000752233</t>
+        </is>
+      </c>
+      <c r="P45" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q45" t="inlineStr">
+        <is>
+          <t>MATCH</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>24</v>
+      </c>
+      <c r="B46" t="n">
+        <v>69.116</v>
+      </c>
+      <c r="C46" t="n">
+        <v>1.35797</v>
+      </c>
+      <c r="D46" t="n">
+        <v>739.095</v>
+      </c>
+      <c r="E46" t="n">
+        <v>34.90067100783394</v>
+      </c>
+      <c r="F46" t="n">
+        <v>68.9388</v>
+      </c>
+      <c r="G46" t="n">
+        <v>1.361</v>
+      </c>
+      <c r="H46" t="n">
+        <v>8</v>
+      </c>
+      <c r="I46" t="n">
+        <v>8</v>
+      </c>
+      <c r="J46" t="n">
+        <v>0.1771999999999991</v>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>2 0 7</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>Cu39S28</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>Spionkopite</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>Cu39S28</t>
+        </is>
+      </c>
+      <c r="O46" t="inlineStr">
+        <is>
+          <t>000360380</t>
+        </is>
+      </c>
+      <c r="P46" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q46" t="inlineStr">
+        <is>
+          <t>MATCH</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>25</v>
+      </c>
+      <c r="B47" t="n">
+        <v>70.03700000000001</v>
+      </c>
+      <c r="C47" t="n">
+        <v>1.34235</v>
+      </c>
+      <c r="D47" t="n">
+        <v>739.048</v>
+      </c>
+      <c r="E47" t="n">
+        <v>34.89845162935435</v>
+      </c>
+      <c r="F47" t="n">
+        <v>69.749</v>
+      </c>
+      <c r="G47" t="n">
+        <v>1.3472</v>
+      </c>
+      <c r="H47" t="n">
+        <v>60</v>
+      </c>
+      <c r="I47" t="n">
+        <v>6.006006006006006</v>
+      </c>
+      <c r="J47" t="n">
+        <v>0.2880000000000109</v>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>1 0 11</t>
+        </is>
+      </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>CuS</t>
+        </is>
+      </c>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>Covellite</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>CuS</t>
+        </is>
+      </c>
+      <c r="O47" t="inlineStr">
+        <is>
+          <t>000752233</t>
+        </is>
+      </c>
+      <c r="P47" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q47" t="inlineStr">
+        <is>
+          <t>MATCH</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>27</v>
+      </c>
+      <c r="B48" t="n">
+        <v>71.101</v>
+      </c>
+      <c r="C48" t="n">
+        <v>1.32485</v>
+      </c>
+      <c r="D48" t="n">
+        <v>711.048</v>
+      </c>
+      <c r="E48" t="n">
+        <v>33.57626870534681</v>
+      </c>
+      <c r="F48" t="n">
+        <v>71.3383</v>
+      </c>
+      <c r="G48" t="n">
+        <v>1.321</v>
+      </c>
+      <c r="H48" t="n">
+        <v>12</v>
+      </c>
+      <c r="I48" t="n">
+        <v>12</v>
+      </c>
+      <c r="J48" t="n">
+        <v>0.2373000000000047</v>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>12 0 19</t>
+        </is>
+      </c>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>Cu39S28</t>
+        </is>
+      </c>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>Spionkopite</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>Cu39S28</t>
+        </is>
+      </c>
+      <c r="O48" t="inlineStr">
+        <is>
+          <t>000360380</t>
+        </is>
+      </c>
+      <c r="P48" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q48" t="inlineStr">
+        <is>
+          <t>MATCH</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>31</v>
+      </c>
+      <c r="B49" t="n">
         <v>74.31399999999999</v>
       </c>
-      <c r="C24" t="n">
+      <c r="C49" t="n">
         <v>1.27533</v>
       </c>
-      <c r="D24" t="n">
+      <c r="D49" t="n">
         <v>765.905</v>
       </c>
-      <c r="E24" t="n">
+      <c r="E49" t="n">
         <v>36.16666115757115</v>
       </c>
-      <c r="F24" t="n">
+      <c r="F49" t="n">
         <v>74.4939</v>
       </c>
-      <c r="G24" t="n">
+      <c r="G49" t="n">
         <v>1.2727</v>
       </c>
-      <c r="H24" t="n">
+      <c r="H49" t="n">
         <v>57</v>
       </c>
-      <c r="I24" t="n">
+      <c r="I49" t="n">
         <v>5.705705705705705</v>
       </c>
-      <c r="J24" t="n">
+      <c r="J49" t="n">
         <v>0.1799000000000035</v>
       </c>
-      <c r="K24" t="inlineStr">
+      <c r="K49" t="inlineStr">
         <is>
           <t>2 0 8</t>
         </is>
       </c>
-      <c r="L24" t="inlineStr">
+      <c r="L49" t="inlineStr">
         <is>
           <t>CuS</t>
         </is>
       </c>
-      <c r="M24" t="inlineStr">
+      <c r="M49" t="inlineStr">
         <is>
           <t>Covellite</t>
         </is>
       </c>
-      <c r="N24" t="inlineStr">
+      <c r="N49" t="inlineStr">
         <is>
           <t>CuS</t>
         </is>
       </c>
-      <c r="O24" t="inlineStr">
+      <c r="O49" t="inlineStr">
         <is>
           <t>000752233</t>
         </is>
       </c>
-      <c r="P24" t="n">
+      <c r="P49" t="n">
         <v>1</v>
       </c>
-      <c r="Q24" t="inlineStr">
+      <c r="Q49" t="inlineStr">
         <is>
           <t>MATCH</t>
         </is>
@@ -22302,7 +24467,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q8"/>
+  <dimension ref="A1:Q16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -22394,58 +24559,58 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B2" t="n">
-        <v>27.905</v>
+        <v>26.186</v>
       </c>
       <c r="C2" t="n">
-        <v>3.19472</v>
+        <v>3.4004</v>
       </c>
       <c r="D2" t="n">
-        <v>758.143</v>
+        <v>498.571</v>
       </c>
       <c r="E2" t="n">
-        <v>35.80013316270878</v>
+        <v>23.54293080733434</v>
       </c>
       <c r="F2" t="n">
-        <v>27.8619</v>
+        <v>26.2118</v>
       </c>
       <c r="G2" t="n">
-        <v>3.1995</v>
+        <v>3.397</v>
       </c>
       <c r="H2" t="n">
-        <v>261</v>
+        <v>43</v>
       </c>
       <c r="I2" t="n">
-        <v>26.12612612612612</v>
+        <v>43</v>
       </c>
       <c r="J2" t="n">
-        <v>0.04310000000000258</v>
+        <v>0.02580000000000027</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>1 0 1</t>
+          <t>4 4 0</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>CuS</t>
+          <t>Cu1.9375S</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>Covellite</t>
+          <t>Djurleite</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>CuS</t>
+          <t>Cu1.9375S</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>000752233</t>
+          <t>000711383</t>
         </is>
       </c>
       <c r="P2" t="n">
@@ -22459,38 +24624,38 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="B3" t="n">
-        <v>29.501</v>
+        <v>27.905</v>
       </c>
       <c r="C3" t="n">
-        <v>3.02541</v>
+        <v>3.19472</v>
       </c>
       <c r="D3" t="n">
-        <v>1238.62</v>
+        <v>758.143</v>
       </c>
       <c r="E3" t="n">
-        <v>58.48865047622195</v>
+        <v>35.80013316270878</v>
       </c>
       <c r="F3" t="n">
-        <v>29.4683</v>
+        <v>27.8619</v>
       </c>
       <c r="G3" t="n">
-        <v>3.0286</v>
+        <v>3.1995</v>
       </c>
       <c r="H3" t="n">
-        <v>572</v>
+        <v>261</v>
       </c>
       <c r="I3" t="n">
-        <v>57.25725725725725</v>
+        <v>26.12612612612612</v>
       </c>
       <c r="J3" t="n">
-        <v>0.03270000000000195</v>
+        <v>0.04310000000000258</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>1 0 2</t>
+          <t>1 0 1</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -22524,58 +24689,58 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="B4" t="n">
-        <v>32.018</v>
+        <v>29.501</v>
       </c>
       <c r="C4" t="n">
-        <v>2.7931</v>
+        <v>3.02541</v>
       </c>
       <c r="D4" t="n">
-        <v>1335.95</v>
+        <v>1238.62</v>
       </c>
       <c r="E4" t="n">
-        <v>63.08465276170958</v>
+        <v>58.48865047622195</v>
       </c>
       <c r="F4" t="n">
-        <v>32.0508</v>
+        <v>29.4683</v>
       </c>
       <c r="G4" t="n">
-        <v>2.7902</v>
+        <v>3.0286</v>
       </c>
       <c r="H4" t="n">
-        <v>6</v>
+        <v>572</v>
       </c>
       <c r="I4" t="n">
-        <v>6</v>
+        <v>57.25725725725725</v>
       </c>
       <c r="J4" t="n">
-        <v>0.03280000000000172</v>
+        <v>0.03270000000000195</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>2 5 2</t>
+          <t>1 0 2</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>Cu1.9375S</t>
+          <t>CuS</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>Djurleite</t>
+          <t>Covellite</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>Cu1.9375S</t>
+          <t>CuS</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>000711383</t>
+          <t>000752233</t>
         </is>
       </c>
       <c r="P4" t="n">
@@ -22589,58 +24754,58 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="B5" t="n">
-        <v>48.224</v>
+        <v>32.018</v>
       </c>
       <c r="C5" t="n">
-        <v>1.88557</v>
+        <v>2.7931</v>
       </c>
       <c r="D5" t="n">
-        <v>2117.71</v>
+        <v>1335.95</v>
       </c>
       <c r="E5" t="n">
-        <v>100</v>
+        <v>63.08465276170958</v>
       </c>
       <c r="F5" t="n">
-        <v>48.2657</v>
+        <v>32.0508</v>
       </c>
       <c r="G5" t="n">
-        <v>1.884</v>
+        <v>2.7902</v>
       </c>
       <c r="H5" t="n">
-        <v>618</v>
+        <v>6</v>
       </c>
       <c r="I5" t="n">
-        <v>61.86186186186187</v>
+        <v>6</v>
       </c>
       <c r="J5" t="n">
-        <v>0.04170000000000584</v>
+        <v>0.03280000000000172</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>1 1 0</t>
+          <t>2 5 2</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>CuS</t>
+          <t>Cu1.9375S</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>Covellite</t>
+          <t>Djurleite</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>CuS</t>
+          <t>Cu1.9375S</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>000752233</t>
+          <t>000711383</t>
         </is>
       </c>
       <c r="P5" t="n">
@@ -22654,58 +24819,58 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="B6" t="n">
-        <v>53.012</v>
+        <v>32.304</v>
       </c>
       <c r="C6" t="n">
-        <v>1.72599</v>
+        <v>2.76898</v>
       </c>
       <c r="D6" t="n">
-        <v>1007.48</v>
+        <v>1318.29</v>
       </c>
       <c r="E6" t="n">
-        <v>47.57403043853974</v>
+        <v>62.25073310321054</v>
       </c>
       <c r="F6" t="n">
-        <v>53.0112</v>
+        <v>32.2076</v>
       </c>
       <c r="G6" t="n">
-        <v>1.726</v>
+        <v>2.777</v>
       </c>
       <c r="H6" t="n">
-        <v>256</v>
+        <v>30</v>
       </c>
       <c r="I6" t="n">
-        <v>25.62562562562562</v>
+        <v>30</v>
       </c>
       <c r="J6" t="n">
-        <v>0.0007999999999981355</v>
+        <v>0.09640000000000271</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>1 0 8</t>
+          <t>6 0 8</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>CuS</t>
+          <t>Cu39S28</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>Covellite</t>
+          <t>Spionkopite</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>CuS</t>
+          <t>Cu39S28</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>000752233</t>
+          <t>000360380</t>
         </is>
       </c>
       <c r="P6" t="n">
@@ -22719,58 +24884,58 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="B7" t="n">
-        <v>59.376</v>
+        <v>34.903</v>
       </c>
       <c r="C7" t="n">
-        <v>1.55528</v>
+        <v>2.56853</v>
       </c>
       <c r="D7" t="n">
-        <v>1194.52</v>
+        <v>635.429</v>
       </c>
       <c r="E7" t="n">
-        <v>56.40621237091008</v>
+        <v>30.00547761497089</v>
       </c>
       <c r="F7" t="n">
-        <v>59.0765</v>
+        <v>34.8545</v>
       </c>
       <c r="G7" t="n">
-        <v>1.5624</v>
+        <v>2.5719</v>
       </c>
       <c r="H7" t="n">
-        <v>104</v>
+        <v>16</v>
       </c>
       <c r="I7" t="n">
-        <v>10.41041041041041</v>
+        <v>16</v>
       </c>
       <c r="J7" t="n">
-        <v>0.2994999999999948</v>
+        <v>0.0484999999999971</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>2 0 3</t>
+          <t>-1 5 3</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>CuS</t>
+          <t>Cu1.9375S</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>Covellite</t>
+          <t>Djurleite</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>CuS</t>
+          <t>Cu1.9375S</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>000752233</t>
+          <t>000711383</t>
         </is>
       </c>
       <c r="P7" t="n">
@@ -22784,64 +24949,584 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="B8" t="n">
-        <v>74.31399999999999</v>
+        <v>38.73</v>
       </c>
       <c r="C8" t="n">
-        <v>1.27533</v>
+        <v>2.32311</v>
       </c>
       <c r="D8" t="n">
-        <v>765.905</v>
+        <v>692.952</v>
       </c>
       <c r="E8" t="n">
-        <v>36.16666115757115</v>
+        <v>32.72176076988823</v>
       </c>
       <c r="F8" t="n">
-        <v>74.4939</v>
+        <v>38.7261</v>
       </c>
       <c r="G8" t="n">
-        <v>1.2727</v>
+        <v>2.3233</v>
       </c>
       <c r="H8" t="n">
-        <v>57</v>
+        <v>8</v>
       </c>
       <c r="I8" t="n">
-        <v>5.705705705705705</v>
+        <v>8</v>
       </c>
       <c r="J8" t="n">
-        <v>0.1799000000000035</v>
+        <v>0.003899999999994463</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>2 0 8</t>
+          <t>-5 6 1</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>CuS</t>
+          <t>Cu1.9375S</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>Covellite</t>
+          <t>Djurleite</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>CuS</t>
+          <t>Cu1.9375S</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>000752233</t>
+          <t>000711383</t>
         </is>
       </c>
       <c r="P8" t="n">
         <v>1</v>
       </c>
       <c r="Q8" t="inlineStr">
+        <is>
+          <t>MATCH</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>11</v>
+      </c>
+      <c r="B9" t="n">
+        <v>44.05</v>
+      </c>
+      <c r="C9" t="n">
+        <v>2.05408</v>
+      </c>
+      <c r="D9" t="n">
+        <v>703.952</v>
+      </c>
+      <c r="E9" t="n">
+        <v>33.24118977574833</v>
+      </c>
+      <c r="F9" t="n">
+        <v>43.9154</v>
+      </c>
+      <c r="G9" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="H9" t="n">
+        <v>8</v>
+      </c>
+      <c r="I9" t="n">
+        <v>8</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0.1345999999999989</v>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>1 0 20</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>Cu39S28</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>Spionkopite</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>Cu39S28</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>000360380</t>
+        </is>
+      </c>
+      <c r="P9" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>MATCH</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>13</v>
+      </c>
+      <c r="B10" t="n">
+        <v>48.224</v>
+      </c>
+      <c r="C10" t="n">
+        <v>1.88557</v>
+      </c>
+      <c r="D10" t="n">
+        <v>2117.71</v>
+      </c>
+      <c r="E10" t="n">
+        <v>100</v>
+      </c>
+      <c r="F10" t="n">
+        <v>48.2657</v>
+      </c>
+      <c r="G10" t="n">
+        <v>1.884</v>
+      </c>
+      <c r="H10" t="n">
+        <v>618</v>
+      </c>
+      <c r="I10" t="n">
+        <v>61.86186186186187</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0.04170000000000584</v>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>1 1 0</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>CuS</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>Covellite</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>CuS</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>000752233</t>
+        </is>
+      </c>
+      <c r="P10" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>MATCH</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>14</v>
+      </c>
+      <c r="B11" t="n">
+        <v>53.012</v>
+      </c>
+      <c r="C11" t="n">
+        <v>1.72599</v>
+      </c>
+      <c r="D11" t="n">
+        <v>1007.48</v>
+      </c>
+      <c r="E11" t="n">
+        <v>47.57403043853974</v>
+      </c>
+      <c r="F11" t="n">
+        <v>53.0112</v>
+      </c>
+      <c r="G11" t="n">
+        <v>1.726</v>
+      </c>
+      <c r="H11" t="n">
+        <v>256</v>
+      </c>
+      <c r="I11" t="n">
+        <v>25.62562562562562</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0.0007999999999981355</v>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>1 0 8</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>CuS</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>Covellite</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>CuS</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>000752233</t>
+        </is>
+      </c>
+      <c r="P11" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t>MATCH</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>18</v>
+      </c>
+      <c r="B12" t="n">
+        <v>59.376</v>
+      </c>
+      <c r="C12" t="n">
+        <v>1.55528</v>
+      </c>
+      <c r="D12" t="n">
+        <v>1194.52</v>
+      </c>
+      <c r="E12" t="n">
+        <v>56.40621237091008</v>
+      </c>
+      <c r="F12" t="n">
+        <v>59.0765</v>
+      </c>
+      <c r="G12" t="n">
+        <v>1.5624</v>
+      </c>
+      <c r="H12" t="n">
+        <v>104</v>
+      </c>
+      <c r="I12" t="n">
+        <v>10.41041041041041</v>
+      </c>
+      <c r="J12" t="n">
+        <v>0.2994999999999948</v>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>2 0 3</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>CuS</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>Covellite</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>CuS</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>000752233</t>
+        </is>
+      </c>
+      <c r="P12" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q12" t="inlineStr">
+        <is>
+          <t>MATCH</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>24</v>
+      </c>
+      <c r="B13" t="n">
+        <v>69.116</v>
+      </c>
+      <c r="C13" t="n">
+        <v>1.35797</v>
+      </c>
+      <c r="D13" t="n">
+        <v>739.095</v>
+      </c>
+      <c r="E13" t="n">
+        <v>34.90067100783394</v>
+      </c>
+      <c r="F13" t="n">
+        <v>68.9388</v>
+      </c>
+      <c r="G13" t="n">
+        <v>1.361</v>
+      </c>
+      <c r="H13" t="n">
+        <v>8</v>
+      </c>
+      <c r="I13" t="n">
+        <v>8</v>
+      </c>
+      <c r="J13" t="n">
+        <v>0.1771999999999991</v>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>2 0 7</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>Cu39S28</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>Spionkopite</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>Cu39S28</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>000360380</t>
+        </is>
+      </c>
+      <c r="P13" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q13" t="inlineStr">
+        <is>
+          <t>MATCH</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>25</v>
+      </c>
+      <c r="B14" t="n">
+        <v>70.03700000000001</v>
+      </c>
+      <c r="C14" t="n">
+        <v>1.34235</v>
+      </c>
+      <c r="D14" t="n">
+        <v>739.048</v>
+      </c>
+      <c r="E14" t="n">
+        <v>34.89845162935435</v>
+      </c>
+      <c r="F14" t="n">
+        <v>69.749</v>
+      </c>
+      <c r="G14" t="n">
+        <v>1.3472</v>
+      </c>
+      <c r="H14" t="n">
+        <v>60</v>
+      </c>
+      <c r="I14" t="n">
+        <v>6.006006006006006</v>
+      </c>
+      <c r="J14" t="n">
+        <v>0.2880000000000109</v>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>1 0 11</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>CuS</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>Covellite</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>CuS</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>000752233</t>
+        </is>
+      </c>
+      <c r="P14" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t>MATCH</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>27</v>
+      </c>
+      <c r="B15" t="n">
+        <v>71.101</v>
+      </c>
+      <c r="C15" t="n">
+        <v>1.32485</v>
+      </c>
+      <c r="D15" t="n">
+        <v>711.048</v>
+      </c>
+      <c r="E15" t="n">
+        <v>33.57626870534681</v>
+      </c>
+      <c r="F15" t="n">
+        <v>71.3383</v>
+      </c>
+      <c r="G15" t="n">
+        <v>1.321</v>
+      </c>
+      <c r="H15" t="n">
+        <v>12</v>
+      </c>
+      <c r="I15" t="n">
+        <v>12</v>
+      </c>
+      <c r="J15" t="n">
+        <v>0.2373000000000047</v>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>12 0 19</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>Cu39S28</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>Spionkopite</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>Cu39S28</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>000360380</t>
+        </is>
+      </c>
+      <c r="P15" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t>MATCH</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>31</v>
+      </c>
+      <c r="B16" t="n">
+        <v>74.31399999999999</v>
+      </c>
+      <c r="C16" t="n">
+        <v>1.27533</v>
+      </c>
+      <c r="D16" t="n">
+        <v>765.905</v>
+      </c>
+      <c r="E16" t="n">
+        <v>36.16666115757115</v>
+      </c>
+      <c r="F16" t="n">
+        <v>74.4939</v>
+      </c>
+      <c r="G16" t="n">
+        <v>1.2727</v>
+      </c>
+      <c r="H16" t="n">
+        <v>57</v>
+      </c>
+      <c r="I16" t="n">
+        <v>5.705705705705705</v>
+      </c>
+      <c r="J16" t="n">
+        <v>0.1799000000000035</v>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>2 0 8</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>CuS</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>Covellite</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>CuS</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>000752233</t>
+        </is>
+      </c>
+      <c r="P16" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q16" t="inlineStr">
         <is>
           <t>MATCH</t>
         </is>
@@ -22858,9 +25543,784 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A1"/>
+  <dimension ref="A1:J20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Peak_ID</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Detected_2theta</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Detected_d</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Experimental_Intensity</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Experimental_Relative_Intensity</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>Nearest_Reference_2theta</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>Nearest_Phase</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>Nearest_Reference_Card</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>Nearest_Difference</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" t="n">
+        <v>19.945</v>
+      </c>
+      <c r="C2" t="n">
+        <v>4.44811</v>
+      </c>
+      <c r="D2" t="n">
+        <v>365.952</v>
+      </c>
+      <c r="E2" t="n">
+        <v>17.28055305022878</v>
+      </c>
+      <c r="F2" t="n">
+        <v>20.6644</v>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>Cu1.9375S</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>000711383</t>
+        </is>
+      </c>
+      <c r="I2" t="n">
+        <v>0.7194000000000003</v>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>NO MATCH</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" t="n">
+        <v>24.242</v>
+      </c>
+      <c r="C3" t="n">
+        <v>3.66849</v>
+      </c>
+      <c r="D3" t="n">
+        <v>461.619</v>
+      </c>
+      <c r="E3" t="n">
+        <v>21.79802711419411</v>
+      </c>
+      <c r="F3" t="n">
+        <v>24.7304</v>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Cu1.9375S</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>000711383</t>
+        </is>
+      </c>
+      <c r="I3" t="n">
+        <v>0.4883999999999986</v>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>NO MATCH</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>10</v>
+      </c>
+      <c r="B4" t="n">
+        <v>39.957</v>
+      </c>
+      <c r="C4" t="n">
+        <v>2.25451</v>
+      </c>
+      <c r="D4" t="n">
+        <v>660.952</v>
+      </c>
+      <c r="E4" t="n">
+        <v>31.21069457102247</v>
+      </c>
+      <c r="F4" t="n">
+        <v>39.2897</v>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Cu1.9375S</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>000711383</t>
+        </is>
+      </c>
+      <c r="I4" t="n">
+        <v>0.6672999999999973</v>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>NO MATCH</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>12</v>
+      </c>
+      <c r="B5" t="n">
+        <v>44.582</v>
+      </c>
+      <c r="C5" t="n">
+        <v>2.03079</v>
+      </c>
+      <c r="D5" t="n">
+        <v>704</v>
+      </c>
+      <c r="E5" t="n">
+        <v>33.24345637504663</v>
+      </c>
+      <c r="F5" t="n">
+        <v>43.9154</v>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Cu39S28</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>000360380</t>
+        </is>
+      </c>
+      <c r="I5" t="n">
+        <v>0.6666000000000025</v>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>NO MATCH</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>15</v>
+      </c>
+      <c r="B6" t="n">
+        <v>55.407</v>
+      </c>
+      <c r="C6" t="n">
+        <v>1.65694</v>
+      </c>
+      <c r="D6" t="n">
+        <v>756.476</v>
+      </c>
+      <c r="E6" t="n">
+        <v>35.72141605791161</v>
+      </c>
+      <c r="F6" t="n">
+        <v>54.4403</v>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Cu39S28</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>000360380</t>
+        </is>
+      </c>
+      <c r="I6" t="n">
+        <v>0.9666999999999959</v>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>NO MATCH</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>16</v>
+      </c>
+      <c r="B7" t="n">
+        <v>55.754</v>
+      </c>
+      <c r="C7" t="n">
+        <v>1.64742</v>
+      </c>
+      <c r="D7" t="n">
+        <v>740.2859999999999</v>
+      </c>
+      <c r="E7" t="n">
+        <v>34.95691100292296</v>
+      </c>
+      <c r="F7" t="n">
+        <v>56.7051</v>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Cu39S28</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>000360380</t>
+        </is>
+      </c>
+      <c r="I7" t="n">
+        <v>0.9511000000000038</v>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>NO MATCH</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>17</v>
+      </c>
+      <c r="B8" t="n">
+        <v>57.453</v>
+      </c>
+      <c r="C8" t="n">
+        <v>1.6027</v>
+      </c>
+      <c r="D8" t="n">
+        <v>842.619</v>
+      </c>
+      <c r="E8" t="n">
+        <v>39.78915904443951</v>
+      </c>
+      <c r="F8" t="n">
+        <v>56.7051</v>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Cu39S28</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>000360380</t>
+        </is>
+      </c>
+      <c r="I8" t="n">
+        <v>0.7479000000000013</v>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>NO MATCH</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>19</v>
+      </c>
+      <c r="B9" t="n">
+        <v>61.75</v>
+      </c>
+      <c r="C9" t="n">
+        <v>1.50107</v>
+      </c>
+      <c r="D9" t="n">
+        <v>771</v>
+      </c>
+      <c r="E9" t="n">
+        <v>36.40725122892181</v>
+      </c>
+      <c r="F9" t="n">
+        <v>63.0584</v>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Cu39S28</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>000360380</t>
+        </is>
+      </c>
+      <c r="I9" t="n">
+        <v>1.308399999999999</v>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>NO MATCH</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>20</v>
+      </c>
+      <c r="B10" t="n">
+        <v>62.118</v>
+      </c>
+      <c r="C10" t="n">
+        <v>1.49305</v>
+      </c>
+      <c r="D10" t="n">
+        <v>773.571</v>
+      </c>
+      <c r="E10" t="n">
+        <v>36.52865595383693</v>
+      </c>
+      <c r="F10" t="n">
+        <v>63.0584</v>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Cu39S28</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>000360380</t>
+        </is>
+      </c>
+      <c r="I10" t="n">
+        <v>0.9403999999999968</v>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>NO MATCH</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>21</v>
+      </c>
+      <c r="B11" t="n">
+        <v>62.446</v>
+      </c>
+      <c r="C11" t="n">
+        <v>1.48601</v>
+      </c>
+      <c r="D11" t="n">
+        <v>769.143</v>
+      </c>
+      <c r="E11" t="n">
+        <v>36.31956216856888</v>
+      </c>
+      <c r="F11" t="n">
+        <v>63.0584</v>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Cu39S28</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>000360380</t>
+        </is>
+      </c>
+      <c r="I11" t="n">
+        <v>0.6124000000000009</v>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>NO MATCH</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>22</v>
+      </c>
+      <c r="B12" t="n">
+        <v>63.489</v>
+      </c>
+      <c r="C12" t="n">
+        <v>1.46407</v>
+      </c>
+      <c r="D12" t="n">
+        <v>766.095</v>
+      </c>
+      <c r="E12" t="n">
+        <v>36.17563311312691</v>
+      </c>
+      <c r="F12" t="n">
+        <v>63.0584</v>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Cu39S28</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>000360380</t>
+        </is>
+      </c>
+      <c r="I12" t="n">
+        <v>0.4305999999999983</v>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>NO MATCH</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>23</v>
+      </c>
+      <c r="B13" t="n">
+        <v>67.13200000000001</v>
+      </c>
+      <c r="C13" t="n">
+        <v>1.39321</v>
+      </c>
+      <c r="D13" t="n">
+        <v>738.2380000000001</v>
+      </c>
+      <c r="E13" t="n">
+        <v>34.86020276619556</v>
+      </c>
+      <c r="F13" t="n">
+        <v>67.5258</v>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Cu39S28</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>000360380</t>
+        </is>
+      </c>
+      <c r="I13" t="n">
+        <v>0.3937999999999988</v>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>NO MATCH</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>26</v>
+      </c>
+      <c r="B14" t="n">
+        <v>70.85599999999999</v>
+      </c>
+      <c r="C14" t="n">
+        <v>1.32884</v>
+      </c>
+      <c r="D14" t="n">
+        <v>722.619</v>
+      </c>
+      <c r="E14" t="n">
+        <v>34.12266079869293</v>
+      </c>
+      <c r="F14" t="n">
+        <v>71.3383</v>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Cu39S28</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>000360380</t>
+        </is>
+      </c>
+      <c r="I14" t="n">
+        <v>0.4823000000000093</v>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>NO MATCH</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>28</v>
+      </c>
+      <c r="B15" t="n">
+        <v>71.69499999999999</v>
+      </c>
+      <c r="C15" t="n">
+        <v>1.31534</v>
+      </c>
+      <c r="D15" t="n">
+        <v>715.381</v>
+      </c>
+      <c r="E15" t="n">
+        <v>33.78087651283698</v>
+      </c>
+      <c r="F15" t="n">
+        <v>71.3383</v>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Cu39S28</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>000360380</t>
+        </is>
+      </c>
+      <c r="I15" t="n">
+        <v>0.3566999999999894</v>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>NO MATCH</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>29</v>
+      </c>
+      <c r="B16" t="n">
+        <v>71.98099999999999</v>
+      </c>
+      <c r="C16" t="n">
+        <v>1.31081</v>
+      </c>
+      <c r="D16" t="n">
+        <v>700.571</v>
+      </c>
+      <c r="E16" t="n">
+        <v>33.08153618767442</v>
+      </c>
+      <c r="F16" t="n">
+        <v>71.3383</v>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Cu39S28</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>000360380</t>
+        </is>
+      </c>
+      <c r="I16" t="n">
+        <v>0.6426999999999907</v>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>NO MATCH</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>30</v>
+      </c>
+      <c r="B17" t="n">
+        <v>73.004</v>
+      </c>
+      <c r="C17" t="n">
+        <v>1.29494</v>
+      </c>
+      <c r="D17" t="n">
+        <v>708.2859999999999</v>
+      </c>
+      <c r="E17" t="n">
+        <v>33.44584480405721</v>
+      </c>
+      <c r="F17" t="n">
+        <v>74.4939</v>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>CuS</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>000752233</t>
+        </is>
+      </c>
+      <c r="I17" t="n">
+        <v>1.489899999999992</v>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>NO MATCH</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>32</v>
+      </c>
+      <c r="B18" t="n">
+        <v>75.64400000000001</v>
+      </c>
+      <c r="C18" t="n">
+        <v>1.25617</v>
+      </c>
+      <c r="D18" t="n">
+        <v>693.381</v>
+      </c>
+      <c r="E18" t="n">
+        <v>32.74201850111677</v>
+      </c>
+      <c r="F18" t="n">
+        <v>76.73350000000001</v>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Cu39S28</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>000360380</t>
+        </is>
+      </c>
+      <c r="I18" t="n">
+        <v>1.089500000000001</v>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>NO MATCH</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>33</v>
+      </c>
+      <c r="B19" t="n">
+        <v>77.813</v>
+      </c>
+      <c r="C19" t="n">
+        <v>1.22649</v>
+      </c>
+      <c r="D19" t="n">
+        <v>742.8099999999999</v>
+      </c>
+      <c r="E19" t="n">
+        <v>35.0760963493585</v>
+      </c>
+      <c r="F19" t="n">
+        <v>77.37909999999999</v>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>CuCl</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>000822117</t>
+        </is>
+      </c>
+      <c r="I19" t="n">
+        <v>0.4339000000000084</v>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>NO MATCH</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>34</v>
+      </c>
+      <c r="B20" t="n">
+        <v>79</v>
+      </c>
+      <c r="C20" t="n">
+        <v>1.21102</v>
+      </c>
+      <c r="D20" t="n">
+        <v>738</v>
+      </c>
+      <c r="E20" t="n">
+        <v>34.8489642113415</v>
+      </c>
+      <c r="F20" t="n">
+        <v>79.6553</v>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>CuS</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>000752233</t>
+        </is>
+      </c>
+      <c r="I20" t="n">
+        <v>0.6552999999999969</v>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>NO MATCH</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -22953,25 +26413,25 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F2" t="n">
-        <v>0.0905285714285726</v>
+        <v>0.1152125000000024</v>
       </c>
       <c r="G2" t="n">
         <v>0.2994999999999948</v>
       </c>
       <c r="H2" t="n">
-        <v>397.5203403676613</v>
+        <v>432.4187919970157</v>
       </c>
       <c r="I2" t="n">
-        <v>100</v>
+        <v>23.52941176470588</v>
       </c>
       <c r="J2" t="n">
         <v>15</v>
       </c>
       <c r="K2" t="n">
-        <v>46.66666666666666</v>
+        <v>53.33333333333334</v>
       </c>
     </row>
     <row r="3">
@@ -22996,25 +26456,25 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="F3" t="n">
-        <v>0.06346666666666678</v>
+        <v>0.07454285714285598</v>
       </c>
       <c r="G3" t="n">
-        <v>0.09339999999999904</v>
+        <v>0.2531999999999996</v>
       </c>
       <c r="H3" t="n">
-        <v>157.3734364006403</v>
+        <v>305.8943386960443</v>
       </c>
       <c r="I3" t="n">
-        <v>42.85714285714285</v>
+        <v>20.58823529411764</v>
       </c>
       <c r="J3" t="n">
         <v>116</v>
       </c>
       <c r="K3" t="n">
-        <v>2.586206896551724</v>
+        <v>6.03448275862069</v>
       </c>
     </row>
     <row r="4">
@@ -23039,25 +26499,25 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="F4" t="n">
-        <v>0.2201000000000004</v>
+        <v>0.163685714285715</v>
       </c>
       <c r="G4" t="n">
         <v>0.2506000000000022</v>
       </c>
       <c r="H4" t="n">
-        <v>98.88478592441835</v>
+        <v>286.3965793238923</v>
       </c>
       <c r="I4" t="n">
-        <v>28.57142857142857</v>
+        <v>20.58823529411764</v>
       </c>
       <c r="J4" t="n">
         <v>31</v>
       </c>
       <c r="K4" t="n">
-        <v>6.451612903225806</v>
+        <v>22.58064516129032</v>
       </c>
     </row>
   </sheetData>

--- a/XRD_Results/CuS B2_CuS_XRD_Analysis.xlsx
+++ b/XRD_Results/CuS B2_CuS_XRD_Analysis.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F35"/>
+  <dimension ref="A1:F13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -460,19 +460,19 @@
         <v>1</v>
       </c>
       <c r="B2" t="n">
-        <v>19.945</v>
+        <v>27.925</v>
       </c>
       <c r="C2" t="n">
-        <v>4.44811</v>
+        <v>3.19243</v>
       </c>
       <c r="D2" t="n">
-        <v>365.952</v>
+        <v>741.667</v>
       </c>
       <c r="E2" t="n">
-        <v>33.78655944055953</v>
+        <v>163.5173356643353</v>
       </c>
       <c r="F2" t="n">
-        <v>17.28055305022878</v>
+        <v>35.30066634935745</v>
       </c>
     </row>
     <row r="3">
@@ -480,19 +480,19 @@
         <v>2</v>
       </c>
       <c r="B3" t="n">
-        <v>24.242</v>
+        <v>29.501</v>
       </c>
       <c r="C3" t="n">
-        <v>3.66849</v>
+        <v>3.02541</v>
       </c>
       <c r="D3" t="n">
-        <v>461.619</v>
+        <v>1238.62</v>
       </c>
       <c r="E3" t="n">
-        <v>39.38721445221461</v>
+        <v>617.8842867132848</v>
       </c>
       <c r="F3" t="n">
-        <v>21.79802711419411</v>
+        <v>58.95383150880532</v>
       </c>
     </row>
     <row r="4">
@@ -500,19 +500,19 @@
         <v>3</v>
       </c>
       <c r="B4" t="n">
-        <v>26.186</v>
+        <v>31.997</v>
       </c>
       <c r="C4" t="n">
-        <v>3.4004</v>
+        <v>2.79484</v>
       </c>
       <c r="D4" t="n">
-        <v>498.571</v>
+        <v>1324.05</v>
       </c>
       <c r="E4" t="n">
-        <v>31.97189976689981</v>
+        <v>59.76867132867119</v>
       </c>
       <c r="F4" t="n">
-        <v>23.54293080733434</v>
+        <v>63.01999048072346</v>
       </c>
     </row>
     <row r="5">
@@ -520,19 +520,19 @@
         <v>4</v>
       </c>
       <c r="B5" t="n">
-        <v>27.905</v>
+        <v>32.304</v>
       </c>
       <c r="C5" t="n">
-        <v>3.19472</v>
+        <v>2.76898</v>
       </c>
       <c r="D5" t="n">
-        <v>758.143</v>
+        <v>1318.29</v>
       </c>
       <c r="E5" t="n">
-        <v>166.9528251748255</v>
+        <v>725.0523776223754</v>
       </c>
       <c r="F5" t="n">
-        <v>35.80013316270878</v>
+        <v>62.74583531651594</v>
       </c>
     </row>
     <row r="6">
@@ -540,19 +540,19 @@
         <v>5</v>
       </c>
       <c r="B6" t="n">
-        <v>29.501</v>
+        <v>38.73</v>
       </c>
       <c r="C6" t="n">
-        <v>3.02541</v>
+        <v>2.32311</v>
       </c>
       <c r="D6" t="n">
-        <v>1238.62</v>
+        <v>692.952</v>
       </c>
       <c r="E6" t="n">
-        <v>617.4257156177173</v>
+        <v>69.96351748251709</v>
       </c>
       <c r="F6" t="n">
-        <v>58.48865047622195</v>
+        <v>32.98200856734888</v>
       </c>
     </row>
     <row r="7">
@@ -560,19 +560,19 @@
         <v>6</v>
       </c>
       <c r="B7" t="n">
-        <v>32.018</v>
+        <v>48.204</v>
       </c>
       <c r="C7" t="n">
-        <v>2.7931</v>
+        <v>1.88632</v>
       </c>
       <c r="D7" t="n">
-        <v>1335.95</v>
+        <v>2101</v>
       </c>
       <c r="E7" t="n">
-        <v>734.5982634032654</v>
+        <v>1456.272398601394</v>
       </c>
       <c r="F7" t="n">
-        <v>63.08465276170958</v>
+        <v>100</v>
       </c>
     </row>
     <row r="8">
@@ -580,19 +580,19 @@
         <v>7</v>
       </c>
       <c r="B8" t="n">
-        <v>32.304</v>
+        <v>53.012</v>
       </c>
       <c r="C8" t="n">
-        <v>2.76898</v>
+        <v>1.72599</v>
       </c>
       <c r="D8" t="n">
-        <v>1318.29</v>
+        <v>1007.48</v>
       </c>
       <c r="E8" t="n">
-        <v>69.00004662004676</v>
+        <v>289.7204265734257</v>
       </c>
       <c r="F8" t="n">
-        <v>62.25073310321054</v>
+        <v>47.95240361732508</v>
       </c>
     </row>
     <row r="9">
@@ -600,19 +600,19 @@
         <v>8</v>
       </c>
       <c r="B9" t="n">
-        <v>34.903</v>
+        <v>57.555</v>
       </c>
       <c r="C9" t="n">
-        <v>2.56853</v>
+        <v>1.60009</v>
       </c>
       <c r="D9" t="n">
-        <v>635.429</v>
+        <v>814.2380000000001</v>
       </c>
       <c r="E9" t="n">
-        <v>36.50466200466212</v>
+        <v>51.43135664335648</v>
       </c>
       <c r="F9" t="n">
-        <v>30.00547761497089</v>
+        <v>38.75478343645884</v>
       </c>
     </row>
     <row r="10">
@@ -620,19 +620,19 @@
         <v>9</v>
       </c>
       <c r="B10" t="n">
-        <v>38.73</v>
+        <v>59.397</v>
       </c>
       <c r="C10" t="n">
-        <v>2.32311</v>
+        <v>1.5548</v>
       </c>
       <c r="D10" t="n">
-        <v>692.952</v>
+        <v>1178</v>
       </c>
       <c r="E10" t="n">
-        <v>80.02541258741269</v>
+        <v>487.2732797202782</v>
       </c>
       <c r="F10" t="n">
-        <v>32.72176076988823</v>
+        <v>56.06853879105188</v>
       </c>
     </row>
     <row r="11">
@@ -640,19 +640,19 @@
         <v>10</v>
       </c>
       <c r="B11" t="n">
-        <v>39.957</v>
+        <v>67.13200000000001</v>
       </c>
       <c r="C11" t="n">
-        <v>2.25451</v>
+        <v>1.39321</v>
       </c>
       <c r="D11" t="n">
-        <v>660.952</v>
+        <v>738.2380000000001</v>
       </c>
       <c r="E11" t="n">
-        <v>35.10022377622386</v>
+        <v>55.30392307692307</v>
       </c>
       <c r="F11" t="n">
-        <v>31.21069457102247</v>
+        <v>35.13745835316517</v>
       </c>
     </row>
     <row r="12">
@@ -660,19 +660,19 @@
         <v>11</v>
       </c>
       <c r="B12" t="n">
-        <v>44.05</v>
+        <v>74.31399999999999</v>
       </c>
       <c r="C12" t="n">
-        <v>2.05408</v>
+        <v>1.27533</v>
       </c>
       <c r="D12" t="n">
-        <v>703.952</v>
+        <v>765.905</v>
       </c>
       <c r="E12" t="n">
-        <v>33.17082750582745</v>
+        <v>100.6712937062933</v>
       </c>
       <c r="F12" t="n">
-        <v>33.24118977574833</v>
+        <v>36.45430747263208</v>
       </c>
     </row>
     <row r="13">
@@ -680,459 +680,19 @@
         <v>12</v>
       </c>
       <c r="B13" t="n">
-        <v>44.582</v>
+        <v>77.834</v>
       </c>
       <c r="C13" t="n">
-        <v>2.03079</v>
+        <v>1.22622</v>
       </c>
       <c r="D13" t="n">
-        <v>704</v>
+        <v>720.8099999999999</v>
       </c>
       <c r="E13" t="n">
-        <v>48.19276923076939</v>
+        <v>55.46110389610214</v>
       </c>
       <c r="F13" t="n">
-        <v>33.24345637504663</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="n">
-        <v>13</v>
-      </c>
-      <c r="B14" t="n">
-        <v>48.224</v>
-      </c>
-      <c r="C14" t="n">
-        <v>1.88557</v>
-      </c>
-      <c r="D14" t="n">
-        <v>2117.71</v>
-      </c>
-      <c r="E14" t="n">
-        <v>1461.322503496507</v>
-      </c>
-      <c r="F14" t="n">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="n">
-        <v>14</v>
-      </c>
-      <c r="B15" t="n">
-        <v>53.012</v>
-      </c>
-      <c r="C15" t="n">
-        <v>1.72599</v>
-      </c>
-      <c r="D15" t="n">
-        <v>1007.48</v>
-      </c>
-      <c r="E15" t="n">
-        <v>293.7466153846162</v>
-      </c>
-      <c r="F15" t="n">
-        <v>47.57403043853974</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="n">
-        <v>15</v>
-      </c>
-      <c r="B16" t="n">
-        <v>55.407</v>
-      </c>
-      <c r="C16" t="n">
-        <v>1.65694</v>
-      </c>
-      <c r="D16" t="n">
-        <v>756.476</v>
-      </c>
-      <c r="E16" t="n">
-        <v>41.34393240093232</v>
-      </c>
-      <c r="F16" t="n">
-        <v>35.72141605791161</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="n">
-        <v>16</v>
-      </c>
-      <c r="B17" t="n">
-        <v>55.754</v>
-      </c>
-      <c r="C17" t="n">
-        <v>1.64742</v>
-      </c>
-      <c r="D17" t="n">
-        <v>740.2859999999999</v>
-      </c>
-      <c r="E17" t="n">
-        <v>35.75706293706298</v>
-      </c>
-      <c r="F17" t="n">
-        <v>34.95691100292296</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="n">
-        <v>17</v>
-      </c>
-      <c r="B18" t="n">
-        <v>57.453</v>
-      </c>
-      <c r="C18" t="n">
-        <v>1.6027</v>
-      </c>
-      <c r="D18" t="n">
-        <v>842.619</v>
-      </c>
-      <c r="E18" t="n">
-        <v>55.18450582750586</v>
-      </c>
-      <c r="F18" t="n">
-        <v>39.78915904443951</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="n">
-        <v>18</v>
-      </c>
-      <c r="B19" t="n">
-        <v>59.376</v>
-      </c>
-      <c r="C19" t="n">
-        <v>1.55528</v>
-      </c>
-      <c r="D19" t="n">
-        <v>1194.52</v>
-      </c>
-      <c r="E19" t="n">
-        <v>490.9883613053626</v>
-      </c>
-      <c r="F19" t="n">
-        <v>56.40621237091008</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="n">
-        <v>19</v>
-      </c>
-      <c r="B20" t="n">
-        <v>61.75</v>
-      </c>
-      <c r="C20" t="n">
-        <v>1.50107</v>
-      </c>
-      <c r="D20" t="n">
-        <v>771</v>
-      </c>
-      <c r="E20" t="n">
-        <v>42.54748484848494</v>
-      </c>
-      <c r="F20" t="n">
-        <v>36.40725122892181</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="n">
-        <v>20</v>
-      </c>
-      <c r="B21" t="n">
-        <v>62.118</v>
-      </c>
-      <c r="C21" t="n">
-        <v>1.49305</v>
-      </c>
-      <c r="D21" t="n">
-        <v>773.571</v>
-      </c>
-      <c r="E21" t="n">
-        <v>50.34564801864815</v>
-      </c>
-      <c r="F21" t="n">
-        <v>36.52865595383693</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="n">
-        <v>21</v>
-      </c>
-      <c r="B22" t="n">
-        <v>62.446</v>
-      </c>
-      <c r="C22" t="n">
-        <v>1.48601</v>
-      </c>
-      <c r="D22" t="n">
-        <v>769.143</v>
-      </c>
-      <c r="E22" t="n">
-        <v>32.00741724941736</v>
-      </c>
-      <c r="F22" t="n">
-        <v>36.31956216856888</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="n">
-        <v>22</v>
-      </c>
-      <c r="B23" t="n">
-        <v>63.489</v>
-      </c>
-      <c r="C23" t="n">
-        <v>1.46407</v>
-      </c>
-      <c r="D23" t="n">
-        <v>766.095</v>
-      </c>
-      <c r="E23" t="n">
-        <v>40.76573659673682</v>
-      </c>
-      <c r="F23" t="n">
-        <v>36.17563311312691</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="n">
-        <v>23</v>
-      </c>
-      <c r="B24" t="n">
-        <v>67.13200000000001</v>
-      </c>
-      <c r="C24" t="n">
-        <v>1.39321</v>
-      </c>
-      <c r="D24" t="n">
-        <v>738.2380000000001</v>
-      </c>
-      <c r="E24" t="n">
-        <v>61.30725641025651</v>
-      </c>
-      <c r="F24" t="n">
-        <v>34.86020276619556</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="n">
-        <v>24</v>
-      </c>
-      <c r="B25" t="n">
-        <v>69.116</v>
-      </c>
-      <c r="C25" t="n">
-        <v>1.35797</v>
-      </c>
-      <c r="D25" t="n">
-        <v>739.095</v>
-      </c>
-      <c r="E25" t="n">
-        <v>32.23910489510502</v>
-      </c>
-      <c r="F25" t="n">
-        <v>34.90067100783394</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="n">
-        <v>25</v>
-      </c>
-      <c r="B26" t="n">
-        <v>70.03700000000001</v>
-      </c>
-      <c r="C26" t="n">
-        <v>1.34235</v>
-      </c>
-      <c r="D26" t="n">
-        <v>739.048</v>
-      </c>
-      <c r="E26" t="n">
-        <v>39.71216317016319</v>
-      </c>
-      <c r="F26" t="n">
-        <v>34.89845162935435</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="n">
-        <v>26</v>
-      </c>
-      <c r="B27" t="n">
-        <v>70.85599999999999</v>
-      </c>
-      <c r="C27" t="n">
-        <v>1.32884</v>
-      </c>
-      <c r="D27" t="n">
-        <v>722.619</v>
-      </c>
-      <c r="E27" t="n">
-        <v>36.57724941724939</v>
-      </c>
-      <c r="F27" t="n">
-        <v>34.12266079869293</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="n">
-        <v>27</v>
-      </c>
-      <c r="B28" t="n">
-        <v>71.101</v>
-      </c>
-      <c r="C28" t="n">
-        <v>1.32485</v>
-      </c>
-      <c r="D28" t="n">
-        <v>711.048</v>
-      </c>
-      <c r="E28" t="n">
-        <v>36.80347086247093</v>
-      </c>
-      <c r="F28" t="n">
-        <v>33.57626870534681</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="n">
-        <v>28</v>
-      </c>
-      <c r="B29" t="n">
-        <v>71.69499999999999</v>
-      </c>
-      <c r="C29" t="n">
-        <v>1.31534</v>
-      </c>
-      <c r="D29" t="n">
-        <v>715.381</v>
-      </c>
-      <c r="E29" t="n">
-        <v>36.67449650349658</v>
-      </c>
-      <c r="F29" t="n">
-        <v>33.78087651283698</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="n">
-        <v>29</v>
-      </c>
-      <c r="B30" t="n">
-        <v>71.98099999999999</v>
-      </c>
-      <c r="C30" t="n">
-        <v>1.31081</v>
-      </c>
-      <c r="D30" t="n">
-        <v>700.571</v>
-      </c>
-      <c r="E30" t="n">
-        <v>43.91138927738939</v>
-      </c>
-      <c r="F30" t="n">
-        <v>33.08153618767442</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="n">
-        <v>30</v>
-      </c>
-      <c r="B31" t="n">
-        <v>73.004</v>
-      </c>
-      <c r="C31" t="n">
-        <v>1.29494</v>
-      </c>
-      <c r="D31" t="n">
-        <v>708.2859999999999</v>
-      </c>
-      <c r="E31" t="n">
-        <v>35.13585314685326</v>
-      </c>
-      <c r="F31" t="n">
-        <v>33.44584480405721</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="n">
-        <v>31</v>
-      </c>
-      <c r="B32" t="n">
-        <v>74.31399999999999</v>
-      </c>
-      <c r="C32" t="n">
-        <v>1.27533</v>
-      </c>
-      <c r="D32" t="n">
-        <v>765.905</v>
-      </c>
-      <c r="E32" t="n">
-        <v>105.9533706293707</v>
-      </c>
-      <c r="F32" t="n">
-        <v>36.16666115757115</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="n">
-        <v>32</v>
-      </c>
-      <c r="B33" t="n">
-        <v>75.64400000000001</v>
-      </c>
-      <c r="C33" t="n">
-        <v>1.25617</v>
-      </c>
-      <c r="D33" t="n">
-        <v>693.381</v>
-      </c>
-      <c r="E33" t="n">
-        <v>38.79579720279753</v>
-      </c>
-      <c r="F33" t="n">
-        <v>32.74201850111677</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="n">
-        <v>33</v>
-      </c>
-      <c r="B34" t="n">
-        <v>77.813</v>
-      </c>
-      <c r="C34" t="n">
-        <v>1.22649</v>
-      </c>
-      <c r="D34" t="n">
-        <v>742.8099999999999</v>
-      </c>
-      <c r="E34" t="n">
-        <v>58.98606993007002</v>
-      </c>
-      <c r="F34" t="n">
-        <v>35.0760963493585</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="n">
-        <v>34</v>
-      </c>
-      <c r="B35" t="n">
-        <v>79</v>
-      </c>
-      <c r="C35" t="n">
-        <v>1.21102</v>
-      </c>
-      <c r="D35" t="n">
-        <v>738</v>
-      </c>
-      <c r="E35" t="n">
-        <v>42.10203496503505</v>
-      </c>
-      <c r="F35" t="n">
-        <v>34.8489642113415</v>
+        <v>34.30794859590671</v>
       </c>
     </row>
   </sheetData>
@@ -21246,7 +20806,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q49"/>
+  <dimension ref="A1:R33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -21335,61 +20895,66 @@
           <t>Status</t>
         </is>
       </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>Phase_Priority</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B2" t="n">
-        <v>26.186</v>
+        <v>27.925</v>
       </c>
       <c r="C2" t="n">
-        <v>3.4004</v>
+        <v>3.19243</v>
       </c>
       <c r="D2" t="n">
-        <v>498.571</v>
+        <v>741.667</v>
       </c>
       <c r="E2" t="n">
-        <v>23.54293080733434</v>
+        <v>35.30066634935745</v>
       </c>
       <c r="F2" t="n">
-        <v>26.2118</v>
+        <v>27.8619</v>
       </c>
       <c r="G2" t="n">
-        <v>3.397</v>
+        <v>3.1995</v>
       </c>
       <c r="H2" t="n">
-        <v>43</v>
+        <v>261</v>
       </c>
       <c r="I2" t="n">
-        <v>43</v>
+        <v>26.12612612612612</v>
       </c>
       <c r="J2" t="n">
-        <v>0.02580000000000027</v>
+        <v>0.06310000000000215</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>4 4 0</t>
+          <t>1 0 1</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>Cu1.9375S</t>
+          <t>CuS</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>Djurleite</t>
+          <t>Covellite</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>Cu1.9375S</t>
+          <t>CuS</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>000711383</t>
+          <t>000752233</t>
         </is>
       </c>
       <c r="P2" t="n">
@@ -21400,41 +20965,44 @@
           <t>MATCH</t>
         </is>
       </c>
+      <c r="R2" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>26.186</v>
+        <v>27.925</v>
       </c>
       <c r="C3" t="n">
-        <v>3.4004</v>
+        <v>3.19243</v>
       </c>
       <c r="D3" t="n">
-        <v>498.571</v>
+        <v>741.667</v>
       </c>
       <c r="E3" t="n">
-        <v>23.54293080733434</v>
+        <v>35.30066634935745</v>
       </c>
       <c r="F3" t="n">
-        <v>26.2118</v>
+        <v>27.8408</v>
       </c>
       <c r="G3" t="n">
-        <v>3.397</v>
+        <v>3.2018</v>
       </c>
       <c r="H3" t="n">
-        <v>43</v>
+        <v>21</v>
       </c>
       <c r="I3" t="n">
-        <v>43</v>
+        <v>21</v>
       </c>
       <c r="J3" t="n">
-        <v>0.02580000000000027</v>
+        <v>0.08419999999999916</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>-4 2 3</t>
+          <t>-3 3 3</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -21465,61 +21033,64 @@
           <t>MATCH</t>
         </is>
       </c>
+      <c r="R3" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B4" t="n">
-        <v>26.186</v>
+        <v>27.925</v>
       </c>
       <c r="C4" t="n">
-        <v>3.4004</v>
+        <v>3.19243</v>
       </c>
       <c r="D4" t="n">
-        <v>498.571</v>
+        <v>741.667</v>
       </c>
       <c r="E4" t="n">
-        <v>23.54293080733434</v>
+        <v>35.30066634935745</v>
       </c>
       <c r="F4" t="n">
-        <v>26.1259</v>
+        <v>27.8408</v>
       </c>
       <c r="G4" t="n">
-        <v>3.408</v>
+        <v>3.2018</v>
       </c>
       <c r="H4" t="n">
-        <v>8</v>
+        <v>21</v>
       </c>
       <c r="I4" t="n">
-        <v>8</v>
+        <v>21</v>
       </c>
       <c r="J4" t="n">
-        <v>0.06009999999999849</v>
+        <v>0.08419999999999916</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>1 0 12</t>
+          <t>3 3 3</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>Cu39S28</t>
+          <t>Cu1.9375S</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>Spionkopite</t>
+          <t>Djurleite</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>Cu39S28</t>
+          <t>Cu1.9375S</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>000360380</t>
+          <t>000711383</t>
         </is>
       </c>
       <c r="P4" t="n">
@@ -21530,270 +21101,285 @@
           <t>MATCH</t>
         </is>
       </c>
+      <c r="R4" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
+        <v>1</v>
+      </c>
+      <c r="B5" t="n">
+        <v>27.925</v>
+      </c>
+      <c r="C5" t="n">
+        <v>3.19243</v>
+      </c>
+      <c r="D5" t="n">
+        <v>741.667</v>
+      </c>
+      <c r="E5" t="n">
+        <v>35.30066634935745</v>
+      </c>
+      <c r="F5" t="n">
+        <v>27.6544</v>
+      </c>
+      <c r="G5" t="n">
+        <v>3.223</v>
+      </c>
+      <c r="H5" t="n">
+        <v>5</v>
+      </c>
+      <c r="I5" t="n">
+        <v>5</v>
+      </c>
+      <c r="J5" t="n">
+        <v>0.2706000000000017</v>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>6 0 3</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>Cu39S28</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>Spionkopite</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>Cu39S28</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>000360380</t>
+        </is>
+      </c>
+      <c r="P5" t="n">
         <v>4</v>
       </c>
-      <c r="B5" t="n">
-        <v>27.905</v>
-      </c>
-      <c r="C5" t="n">
-        <v>3.19472</v>
-      </c>
-      <c r="D5" t="n">
-        <v>758.143</v>
-      </c>
-      <c r="E5" t="n">
-        <v>35.80013316270878</v>
-      </c>
-      <c r="F5" t="n">
-        <v>27.8619</v>
-      </c>
-      <c r="G5" t="n">
-        <v>3.1995</v>
-      </c>
-      <c r="H5" t="n">
-        <v>261</v>
-      </c>
-      <c r="I5" t="n">
-        <v>26.12612612612612</v>
-      </c>
-      <c r="J5" t="n">
-        <v>0.04310000000000258</v>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>1 0 1</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>CuS</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>Covellite</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>CuS</t>
-        </is>
-      </c>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t>000752233</t>
-        </is>
-      </c>
-      <c r="P5" t="n">
-        <v>1</v>
-      </c>
       <c r="Q5" t="inlineStr">
         <is>
           <t>MATCH</t>
         </is>
+      </c>
+      <c r="R5" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="B6" t="n">
-        <v>27.905</v>
+        <v>29.501</v>
       </c>
       <c r="C6" t="n">
-        <v>3.19472</v>
+        <v>3.02541</v>
       </c>
       <c r="D6" t="n">
-        <v>758.143</v>
+        <v>1238.62</v>
       </c>
       <c r="E6" t="n">
-        <v>35.80013316270878</v>
+        <v>58.95383150880532</v>
       </c>
       <c r="F6" t="n">
-        <v>27.8408</v>
+        <v>29.4683</v>
       </c>
       <c r="G6" t="n">
-        <v>3.2018</v>
+        <v>3.0286</v>
       </c>
       <c r="H6" t="n">
-        <v>21</v>
+        <v>572</v>
       </c>
       <c r="I6" t="n">
-        <v>21</v>
+        <v>57.25725725725725</v>
       </c>
       <c r="J6" t="n">
-        <v>0.06419999999999959</v>
+        <v>0.03270000000000195</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>-3 3 3</t>
+          <t>1 0 2</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>Cu1.9375S</t>
+          <t>CuS</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>Djurleite</t>
+          <t>Covellite</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>Cu1.9375S</t>
+          <t>CuS</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>000711383</t>
+          <t>000752233</t>
         </is>
       </c>
       <c r="P6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
           <t>MATCH</t>
         </is>
+      </c>
+      <c r="R6" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
+        <v>2</v>
+      </c>
+      <c r="B7" t="n">
+        <v>29.501</v>
+      </c>
+      <c r="C7" t="n">
+        <v>3.02541</v>
+      </c>
+      <c r="D7" t="n">
+        <v>1238.62</v>
+      </c>
+      <c r="E7" t="n">
+        <v>58.95383150880532</v>
+      </c>
+      <c r="F7" t="n">
+        <v>29.5944</v>
+      </c>
+      <c r="G7" t="n">
+        <v>3.016</v>
+      </c>
+      <c r="H7" t="n">
+        <v>23</v>
+      </c>
+      <c r="I7" t="n">
+        <v>23</v>
+      </c>
+      <c r="J7" t="n">
+        <v>0.09339999999999904</v>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>-8 2 1</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>Cu1.9375S</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>Djurleite</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>Cu1.9375S</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>000711383</t>
+        </is>
+      </c>
+      <c r="P7" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>MATCH</t>
+        </is>
+      </c>
+      <c r="R7" t="n">
         <v>4</v>
-      </c>
-      <c r="B7" t="n">
-        <v>27.905</v>
-      </c>
-      <c r="C7" t="n">
-        <v>3.19472</v>
-      </c>
-      <c r="D7" t="n">
-        <v>758.143</v>
-      </c>
-      <c r="E7" t="n">
-        <v>35.80013316270878</v>
-      </c>
-      <c r="F7" t="n">
-        <v>27.8408</v>
-      </c>
-      <c r="G7" t="n">
-        <v>3.2018</v>
-      </c>
-      <c r="H7" t="n">
-        <v>21</v>
-      </c>
-      <c r="I7" t="n">
-        <v>21</v>
-      </c>
-      <c r="J7" t="n">
-        <v>0.06419999999999959</v>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>3 3 3</t>
-        </is>
-      </c>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>Cu1.9375S</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>Djurleite</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>Cu1.9375S</t>
-        </is>
-      </c>
-      <c r="O7" t="inlineStr">
-        <is>
-          <t>000711383</t>
-        </is>
-      </c>
-      <c r="P7" t="n">
-        <v>3</v>
-      </c>
-      <c r="Q7" t="inlineStr">
-        <is>
-          <t>MATCH</t>
-        </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
+        <v>2</v>
+      </c>
+      <c r="B8" t="n">
+        <v>29.501</v>
+      </c>
+      <c r="C8" t="n">
+        <v>3.02541</v>
+      </c>
+      <c r="D8" t="n">
+        <v>1238.62</v>
+      </c>
+      <c r="E8" t="n">
+        <v>58.95383150880532</v>
+      </c>
+      <c r="F8" t="n">
+        <v>29.5944</v>
+      </c>
+      <c r="G8" t="n">
+        <v>3.016</v>
+      </c>
+      <c r="H8" t="n">
+        <v>23</v>
+      </c>
+      <c r="I8" t="n">
+        <v>23</v>
+      </c>
+      <c r="J8" t="n">
+        <v>0.09339999999999904</v>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>-8 0 2</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>Cu1.9375S</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>Djurleite</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>Cu1.9375S</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>000711383</t>
+        </is>
+      </c>
+      <c r="P8" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>MATCH</t>
+        </is>
+      </c>
+      <c r="R8" t="n">
         <v>4</v>
-      </c>
-      <c r="B8" t="n">
-        <v>27.905</v>
-      </c>
-      <c r="C8" t="n">
-        <v>3.19472</v>
-      </c>
-      <c r="D8" t="n">
-        <v>758.143</v>
-      </c>
-      <c r="E8" t="n">
-        <v>35.80013316270878</v>
-      </c>
-      <c r="F8" t="n">
-        <v>27.6544</v>
-      </c>
-      <c r="G8" t="n">
-        <v>3.223</v>
-      </c>
-      <c r="H8" t="n">
-        <v>5</v>
-      </c>
-      <c r="I8" t="n">
-        <v>5</v>
-      </c>
-      <c r="J8" t="n">
-        <v>0.2506000000000022</v>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>6 0 3</t>
-        </is>
-      </c>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>Cu39S28</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>Spionkopite</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>Cu39S28</t>
-        </is>
-      </c>
-      <c r="O8" t="inlineStr">
-        <is>
-          <t>000360380</t>
-        </is>
-      </c>
-      <c r="P8" t="n">
-        <v>4</v>
-      </c>
-      <c r="Q8" t="inlineStr">
-        <is>
-          <t>MATCH</t>
-        </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="B9" t="n">
         <v>29.501</v>
@@ -21805,60 +21391,63 @@
         <v>1238.62</v>
       </c>
       <c r="E9" t="n">
-        <v>58.48865047622195</v>
+        <v>58.95383150880532</v>
       </c>
       <c r="F9" t="n">
-        <v>29.4683</v>
+        <v>29.3679</v>
       </c>
       <c r="G9" t="n">
-        <v>3.0286</v>
+        <v>3.0387</v>
       </c>
       <c r="H9" t="n">
-        <v>572</v>
+        <v>16</v>
       </c>
       <c r="I9" t="n">
-        <v>57.25725725725725</v>
+        <v>16</v>
       </c>
       <c r="J9" t="n">
-        <v>0.03270000000000195</v>
+        <v>0.1331000000000024</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>1 0 2</t>
+          <t>-4 4 2</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>CuS</t>
+          <t>Cu1.9375S</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>Covellite</t>
+          <t>Djurleite</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>CuS</t>
+          <t>Cu1.9375S</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>000752233</t>
+          <t>000711383</t>
         </is>
       </c>
       <c r="P9" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
           <t>MATCH</t>
         </is>
+      </c>
+      <c r="R9" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="B10" t="n">
         <v>29.501</v>
@@ -21870,26 +21459,26 @@
         <v>1238.62</v>
       </c>
       <c r="E10" t="n">
-        <v>58.48865047622195</v>
+        <v>58.95383150880532</v>
       </c>
       <c r="F10" t="n">
-        <v>29.5944</v>
+        <v>29.3679</v>
       </c>
       <c r="G10" t="n">
-        <v>3.016</v>
+        <v>3.0387</v>
       </c>
       <c r="H10" t="n">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="I10" t="n">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="J10" t="n">
-        <v>0.09339999999999904</v>
+        <v>0.1331000000000024</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>-8 2 1</t>
+          <t>4 4 2</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
@@ -21913,17 +21502,20 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
           <t>MATCH</t>
         </is>
+      </c>
+      <c r="R10" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="B11" t="n">
         <v>29.501</v>
@@ -21935,26 +21527,26 @@
         <v>1238.62</v>
       </c>
       <c r="E11" t="n">
-        <v>58.48865047622195</v>
+        <v>58.95383150880532</v>
       </c>
       <c r="F11" t="n">
-        <v>29.5944</v>
+        <v>29.6586</v>
       </c>
       <c r="G11" t="n">
-        <v>3.016</v>
+        <v>3.0096</v>
       </c>
       <c r="H11" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="I11" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="J11" t="n">
-        <v>0.09339999999999904</v>
+        <v>0.1575999999999986</v>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>-8 0 2</t>
+          <t>8 0 2</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
@@ -21978,17 +21570,20 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
           <t>MATCH</t>
         </is>
+      </c>
+      <c r="R11" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="B12" t="n">
         <v>29.501</v>
@@ -22000,26 +21595,26 @@
         <v>1238.62</v>
       </c>
       <c r="E12" t="n">
-        <v>58.48865047622195</v>
+        <v>58.95383150880532</v>
       </c>
       <c r="F12" t="n">
-        <v>29.3679</v>
+        <v>29.2781</v>
       </c>
       <c r="G12" t="n">
-        <v>3.0387</v>
+        <v>3.0478</v>
       </c>
       <c r="H12" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I12" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J12" t="n">
-        <v>0.1331000000000024</v>
+        <v>0.2229000000000028</v>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>-4 4 2</t>
+          <t>4 3 3</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
@@ -22043,17 +21638,20 @@
         </is>
       </c>
       <c r="P12" t="n">
+        <v>7</v>
+      </c>
+      <c r="Q12" t="inlineStr">
+        <is>
+          <t>MATCH</t>
+        </is>
+      </c>
+      <c r="R12" t="n">
         <v>4</v>
-      </c>
-      <c r="Q12" t="inlineStr">
-        <is>
-          <t>MATCH</t>
-        </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="B13" t="n">
         <v>29.501</v>
@@ -22065,26 +21663,26 @@
         <v>1238.62</v>
       </c>
       <c r="E13" t="n">
-        <v>58.48865047622195</v>
+        <v>58.95383150880532</v>
       </c>
       <c r="F13" t="n">
-        <v>29.3679</v>
+        <v>29.2781</v>
       </c>
       <c r="G13" t="n">
-        <v>3.0387</v>
+        <v>3.0478</v>
       </c>
       <c r="H13" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I13" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J13" t="n">
-        <v>0.1331000000000024</v>
+        <v>0.2229000000000028</v>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>4 4 2</t>
+          <t>-1 5 1</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
@@ -22108,113 +21706,119 @@
         </is>
       </c>
       <c r="P13" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
           <t>MATCH</t>
         </is>
+      </c>
+      <c r="R13" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="B14" t="n">
-        <v>29.501</v>
+        <v>31.997</v>
       </c>
       <c r="C14" t="n">
-        <v>3.02541</v>
+        <v>2.79484</v>
       </c>
       <c r="D14" t="n">
-        <v>1238.62</v>
+        <v>1324.05</v>
       </c>
       <c r="E14" t="n">
-        <v>58.48865047622195</v>
+        <v>63.01999048072346</v>
       </c>
       <c r="F14" t="n">
-        <v>29.6586</v>
+        <v>31.982</v>
       </c>
       <c r="G14" t="n">
-        <v>3.0096</v>
+        <v>2.7961</v>
       </c>
       <c r="H14" t="n">
-        <v>21</v>
+        <v>999</v>
       </c>
       <c r="I14" t="n">
-        <v>21</v>
+        <v>100</v>
       </c>
       <c r="J14" t="n">
-        <v>0.1575999999999986</v>
+        <v>0.01500000000000057</v>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>8 0 2</t>
+          <t>1 0 3</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>Cu1.9375S</t>
+          <t>CuS</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>Djurleite</t>
+          <t>Covellite</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>Cu1.9375S</t>
+          <t>CuS</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>000711383</t>
+          <t>000752233</t>
         </is>
       </c>
       <c r="P14" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
           <t>MATCH</t>
         </is>
+      </c>
+      <c r="R14" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="B15" t="n">
-        <v>29.501</v>
+        <v>31.997</v>
       </c>
       <c r="C15" t="n">
-        <v>3.02541</v>
+        <v>2.79484</v>
       </c>
       <c r="D15" t="n">
-        <v>1238.62</v>
+        <v>1324.05</v>
       </c>
       <c r="E15" t="n">
-        <v>58.48865047622195</v>
+        <v>63.01999048072346</v>
       </c>
       <c r="F15" t="n">
-        <v>29.2781</v>
+        <v>32.0508</v>
       </c>
       <c r="G15" t="n">
-        <v>3.0478</v>
+        <v>2.7902</v>
       </c>
       <c r="H15" t="n">
-        <v>17</v>
+        <v>6</v>
       </c>
       <c r="I15" t="n">
-        <v>17</v>
+        <v>6</v>
       </c>
       <c r="J15" t="n">
-        <v>0.2229000000000028</v>
+        <v>0.05380000000000251</v>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>4 3 3</t>
+          <t>2 5 2</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
@@ -22238,48 +21842,51 @@
         </is>
       </c>
       <c r="P15" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
           <t>MATCH</t>
         </is>
+      </c>
+      <c r="R15" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="B16" t="n">
-        <v>29.501</v>
+        <v>31.997</v>
       </c>
       <c r="C16" t="n">
-        <v>3.02541</v>
+        <v>2.79484</v>
       </c>
       <c r="D16" t="n">
-        <v>1238.62</v>
+        <v>1324.05</v>
       </c>
       <c r="E16" t="n">
-        <v>58.48865047622195</v>
+        <v>63.01999048072346</v>
       </c>
       <c r="F16" t="n">
-        <v>29.2781</v>
+        <v>32.0508</v>
       </c>
       <c r="G16" t="n">
-        <v>3.0478</v>
+        <v>2.7902</v>
       </c>
       <c r="H16" t="n">
-        <v>17</v>
+        <v>6</v>
       </c>
       <c r="I16" t="n">
-        <v>17</v>
+        <v>6</v>
       </c>
       <c r="J16" t="n">
-        <v>0.2229000000000028</v>
+        <v>0.05380000000000251</v>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>-1 5 1</t>
+          <t>4 5 1</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
@@ -22303,113 +21910,119 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
           <t>MATCH</t>
         </is>
+      </c>
+      <c r="R16" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="B17" t="n">
-        <v>32.018</v>
+        <v>31.997</v>
       </c>
       <c r="C17" t="n">
-        <v>2.7931</v>
+        <v>2.79484</v>
       </c>
       <c r="D17" t="n">
-        <v>1335.95</v>
+        <v>1324.05</v>
       </c>
       <c r="E17" t="n">
-        <v>63.08465276170958</v>
+        <v>63.01999048072346</v>
       </c>
       <c r="F17" t="n">
-        <v>32.0508</v>
+        <v>32.2076</v>
       </c>
       <c r="G17" t="n">
-        <v>2.7902</v>
+        <v>2.777</v>
       </c>
       <c r="H17" t="n">
-        <v>6</v>
+        <v>30</v>
       </c>
       <c r="I17" t="n">
-        <v>6</v>
+        <v>30</v>
       </c>
       <c r="J17" t="n">
-        <v>0.03280000000000172</v>
+        <v>0.2105999999999995</v>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>2 5 2</t>
+          <t>6 0 8</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>Cu1.9375S</t>
+          <t>Cu39S28</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>Djurleite</t>
+          <t>Spionkopite</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>Cu1.9375S</t>
+          <t>Cu39S28</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>000711383</t>
+          <t>000360380</t>
         </is>
       </c>
       <c r="P17" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
           <t>MATCH</t>
         </is>
+      </c>
+      <c r="R17" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="B18" t="n">
-        <v>32.018</v>
+        <v>31.997</v>
       </c>
       <c r="C18" t="n">
-        <v>2.7931</v>
+        <v>2.79484</v>
       </c>
       <c r="D18" t="n">
-        <v>1335.95</v>
+        <v>1324.05</v>
       </c>
       <c r="E18" t="n">
-        <v>63.08465276170958</v>
+        <v>63.01999048072346</v>
       </c>
       <c r="F18" t="n">
-        <v>32.0508</v>
+        <v>31.7366</v>
       </c>
       <c r="G18" t="n">
-        <v>2.7902</v>
+        <v>2.8171</v>
       </c>
       <c r="H18" t="n">
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="I18" t="n">
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="J18" t="n">
-        <v>0.03280000000000172</v>
+        <v>0.2604000000000006</v>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>4 5 1</t>
+          <t>-3 4 3</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
@@ -22433,94 +22046,100 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
           <t>MATCH</t>
         </is>
+      </c>
+      <c r="R18" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
+        <v>3</v>
+      </c>
+      <c r="B19" t="n">
+        <v>31.997</v>
+      </c>
+      <c r="C19" t="n">
+        <v>2.79484</v>
+      </c>
+      <c r="D19" t="n">
+        <v>1324.05</v>
+      </c>
+      <c r="E19" t="n">
+        <v>63.01999048072346</v>
+      </c>
+      <c r="F19" t="n">
+        <v>31.7366</v>
+      </c>
+      <c r="G19" t="n">
+        <v>2.8171</v>
+      </c>
+      <c r="H19" t="n">
+        <v>17</v>
+      </c>
+      <c r="I19" t="n">
+        <v>17</v>
+      </c>
+      <c r="J19" t="n">
+        <v>0.2604000000000006</v>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>3 4 3</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>Cu1.9375S</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>Djurleite</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>Cu1.9375S</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>000711383</t>
+        </is>
+      </c>
+      <c r="P19" t="n">
         <v>6</v>
       </c>
-      <c r="B19" t="n">
-        <v>32.018</v>
-      </c>
-      <c r="C19" t="n">
-        <v>2.7931</v>
-      </c>
-      <c r="D19" t="n">
-        <v>1335.95</v>
-      </c>
-      <c r="E19" t="n">
-        <v>63.08465276170958</v>
-      </c>
-      <c r="F19" t="n">
-        <v>31.982</v>
-      </c>
-      <c r="G19" t="n">
-        <v>2.7961</v>
-      </c>
-      <c r="H19" t="n">
-        <v>999</v>
-      </c>
-      <c r="I19" t="n">
-        <v>100</v>
-      </c>
-      <c r="J19" t="n">
-        <v>0.03600000000000136</v>
-      </c>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>1 0 3</t>
-        </is>
-      </c>
-      <c r="L19" t="inlineStr">
-        <is>
-          <t>CuS</t>
-        </is>
-      </c>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>Covellite</t>
-        </is>
-      </c>
-      <c r="N19" t="inlineStr">
-        <is>
-          <t>CuS</t>
-        </is>
-      </c>
-      <c r="O19" t="inlineStr">
-        <is>
-          <t>000752233</t>
-        </is>
-      </c>
-      <c r="P19" t="n">
-        <v>3</v>
-      </c>
       <c r="Q19" t="inlineStr">
         <is>
           <t>MATCH</t>
         </is>
+      </c>
+      <c r="R19" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="B20" t="n">
-        <v>32.018</v>
+        <v>32.304</v>
       </c>
       <c r="C20" t="n">
-        <v>2.7931</v>
+        <v>2.76898</v>
       </c>
       <c r="D20" t="n">
-        <v>1335.95</v>
+        <v>1318.29</v>
       </c>
       <c r="E20" t="n">
-        <v>63.08465276170958</v>
+        <v>62.74583531651594</v>
       </c>
       <c r="F20" t="n">
         <v>32.2076</v>
@@ -22535,7 +22154,7 @@
         <v>30</v>
       </c>
       <c r="J20" t="n">
-        <v>0.1895999999999987</v>
+        <v>0.09640000000000271</v>
       </c>
       <c r="K20" t="inlineStr">
         <is>
@@ -22563,48 +22182,51 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
           <t>MATCH</t>
         </is>
+      </c>
+      <c r="R20" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
+        <v>4</v>
+      </c>
+      <c r="B21" t="n">
+        <v>32.304</v>
+      </c>
+      <c r="C21" t="n">
+        <v>2.76898</v>
+      </c>
+      <c r="D21" t="n">
+        <v>1318.29</v>
+      </c>
+      <c r="E21" t="n">
+        <v>62.74583531651594</v>
+      </c>
+      <c r="F21" t="n">
+        <v>32.0508</v>
+      </c>
+      <c r="G21" t="n">
+        <v>2.7902</v>
+      </c>
+      <c r="H21" t="n">
         <v>6</v>
       </c>
-      <c r="B21" t="n">
-        <v>32.018</v>
-      </c>
-      <c r="C21" t="n">
-        <v>2.7931</v>
-      </c>
-      <c r="D21" t="n">
-        <v>1335.95</v>
-      </c>
-      <c r="E21" t="n">
-        <v>63.08465276170958</v>
-      </c>
-      <c r="F21" t="n">
-        <v>31.7366</v>
-      </c>
-      <c r="G21" t="n">
-        <v>2.8171</v>
-      </c>
-      <c r="H21" t="n">
-        <v>17</v>
-      </c>
       <c r="I21" t="n">
-        <v>17</v>
+        <v>6</v>
       </c>
       <c r="J21" t="n">
-        <v>0.2814000000000014</v>
+        <v>0.2531999999999996</v>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>-3 4 3</t>
+          <t>2 5 2</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
@@ -22628,48 +22250,51 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
           <t>MATCH</t>
         </is>
+      </c>
+      <c r="R21" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
+        <v>4</v>
+      </c>
+      <c r="B22" t="n">
+        <v>32.304</v>
+      </c>
+      <c r="C22" t="n">
+        <v>2.76898</v>
+      </c>
+      <c r="D22" t="n">
+        <v>1318.29</v>
+      </c>
+      <c r="E22" t="n">
+        <v>62.74583531651594</v>
+      </c>
+      <c r="F22" t="n">
+        <v>32.0508</v>
+      </c>
+      <c r="G22" t="n">
+        <v>2.7902</v>
+      </c>
+      <c r="H22" t="n">
         <v>6</v>
       </c>
-      <c r="B22" t="n">
-        <v>32.018</v>
-      </c>
-      <c r="C22" t="n">
-        <v>2.7931</v>
-      </c>
-      <c r="D22" t="n">
-        <v>1335.95</v>
-      </c>
-      <c r="E22" t="n">
-        <v>63.08465276170958</v>
-      </c>
-      <c r="F22" t="n">
-        <v>31.7366</v>
-      </c>
-      <c r="G22" t="n">
-        <v>2.8171</v>
-      </c>
-      <c r="H22" t="n">
-        <v>17</v>
-      </c>
       <c r="I22" t="n">
-        <v>17</v>
+        <v>6</v>
       </c>
       <c r="J22" t="n">
-        <v>0.2814000000000014</v>
+        <v>0.2531999999999996</v>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>3 4 3</t>
+          <t>4 5 1</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
@@ -22693,68 +22318,71 @@
         </is>
       </c>
       <c r="P22" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
           <t>MATCH</t>
         </is>
+      </c>
+      <c r="R22" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="B23" t="n">
-        <v>32.304</v>
+        <v>38.73</v>
       </c>
       <c r="C23" t="n">
-        <v>2.76898</v>
+        <v>2.32311</v>
       </c>
       <c r="D23" t="n">
-        <v>1318.29</v>
+        <v>692.952</v>
       </c>
       <c r="E23" t="n">
-        <v>62.25073310321054</v>
+        <v>32.98200856734888</v>
       </c>
       <c r="F23" t="n">
-        <v>32.2076</v>
+        <v>38.7261</v>
       </c>
       <c r="G23" t="n">
-        <v>2.777</v>
+        <v>2.3233</v>
       </c>
       <c r="H23" t="n">
-        <v>30</v>
+        <v>8</v>
       </c>
       <c r="I23" t="n">
-        <v>30</v>
+        <v>8</v>
       </c>
       <c r="J23" t="n">
-        <v>0.09640000000000271</v>
+        <v>0.003899999999994463</v>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>6 0 8</t>
+          <t>-5 6 1</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>Cu39S28</t>
+          <t>Cu1.9375S</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>Spionkopite</t>
+          <t>Djurleite</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>Cu39S28</t>
+          <t>Cu1.9375S</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>000360380</t>
+          <t>000711383</t>
         </is>
       </c>
       <c r="P23" t="n">
@@ -22765,41 +22393,44 @@
           <t>MATCH</t>
         </is>
       </c>
+      <c r="R23" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="B24" t="n">
-        <v>32.304</v>
+        <v>38.73</v>
       </c>
       <c r="C24" t="n">
-        <v>2.76898</v>
+        <v>2.32311</v>
       </c>
       <c r="D24" t="n">
-        <v>1318.29</v>
+        <v>692.952</v>
       </c>
       <c r="E24" t="n">
-        <v>62.25073310321054</v>
+        <v>32.98200856734888</v>
       </c>
       <c r="F24" t="n">
-        <v>32.0508</v>
+        <v>38.7261</v>
       </c>
       <c r="G24" t="n">
-        <v>2.7902</v>
+        <v>2.3233</v>
       </c>
       <c r="H24" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="I24" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="J24" t="n">
-        <v>0.2531999999999996</v>
+        <v>0.003899999999994463</v>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>2 5 2</t>
+          <t>5 6 1</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
@@ -22830,28 +22461,31 @@
           <t>MATCH</t>
         </is>
       </c>
+      <c r="R24" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="B25" t="n">
-        <v>32.304</v>
+        <v>38.73</v>
       </c>
       <c r="C25" t="n">
-        <v>2.76898</v>
+        <v>2.32311</v>
       </c>
       <c r="D25" t="n">
-        <v>1318.29</v>
+        <v>692.952</v>
       </c>
       <c r="E25" t="n">
-        <v>62.25073310321054</v>
+        <v>32.98200856734888</v>
       </c>
       <c r="F25" t="n">
-        <v>32.0508</v>
+        <v>38.642</v>
       </c>
       <c r="G25" t="n">
-        <v>2.7902</v>
+        <v>2.3281</v>
       </c>
       <c r="H25" t="n">
         <v>6</v>
@@ -22860,11 +22494,11 @@
         <v>6</v>
       </c>
       <c r="J25" t="n">
-        <v>0.2531999999999996</v>
+        <v>0.08799999999999386</v>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>4 5 1</t>
+          <t>-3 3 5</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
@@ -22895,41 +22529,44 @@
           <t>MATCH</t>
         </is>
       </c>
+      <c r="R25" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="B26" t="n">
-        <v>34.903</v>
+        <v>38.73</v>
       </c>
       <c r="C26" t="n">
-        <v>2.56853</v>
+        <v>2.32311</v>
       </c>
       <c r="D26" t="n">
-        <v>635.429</v>
+        <v>692.952</v>
       </c>
       <c r="E26" t="n">
-        <v>30.00547761497089</v>
+        <v>32.98200856734888</v>
       </c>
       <c r="F26" t="n">
-        <v>34.8545</v>
+        <v>38.642</v>
       </c>
       <c r="G26" t="n">
-        <v>2.5719</v>
+        <v>2.3281</v>
       </c>
       <c r="H26" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="I26" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="J26" t="n">
-        <v>0.0484999999999971</v>
+        <v>0.08799999999999386</v>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>-1 5 3</t>
+          <t>5 5 3</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
@@ -22953,48 +22590,51 @@
         </is>
       </c>
       <c r="P26" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="Q26" t="inlineStr">
         <is>
           <t>MATCH</t>
         </is>
+      </c>
+      <c r="R26" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="B27" t="n">
-        <v>34.903</v>
+        <v>38.73</v>
       </c>
       <c r="C27" t="n">
-        <v>2.56853</v>
+        <v>2.32311</v>
       </c>
       <c r="D27" t="n">
-        <v>635.429</v>
+        <v>692.952</v>
       </c>
       <c r="E27" t="n">
-        <v>30.00547761497089</v>
+        <v>32.98200856734888</v>
       </c>
       <c r="F27" t="n">
-        <v>34.8545</v>
+        <v>38.8318</v>
       </c>
       <c r="G27" t="n">
-        <v>2.5719</v>
+        <v>2.3172</v>
       </c>
       <c r="H27" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="I27" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="J27" t="n">
-        <v>0.0484999999999971</v>
+        <v>0.1018000000000043</v>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>1 5 3</t>
+          <t>-5 2 5</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
@@ -23018,48 +22658,51 @@
         </is>
       </c>
       <c r="P27" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="Q27" t="inlineStr">
         <is>
           <t>MATCH</t>
         </is>
+      </c>
+      <c r="R27" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="B28" t="n">
-        <v>34.903</v>
+        <v>38.73</v>
       </c>
       <c r="C28" t="n">
-        <v>2.56853</v>
+        <v>2.32311</v>
       </c>
       <c r="D28" t="n">
-        <v>635.429</v>
+        <v>692.952</v>
       </c>
       <c r="E28" t="n">
-        <v>30.00547761497089</v>
+        <v>32.98200856734888</v>
       </c>
       <c r="F28" t="n">
-        <v>34.9523</v>
+        <v>38.8318</v>
       </c>
       <c r="G28" t="n">
-        <v>2.565</v>
+        <v>2.3172</v>
       </c>
       <c r="H28" t="n">
-        <v>17</v>
+        <v>6</v>
       </c>
       <c r="I28" t="n">
-        <v>17</v>
+        <v>6</v>
       </c>
       <c r="J28" t="n">
-        <v>0.04930000000000234</v>
+        <v>0.1018000000000043</v>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>0 2 5</t>
+          <t>5 4 4</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
@@ -23083,48 +22726,51 @@
         </is>
       </c>
       <c r="P28" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="Q28" t="inlineStr">
         <is>
           <t>MATCH</t>
         </is>
+      </c>
+      <c r="R28" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="B29" t="n">
-        <v>34.903</v>
+        <v>38.73</v>
       </c>
       <c r="C29" t="n">
-        <v>2.56853</v>
+        <v>2.32311</v>
       </c>
       <c r="D29" t="n">
-        <v>635.429</v>
+        <v>692.952</v>
       </c>
       <c r="E29" t="n">
-        <v>30.00547761497089</v>
+        <v>32.98200856734888</v>
       </c>
       <c r="F29" t="n">
-        <v>34.9523</v>
+        <v>38.5213</v>
       </c>
       <c r="G29" t="n">
-        <v>2.565</v>
+        <v>2.3351</v>
       </c>
       <c r="H29" t="n">
-        <v>17</v>
+        <v>5</v>
       </c>
       <c r="I29" t="n">
-        <v>17</v>
+        <v>5</v>
       </c>
       <c r="J29" t="n">
-        <v>0.04930000000000234</v>
+        <v>0.2087000000000003</v>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>-1 6 1</t>
+          <t>11 2 0</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
@@ -23148,1312 +22794,287 @@
         </is>
       </c>
       <c r="P29" t="n">
+        <v>7</v>
+      </c>
+      <c r="Q29" t="inlineStr">
+        <is>
+          <t>MATCH</t>
+        </is>
+      </c>
+      <c r="R29" t="n">
         <v>4</v>
-      </c>
-      <c r="Q29" t="inlineStr">
-        <is>
-          <t>MATCH</t>
-        </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B30" t="n">
-        <v>34.903</v>
+        <v>48.204</v>
       </c>
       <c r="C30" t="n">
-        <v>2.56853</v>
+        <v>1.88632</v>
       </c>
       <c r="D30" t="n">
-        <v>635.429</v>
+        <v>2101</v>
       </c>
       <c r="E30" t="n">
-        <v>30.00547761497089</v>
+        <v>100</v>
       </c>
       <c r="F30" t="n">
-        <v>35.0147</v>
+        <v>48.2657</v>
       </c>
       <c r="G30" t="n">
-        <v>2.5605</v>
+        <v>1.884</v>
       </c>
       <c r="H30" t="n">
-        <v>18</v>
+        <v>618</v>
       </c>
       <c r="I30" t="n">
-        <v>18</v>
+        <v>61.86186186186187</v>
       </c>
       <c r="J30" t="n">
-        <v>0.111699999999999</v>
+        <v>0.06170000000000186</v>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>3 1 5</t>
+          <t>1 1 0</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>Cu1.9375S</t>
+          <t>CuS</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>Djurleite</t>
+          <t>Covellite</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>Cu1.9375S</t>
+          <t>CuS</t>
         </is>
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>000711383</t>
+          <t>000752233</t>
         </is>
       </c>
       <c r="P30" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
           <t>MATCH</t>
         </is>
+      </c>
+      <c r="R30" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B31" t="n">
-        <v>34.903</v>
+        <v>48.204</v>
       </c>
       <c r="C31" t="n">
-        <v>2.56853</v>
+        <v>1.88632</v>
       </c>
       <c r="D31" t="n">
-        <v>635.429</v>
+        <v>2101</v>
       </c>
       <c r="E31" t="n">
-        <v>30.00547761497089</v>
+        <v>100</v>
       </c>
       <c r="F31" t="n">
-        <v>35.0147</v>
+        <v>48.0177</v>
       </c>
       <c r="G31" t="n">
-        <v>2.5605</v>
+        <v>1.8931</v>
       </c>
       <c r="H31" t="n">
-        <v>18</v>
+        <v>165</v>
       </c>
       <c r="I31" t="n">
-        <v>18</v>
+        <v>16.51651651651652</v>
       </c>
       <c r="J31" t="n">
-        <v>0.111699999999999</v>
+        <v>0.1863000000000028</v>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>-6 2 4</t>
+          <t>1 0 7</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>Cu1.9375S</t>
+          <t>CuS</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>Djurleite</t>
+          <t>Covellite</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>Cu1.9375S</t>
+          <t>CuS</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>000711383</t>
+          <t>000752233</t>
         </is>
       </c>
       <c r="P31" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
           <t>MATCH</t>
         </is>
+      </c>
+      <c r="R31" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B32" t="n">
-        <v>34.903</v>
+        <v>53.012</v>
       </c>
       <c r="C32" t="n">
-        <v>2.56853</v>
+        <v>1.72599</v>
       </c>
       <c r="D32" t="n">
-        <v>635.429</v>
+        <v>1007.48</v>
       </c>
       <c r="E32" t="n">
-        <v>30.00547761497089</v>
+        <v>47.95240361732508</v>
       </c>
       <c r="F32" t="n">
-        <v>35.0955</v>
+        <v>53.0112</v>
       </c>
       <c r="G32" t="n">
-        <v>2.5548</v>
+        <v>1.726</v>
       </c>
       <c r="H32" t="n">
-        <v>14</v>
+        <v>256</v>
       </c>
       <c r="I32" t="n">
-        <v>14</v>
+        <v>25.62562562562562</v>
       </c>
       <c r="J32" t="n">
-        <v>0.1925000000000026</v>
+        <v>0.0007999999999981355</v>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>7 3 3</t>
+          <t>1 0 8</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>Cu1.9375S</t>
+          <t>CuS</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>Djurleite</t>
+          <t>Covellite</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>Cu1.9375S</t>
+          <t>CuS</t>
         </is>
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>000711383</t>
+          <t>000752233</t>
         </is>
       </c>
       <c r="P32" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="Q32" t="inlineStr">
         <is>
           <t>MATCH</t>
         </is>
+      </c>
+      <c r="R32" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="B33" t="n">
-        <v>34.903</v>
+        <v>74.31399999999999</v>
       </c>
       <c r="C33" t="n">
-        <v>2.56853</v>
+        <v>1.27533</v>
       </c>
       <c r="D33" t="n">
-        <v>635.429</v>
+        <v>765.905</v>
       </c>
       <c r="E33" t="n">
-        <v>30.00547761497089</v>
+        <v>36.45430747263208</v>
       </c>
       <c r="F33" t="n">
-        <v>35.0955</v>
+        <v>74.4939</v>
       </c>
       <c r="G33" t="n">
-        <v>2.5548</v>
+        <v>1.2727</v>
       </c>
       <c r="H33" t="n">
-        <v>14</v>
+        <v>57</v>
       </c>
       <c r="I33" t="n">
-        <v>14</v>
+        <v>5.705705705705705</v>
       </c>
       <c r="J33" t="n">
-        <v>0.1925000000000026</v>
+        <v>0.1799000000000035</v>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>-8 2 3</t>
+          <t>2 0 8</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>Cu1.9375S</t>
+          <t>CuS</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>Djurleite</t>
+          <t>Covellite</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>Cu1.9375S</t>
+          <t>CuS</t>
         </is>
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>000711383</t>
+          <t>000752233</t>
         </is>
       </c>
       <c r="P33" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="Q33" t="inlineStr">
         <is>
           <t>MATCH</t>
         </is>
       </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="n">
-        <v>9</v>
-      </c>
-      <c r="B34" t="n">
-        <v>38.73</v>
-      </c>
-      <c r="C34" t="n">
-        <v>2.32311</v>
-      </c>
-      <c r="D34" t="n">
-        <v>692.952</v>
-      </c>
-      <c r="E34" t="n">
-        <v>32.72176076988823</v>
-      </c>
-      <c r="F34" t="n">
-        <v>38.7261</v>
-      </c>
-      <c r="G34" t="n">
-        <v>2.3233</v>
-      </c>
-      <c r="H34" t="n">
-        <v>8</v>
-      </c>
-      <c r="I34" t="n">
-        <v>8</v>
-      </c>
-      <c r="J34" t="n">
-        <v>0.003899999999994463</v>
-      </c>
-      <c r="K34" t="inlineStr">
-        <is>
-          <t>-5 6 1</t>
-        </is>
-      </c>
-      <c r="L34" t="inlineStr">
-        <is>
-          <t>Cu1.9375S</t>
-        </is>
-      </c>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>Djurleite</t>
-        </is>
-      </c>
-      <c r="N34" t="inlineStr">
-        <is>
-          <t>Cu1.9375S</t>
-        </is>
-      </c>
-      <c r="O34" t="inlineStr">
-        <is>
-          <t>000711383</t>
-        </is>
-      </c>
-      <c r="P34" t="n">
+      <c r="R33" t="n">
         <v>1</v>
-      </c>
-      <c r="Q34" t="inlineStr">
-        <is>
-          <t>MATCH</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="n">
-        <v>9</v>
-      </c>
-      <c r="B35" t="n">
-        <v>38.73</v>
-      </c>
-      <c r="C35" t="n">
-        <v>2.32311</v>
-      </c>
-      <c r="D35" t="n">
-        <v>692.952</v>
-      </c>
-      <c r="E35" t="n">
-        <v>32.72176076988823</v>
-      </c>
-      <c r="F35" t="n">
-        <v>38.7261</v>
-      </c>
-      <c r="G35" t="n">
-        <v>2.3233</v>
-      </c>
-      <c r="H35" t="n">
-        <v>8</v>
-      </c>
-      <c r="I35" t="n">
-        <v>8</v>
-      </c>
-      <c r="J35" t="n">
-        <v>0.003899999999994463</v>
-      </c>
-      <c r="K35" t="inlineStr">
-        <is>
-          <t>5 6 1</t>
-        </is>
-      </c>
-      <c r="L35" t="inlineStr">
-        <is>
-          <t>Cu1.9375S</t>
-        </is>
-      </c>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>Djurleite</t>
-        </is>
-      </c>
-      <c r="N35" t="inlineStr">
-        <is>
-          <t>Cu1.9375S</t>
-        </is>
-      </c>
-      <c r="O35" t="inlineStr">
-        <is>
-          <t>000711383</t>
-        </is>
-      </c>
-      <c r="P35" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q35" t="inlineStr">
-        <is>
-          <t>MATCH</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="n">
-        <v>9</v>
-      </c>
-      <c r="B36" t="n">
-        <v>38.73</v>
-      </c>
-      <c r="C36" t="n">
-        <v>2.32311</v>
-      </c>
-      <c r="D36" t="n">
-        <v>692.952</v>
-      </c>
-      <c r="E36" t="n">
-        <v>32.72176076988823</v>
-      </c>
-      <c r="F36" t="n">
-        <v>38.642</v>
-      </c>
-      <c r="G36" t="n">
-        <v>2.3281</v>
-      </c>
-      <c r="H36" t="n">
-        <v>6</v>
-      </c>
-      <c r="I36" t="n">
-        <v>6</v>
-      </c>
-      <c r="J36" t="n">
-        <v>0.08799999999999386</v>
-      </c>
-      <c r="K36" t="inlineStr">
-        <is>
-          <t>-3 3 5</t>
-        </is>
-      </c>
-      <c r="L36" t="inlineStr">
-        <is>
-          <t>Cu1.9375S</t>
-        </is>
-      </c>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>Djurleite</t>
-        </is>
-      </c>
-      <c r="N36" t="inlineStr">
-        <is>
-          <t>Cu1.9375S</t>
-        </is>
-      </c>
-      <c r="O36" t="inlineStr">
-        <is>
-          <t>000711383</t>
-        </is>
-      </c>
-      <c r="P36" t="n">
-        <v>3</v>
-      </c>
-      <c r="Q36" t="inlineStr">
-        <is>
-          <t>MATCH</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="n">
-        <v>9</v>
-      </c>
-      <c r="B37" t="n">
-        <v>38.73</v>
-      </c>
-      <c r="C37" t="n">
-        <v>2.32311</v>
-      </c>
-      <c r="D37" t="n">
-        <v>692.952</v>
-      </c>
-      <c r="E37" t="n">
-        <v>32.72176076988823</v>
-      </c>
-      <c r="F37" t="n">
-        <v>38.642</v>
-      </c>
-      <c r="G37" t="n">
-        <v>2.3281</v>
-      </c>
-      <c r="H37" t="n">
-        <v>6</v>
-      </c>
-      <c r="I37" t="n">
-        <v>6</v>
-      </c>
-      <c r="J37" t="n">
-        <v>0.08799999999999386</v>
-      </c>
-      <c r="K37" t="inlineStr">
-        <is>
-          <t>5 5 3</t>
-        </is>
-      </c>
-      <c r="L37" t="inlineStr">
-        <is>
-          <t>Cu1.9375S</t>
-        </is>
-      </c>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>Djurleite</t>
-        </is>
-      </c>
-      <c r="N37" t="inlineStr">
-        <is>
-          <t>Cu1.9375S</t>
-        </is>
-      </c>
-      <c r="O37" t="inlineStr">
-        <is>
-          <t>000711383</t>
-        </is>
-      </c>
-      <c r="P37" t="n">
-        <v>4</v>
-      </c>
-      <c r="Q37" t="inlineStr">
-        <is>
-          <t>MATCH</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="n">
-        <v>9</v>
-      </c>
-      <c r="B38" t="n">
-        <v>38.73</v>
-      </c>
-      <c r="C38" t="n">
-        <v>2.32311</v>
-      </c>
-      <c r="D38" t="n">
-        <v>692.952</v>
-      </c>
-      <c r="E38" t="n">
-        <v>32.72176076988823</v>
-      </c>
-      <c r="F38" t="n">
-        <v>38.8318</v>
-      </c>
-      <c r="G38" t="n">
-        <v>2.3172</v>
-      </c>
-      <c r="H38" t="n">
-        <v>6</v>
-      </c>
-      <c r="I38" t="n">
-        <v>6</v>
-      </c>
-      <c r="J38" t="n">
-        <v>0.1018000000000043</v>
-      </c>
-      <c r="K38" t="inlineStr">
-        <is>
-          <t>-5 2 5</t>
-        </is>
-      </c>
-      <c r="L38" t="inlineStr">
-        <is>
-          <t>Cu1.9375S</t>
-        </is>
-      </c>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>Djurleite</t>
-        </is>
-      </c>
-      <c r="N38" t="inlineStr">
-        <is>
-          <t>Cu1.9375S</t>
-        </is>
-      </c>
-      <c r="O38" t="inlineStr">
-        <is>
-          <t>000711383</t>
-        </is>
-      </c>
-      <c r="P38" t="n">
-        <v>5</v>
-      </c>
-      <c r="Q38" t="inlineStr">
-        <is>
-          <t>MATCH</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="n">
-        <v>9</v>
-      </c>
-      <c r="B39" t="n">
-        <v>38.73</v>
-      </c>
-      <c r="C39" t="n">
-        <v>2.32311</v>
-      </c>
-      <c r="D39" t="n">
-        <v>692.952</v>
-      </c>
-      <c r="E39" t="n">
-        <v>32.72176076988823</v>
-      </c>
-      <c r="F39" t="n">
-        <v>38.8318</v>
-      </c>
-      <c r="G39" t="n">
-        <v>2.3172</v>
-      </c>
-      <c r="H39" t="n">
-        <v>6</v>
-      </c>
-      <c r="I39" t="n">
-        <v>6</v>
-      </c>
-      <c r="J39" t="n">
-        <v>0.1018000000000043</v>
-      </c>
-      <c r="K39" t="inlineStr">
-        <is>
-          <t>5 4 4</t>
-        </is>
-      </c>
-      <c r="L39" t="inlineStr">
-        <is>
-          <t>Cu1.9375S</t>
-        </is>
-      </c>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>Djurleite</t>
-        </is>
-      </c>
-      <c r="N39" t="inlineStr">
-        <is>
-          <t>Cu1.9375S</t>
-        </is>
-      </c>
-      <c r="O39" t="inlineStr">
-        <is>
-          <t>000711383</t>
-        </is>
-      </c>
-      <c r="P39" t="n">
-        <v>6</v>
-      </c>
-      <c r="Q39" t="inlineStr">
-        <is>
-          <t>MATCH</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="n">
-        <v>9</v>
-      </c>
-      <c r="B40" t="n">
-        <v>38.73</v>
-      </c>
-      <c r="C40" t="n">
-        <v>2.32311</v>
-      </c>
-      <c r="D40" t="n">
-        <v>692.952</v>
-      </c>
-      <c r="E40" t="n">
-        <v>32.72176076988823</v>
-      </c>
-      <c r="F40" t="n">
-        <v>38.5213</v>
-      </c>
-      <c r="G40" t="n">
-        <v>2.3351</v>
-      </c>
-      <c r="H40" t="n">
-        <v>5</v>
-      </c>
-      <c r="I40" t="n">
-        <v>5</v>
-      </c>
-      <c r="J40" t="n">
-        <v>0.2087000000000003</v>
-      </c>
-      <c r="K40" t="inlineStr">
-        <is>
-          <t>11 2 0</t>
-        </is>
-      </c>
-      <c r="L40" t="inlineStr">
-        <is>
-          <t>Cu1.9375S</t>
-        </is>
-      </c>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>Djurleite</t>
-        </is>
-      </c>
-      <c r="N40" t="inlineStr">
-        <is>
-          <t>Cu1.9375S</t>
-        </is>
-      </c>
-      <c r="O40" t="inlineStr">
-        <is>
-          <t>000711383</t>
-        </is>
-      </c>
-      <c r="P40" t="n">
-        <v>7</v>
-      </c>
-      <c r="Q40" t="inlineStr">
-        <is>
-          <t>MATCH</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="n">
-        <v>11</v>
-      </c>
-      <c r="B41" t="n">
-        <v>44.05</v>
-      </c>
-      <c r="C41" t="n">
-        <v>2.05408</v>
-      </c>
-      <c r="D41" t="n">
-        <v>703.952</v>
-      </c>
-      <c r="E41" t="n">
-        <v>33.24118977574833</v>
-      </c>
-      <c r="F41" t="n">
-        <v>43.9154</v>
-      </c>
-      <c r="G41" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="H41" t="n">
-        <v>8</v>
-      </c>
-      <c r="I41" t="n">
-        <v>8</v>
-      </c>
-      <c r="J41" t="n">
-        <v>0.1345999999999989</v>
-      </c>
-      <c r="K41" t="inlineStr">
-        <is>
-          <t>1 0 20</t>
-        </is>
-      </c>
-      <c r="L41" t="inlineStr">
-        <is>
-          <t>Cu39S28</t>
-        </is>
-      </c>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>Spionkopite</t>
-        </is>
-      </c>
-      <c r="N41" t="inlineStr">
-        <is>
-          <t>Cu39S28</t>
-        </is>
-      </c>
-      <c r="O41" t="inlineStr">
-        <is>
-          <t>000360380</t>
-        </is>
-      </c>
-      <c r="P41" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q41" t="inlineStr">
-        <is>
-          <t>MATCH</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="n">
-        <v>13</v>
-      </c>
-      <c r="B42" t="n">
-        <v>48.224</v>
-      </c>
-      <c r="C42" t="n">
-        <v>1.88557</v>
-      </c>
-      <c r="D42" t="n">
-        <v>2117.71</v>
-      </c>
-      <c r="E42" t="n">
-        <v>100</v>
-      </c>
-      <c r="F42" t="n">
-        <v>48.2657</v>
-      </c>
-      <c r="G42" t="n">
-        <v>1.884</v>
-      </c>
-      <c r="H42" t="n">
-        <v>618</v>
-      </c>
-      <c r="I42" t="n">
-        <v>61.86186186186187</v>
-      </c>
-      <c r="J42" t="n">
-        <v>0.04170000000000584</v>
-      </c>
-      <c r="K42" t="inlineStr">
-        <is>
-          <t>1 1 0</t>
-        </is>
-      </c>
-      <c r="L42" t="inlineStr">
-        <is>
-          <t>CuS</t>
-        </is>
-      </c>
-      <c r="M42" t="inlineStr">
-        <is>
-          <t>Covellite</t>
-        </is>
-      </c>
-      <c r="N42" t="inlineStr">
-        <is>
-          <t>CuS</t>
-        </is>
-      </c>
-      <c r="O42" t="inlineStr">
-        <is>
-          <t>000752233</t>
-        </is>
-      </c>
-      <c r="P42" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q42" t="inlineStr">
-        <is>
-          <t>MATCH</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="n">
-        <v>13</v>
-      </c>
-      <c r="B43" t="n">
-        <v>48.224</v>
-      </c>
-      <c r="C43" t="n">
-        <v>1.88557</v>
-      </c>
-      <c r="D43" t="n">
-        <v>2117.71</v>
-      </c>
-      <c r="E43" t="n">
-        <v>100</v>
-      </c>
-      <c r="F43" t="n">
-        <v>48.0177</v>
-      </c>
-      <c r="G43" t="n">
-        <v>1.8931</v>
-      </c>
-      <c r="H43" t="n">
-        <v>165</v>
-      </c>
-      <c r="I43" t="n">
-        <v>16.51651651651652</v>
-      </c>
-      <c r="J43" t="n">
-        <v>0.2062999999999988</v>
-      </c>
-      <c r="K43" t="inlineStr">
-        <is>
-          <t>1 0 7</t>
-        </is>
-      </c>
-      <c r="L43" t="inlineStr">
-        <is>
-          <t>CuS</t>
-        </is>
-      </c>
-      <c r="M43" t="inlineStr">
-        <is>
-          <t>Covellite</t>
-        </is>
-      </c>
-      <c r="N43" t="inlineStr">
-        <is>
-          <t>CuS</t>
-        </is>
-      </c>
-      <c r="O43" t="inlineStr">
-        <is>
-          <t>000752233</t>
-        </is>
-      </c>
-      <c r="P43" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q43" t="inlineStr">
-        <is>
-          <t>MATCH</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="n">
-        <v>14</v>
-      </c>
-      <c r="B44" t="n">
-        <v>53.012</v>
-      </c>
-      <c r="C44" t="n">
-        <v>1.72599</v>
-      </c>
-      <c r="D44" t="n">
-        <v>1007.48</v>
-      </c>
-      <c r="E44" t="n">
-        <v>47.57403043853974</v>
-      </c>
-      <c r="F44" t="n">
-        <v>53.0112</v>
-      </c>
-      <c r="G44" t="n">
-        <v>1.726</v>
-      </c>
-      <c r="H44" t="n">
-        <v>256</v>
-      </c>
-      <c r="I44" t="n">
-        <v>25.62562562562562</v>
-      </c>
-      <c r="J44" t="n">
-        <v>0.0007999999999981355</v>
-      </c>
-      <c r="K44" t="inlineStr">
-        <is>
-          <t>1 0 8</t>
-        </is>
-      </c>
-      <c r="L44" t="inlineStr">
-        <is>
-          <t>CuS</t>
-        </is>
-      </c>
-      <c r="M44" t="inlineStr">
-        <is>
-          <t>Covellite</t>
-        </is>
-      </c>
-      <c r="N44" t="inlineStr">
-        <is>
-          <t>CuS</t>
-        </is>
-      </c>
-      <c r="O44" t="inlineStr">
-        <is>
-          <t>000752233</t>
-        </is>
-      </c>
-      <c r="P44" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q44" t="inlineStr">
-        <is>
-          <t>MATCH</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="n">
-        <v>18</v>
-      </c>
-      <c r="B45" t="n">
-        <v>59.376</v>
-      </c>
-      <c r="C45" t="n">
-        <v>1.55528</v>
-      </c>
-      <c r="D45" t="n">
-        <v>1194.52</v>
-      </c>
-      <c r="E45" t="n">
-        <v>56.40621237091008</v>
-      </c>
-      <c r="F45" t="n">
-        <v>59.0765</v>
-      </c>
-      <c r="G45" t="n">
-        <v>1.5624</v>
-      </c>
-      <c r="H45" t="n">
-        <v>104</v>
-      </c>
-      <c r="I45" t="n">
-        <v>10.41041041041041</v>
-      </c>
-      <c r="J45" t="n">
-        <v>0.2994999999999948</v>
-      </c>
-      <c r="K45" t="inlineStr">
-        <is>
-          <t>2 0 3</t>
-        </is>
-      </c>
-      <c r="L45" t="inlineStr">
-        <is>
-          <t>CuS</t>
-        </is>
-      </c>
-      <c r="M45" t="inlineStr">
-        <is>
-          <t>Covellite</t>
-        </is>
-      </c>
-      <c r="N45" t="inlineStr">
-        <is>
-          <t>CuS</t>
-        </is>
-      </c>
-      <c r="O45" t="inlineStr">
-        <is>
-          <t>000752233</t>
-        </is>
-      </c>
-      <c r="P45" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q45" t="inlineStr">
-        <is>
-          <t>MATCH</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="n">
-        <v>24</v>
-      </c>
-      <c r="B46" t="n">
-        <v>69.116</v>
-      </c>
-      <c r="C46" t="n">
-        <v>1.35797</v>
-      </c>
-      <c r="D46" t="n">
-        <v>739.095</v>
-      </c>
-      <c r="E46" t="n">
-        <v>34.90067100783394</v>
-      </c>
-      <c r="F46" t="n">
-        <v>68.9388</v>
-      </c>
-      <c r="G46" t="n">
-        <v>1.361</v>
-      </c>
-      <c r="H46" t="n">
-        <v>8</v>
-      </c>
-      <c r="I46" t="n">
-        <v>8</v>
-      </c>
-      <c r="J46" t="n">
-        <v>0.1771999999999991</v>
-      </c>
-      <c r="K46" t="inlineStr">
-        <is>
-          <t>2 0 7</t>
-        </is>
-      </c>
-      <c r="L46" t="inlineStr">
-        <is>
-          <t>Cu39S28</t>
-        </is>
-      </c>
-      <c r="M46" t="inlineStr">
-        <is>
-          <t>Spionkopite</t>
-        </is>
-      </c>
-      <c r="N46" t="inlineStr">
-        <is>
-          <t>Cu39S28</t>
-        </is>
-      </c>
-      <c r="O46" t="inlineStr">
-        <is>
-          <t>000360380</t>
-        </is>
-      </c>
-      <c r="P46" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q46" t="inlineStr">
-        <is>
-          <t>MATCH</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="n">
-        <v>25</v>
-      </c>
-      <c r="B47" t="n">
-        <v>70.03700000000001</v>
-      </c>
-      <c r="C47" t="n">
-        <v>1.34235</v>
-      </c>
-      <c r="D47" t="n">
-        <v>739.048</v>
-      </c>
-      <c r="E47" t="n">
-        <v>34.89845162935435</v>
-      </c>
-      <c r="F47" t="n">
-        <v>69.749</v>
-      </c>
-      <c r="G47" t="n">
-        <v>1.3472</v>
-      </c>
-      <c r="H47" t="n">
-        <v>60</v>
-      </c>
-      <c r="I47" t="n">
-        <v>6.006006006006006</v>
-      </c>
-      <c r="J47" t="n">
-        <v>0.2880000000000109</v>
-      </c>
-      <c r="K47" t="inlineStr">
-        <is>
-          <t>1 0 11</t>
-        </is>
-      </c>
-      <c r="L47" t="inlineStr">
-        <is>
-          <t>CuS</t>
-        </is>
-      </c>
-      <c r="M47" t="inlineStr">
-        <is>
-          <t>Covellite</t>
-        </is>
-      </c>
-      <c r="N47" t="inlineStr">
-        <is>
-          <t>CuS</t>
-        </is>
-      </c>
-      <c r="O47" t="inlineStr">
-        <is>
-          <t>000752233</t>
-        </is>
-      </c>
-      <c r="P47" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q47" t="inlineStr">
-        <is>
-          <t>MATCH</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="n">
-        <v>27</v>
-      </c>
-      <c r="B48" t="n">
-        <v>71.101</v>
-      </c>
-      <c r="C48" t="n">
-        <v>1.32485</v>
-      </c>
-      <c r="D48" t="n">
-        <v>711.048</v>
-      </c>
-      <c r="E48" t="n">
-        <v>33.57626870534681</v>
-      </c>
-      <c r="F48" t="n">
-        <v>71.3383</v>
-      </c>
-      <c r="G48" t="n">
-        <v>1.321</v>
-      </c>
-      <c r="H48" t="n">
-        <v>12</v>
-      </c>
-      <c r="I48" t="n">
-        <v>12</v>
-      </c>
-      <c r="J48" t="n">
-        <v>0.2373000000000047</v>
-      </c>
-      <c r="K48" t="inlineStr">
-        <is>
-          <t>12 0 19</t>
-        </is>
-      </c>
-      <c r="L48" t="inlineStr">
-        <is>
-          <t>Cu39S28</t>
-        </is>
-      </c>
-      <c r="M48" t="inlineStr">
-        <is>
-          <t>Spionkopite</t>
-        </is>
-      </c>
-      <c r="N48" t="inlineStr">
-        <is>
-          <t>Cu39S28</t>
-        </is>
-      </c>
-      <c r="O48" t="inlineStr">
-        <is>
-          <t>000360380</t>
-        </is>
-      </c>
-      <c r="P48" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q48" t="inlineStr">
-        <is>
-          <t>MATCH</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="n">
-        <v>31</v>
-      </c>
-      <c r="B49" t="n">
-        <v>74.31399999999999</v>
-      </c>
-      <c r="C49" t="n">
-        <v>1.27533</v>
-      </c>
-      <c r="D49" t="n">
-        <v>765.905</v>
-      </c>
-      <c r="E49" t="n">
-        <v>36.16666115757115</v>
-      </c>
-      <c r="F49" t="n">
-        <v>74.4939</v>
-      </c>
-      <c r="G49" t="n">
-        <v>1.2727</v>
-      </c>
-      <c r="H49" t="n">
-        <v>57</v>
-      </c>
-      <c r="I49" t="n">
-        <v>5.705705705705705</v>
-      </c>
-      <c r="J49" t="n">
-        <v>0.1799000000000035</v>
-      </c>
-      <c r="K49" t="inlineStr">
-        <is>
-          <t>2 0 8</t>
-        </is>
-      </c>
-      <c r="L49" t="inlineStr">
-        <is>
-          <t>CuS</t>
-        </is>
-      </c>
-      <c r="M49" t="inlineStr">
-        <is>
-          <t>Covellite</t>
-        </is>
-      </c>
-      <c r="N49" t="inlineStr">
-        <is>
-          <t>CuS</t>
-        </is>
-      </c>
-      <c r="O49" t="inlineStr">
-        <is>
-          <t>000752233</t>
-        </is>
-      </c>
-      <c r="P49" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q49" t="inlineStr">
-        <is>
-          <t>MATCH</t>
-        </is>
       </c>
     </row>
   </sheetData>
@@ -24467,7 +23088,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q16"/>
+  <dimension ref="A1:R9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -24556,61 +23177,66 @@
           <t>Status</t>
         </is>
       </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>Phase_Priority</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B2" t="n">
-        <v>26.186</v>
+        <v>27.925</v>
       </c>
       <c r="C2" t="n">
-        <v>3.4004</v>
+        <v>3.19243</v>
       </c>
       <c r="D2" t="n">
-        <v>498.571</v>
+        <v>741.667</v>
       </c>
       <c r="E2" t="n">
-        <v>23.54293080733434</v>
+        <v>35.30066634935745</v>
       </c>
       <c r="F2" t="n">
-        <v>26.2118</v>
+        <v>27.8619</v>
       </c>
       <c r="G2" t="n">
-        <v>3.397</v>
+        <v>3.1995</v>
       </c>
       <c r="H2" t="n">
-        <v>43</v>
+        <v>261</v>
       </c>
       <c r="I2" t="n">
-        <v>43</v>
+        <v>26.12612612612612</v>
       </c>
       <c r="J2" t="n">
-        <v>0.02580000000000027</v>
+        <v>0.06310000000000215</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>4 4 0</t>
+          <t>1 0 1</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>Cu1.9375S</t>
+          <t>CuS</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>Djurleite</t>
+          <t>Covellite</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>Cu1.9375S</t>
+          <t>CuS</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>000711383</t>
+          <t>000752233</t>
         </is>
       </c>
       <c r="P2" t="n">
@@ -24621,41 +23247,44 @@
           <t>MATCH</t>
         </is>
       </c>
+      <c r="R2" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="B3" t="n">
-        <v>27.905</v>
+        <v>29.501</v>
       </c>
       <c r="C3" t="n">
-        <v>3.19472</v>
+        <v>3.02541</v>
       </c>
       <c r="D3" t="n">
-        <v>758.143</v>
+        <v>1238.62</v>
       </c>
       <c r="E3" t="n">
-        <v>35.80013316270878</v>
+        <v>58.95383150880532</v>
       </c>
       <c r="F3" t="n">
-        <v>27.8619</v>
+        <v>29.4683</v>
       </c>
       <c r="G3" t="n">
-        <v>3.1995</v>
+        <v>3.0286</v>
       </c>
       <c r="H3" t="n">
-        <v>261</v>
+        <v>572</v>
       </c>
       <c r="I3" t="n">
-        <v>26.12612612612612</v>
+        <v>57.25725725725725</v>
       </c>
       <c r="J3" t="n">
-        <v>0.04310000000000258</v>
+        <v>0.03270000000000195</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>1 0 1</t>
+          <t>1 0 2</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -24686,41 +23315,44 @@
           <t>MATCH</t>
         </is>
       </c>
+      <c r="R3" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="B4" t="n">
-        <v>29.501</v>
+        <v>31.997</v>
       </c>
       <c r="C4" t="n">
-        <v>3.02541</v>
+        <v>2.79484</v>
       </c>
       <c r="D4" t="n">
-        <v>1238.62</v>
+        <v>1324.05</v>
       </c>
       <c r="E4" t="n">
-        <v>58.48865047622195</v>
+        <v>63.01999048072346</v>
       </c>
       <c r="F4" t="n">
-        <v>29.4683</v>
+        <v>31.982</v>
       </c>
       <c r="G4" t="n">
-        <v>3.0286</v>
+        <v>2.7961</v>
       </c>
       <c r="H4" t="n">
-        <v>572</v>
+        <v>999</v>
       </c>
       <c r="I4" t="n">
-        <v>57.25725725725725</v>
+        <v>100</v>
       </c>
       <c r="J4" t="n">
-        <v>0.03270000000000195</v>
+        <v>0.01500000000000057</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>1 0 2</t>
+          <t>1 0 3</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -24751,61 +23383,64 @@
           <t>MATCH</t>
         </is>
       </c>
+      <c r="R4" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="B5" t="n">
-        <v>32.018</v>
+        <v>32.304</v>
       </c>
       <c r="C5" t="n">
-        <v>2.7931</v>
+        <v>2.76898</v>
       </c>
       <c r="D5" t="n">
-        <v>1335.95</v>
+        <v>1318.29</v>
       </c>
       <c r="E5" t="n">
-        <v>63.08465276170958</v>
+        <v>62.74583531651594</v>
       </c>
       <c r="F5" t="n">
-        <v>32.0508</v>
+        <v>32.2076</v>
       </c>
       <c r="G5" t="n">
-        <v>2.7902</v>
+        <v>2.777</v>
       </c>
       <c r="H5" t="n">
-        <v>6</v>
+        <v>30</v>
       </c>
       <c r="I5" t="n">
-        <v>6</v>
+        <v>30</v>
       </c>
       <c r="J5" t="n">
-        <v>0.03280000000000172</v>
+        <v>0.09640000000000271</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>2 5 2</t>
+          <t>6 0 8</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>Cu1.9375S</t>
+          <t>Cu39S28</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>Djurleite</t>
+          <t>Spionkopite</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>Cu1.9375S</t>
+          <t>Cu39S28</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>000711383</t>
+          <t>000360380</t>
         </is>
       </c>
       <c r="P5" t="n">
@@ -24816,61 +23451,64 @@
           <t>MATCH</t>
         </is>
       </c>
+      <c r="R5" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="B6" t="n">
-        <v>32.304</v>
+        <v>38.73</v>
       </c>
       <c r="C6" t="n">
-        <v>2.76898</v>
+        <v>2.32311</v>
       </c>
       <c r="D6" t="n">
-        <v>1318.29</v>
+        <v>692.952</v>
       </c>
       <c r="E6" t="n">
-        <v>62.25073310321054</v>
+        <v>32.98200856734888</v>
       </c>
       <c r="F6" t="n">
-        <v>32.2076</v>
+        <v>38.7261</v>
       </c>
       <c r="G6" t="n">
-        <v>2.777</v>
+        <v>2.3233</v>
       </c>
       <c r="H6" t="n">
-        <v>30</v>
+        <v>8</v>
       </c>
       <c r="I6" t="n">
-        <v>30</v>
+        <v>8</v>
       </c>
       <c r="J6" t="n">
-        <v>0.09640000000000271</v>
+        <v>0.003899999999994463</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>6 0 8</t>
+          <t>-5 6 1</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>Cu39S28</t>
+          <t>Cu1.9375S</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>Spionkopite</t>
+          <t>Djurleite</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>Cu39S28</t>
+          <t>Cu1.9375S</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>000360380</t>
+          <t>000711383</t>
         </is>
       </c>
       <c r="P6" t="n">
@@ -24881,61 +23519,64 @@
           <t>MATCH</t>
         </is>
       </c>
+      <c r="R6" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B7" t="n">
-        <v>34.903</v>
+        <v>48.204</v>
       </c>
       <c r="C7" t="n">
-        <v>2.56853</v>
+        <v>1.88632</v>
       </c>
       <c r="D7" t="n">
-        <v>635.429</v>
+        <v>2101</v>
       </c>
       <c r="E7" t="n">
-        <v>30.00547761497089</v>
+        <v>100</v>
       </c>
       <c r="F7" t="n">
-        <v>34.8545</v>
+        <v>48.2657</v>
       </c>
       <c r="G7" t="n">
-        <v>2.5719</v>
+        <v>1.884</v>
       </c>
       <c r="H7" t="n">
-        <v>16</v>
+        <v>618</v>
       </c>
       <c r="I7" t="n">
-        <v>16</v>
+        <v>61.86186186186187</v>
       </c>
       <c r="J7" t="n">
-        <v>0.0484999999999971</v>
+        <v>0.06170000000000186</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>-1 5 3</t>
+          <t>1 1 0</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>Cu1.9375S</t>
+          <t>CuS</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>Djurleite</t>
+          <t>Covellite</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>Cu1.9375S</t>
+          <t>CuS</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>000711383</t>
+          <t>000752233</t>
         </is>
       </c>
       <c r="P7" t="n">
@@ -24946,61 +23587,64 @@
           <t>MATCH</t>
         </is>
       </c>
+      <c r="R7" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B8" t="n">
-        <v>38.73</v>
+        <v>53.012</v>
       </c>
       <c r="C8" t="n">
-        <v>2.32311</v>
+        <v>1.72599</v>
       </c>
       <c r="D8" t="n">
-        <v>692.952</v>
+        <v>1007.48</v>
       </c>
       <c r="E8" t="n">
-        <v>32.72176076988823</v>
+        <v>47.95240361732508</v>
       </c>
       <c r="F8" t="n">
-        <v>38.7261</v>
+        <v>53.0112</v>
       </c>
       <c r="G8" t="n">
-        <v>2.3233</v>
+        <v>1.726</v>
       </c>
       <c r="H8" t="n">
-        <v>8</v>
+        <v>256</v>
       </c>
       <c r="I8" t="n">
-        <v>8</v>
+        <v>25.62562562562562</v>
       </c>
       <c r="J8" t="n">
-        <v>0.003899999999994463</v>
+        <v>0.0007999999999981355</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>-5 6 1</t>
+          <t>1 0 8</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>Cu1.9375S</t>
+          <t>CuS</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>Djurleite</t>
+          <t>Covellite</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>Cu1.9375S</t>
+          <t>CuS</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>000711383</t>
+          <t>000752233</t>
         </is>
       </c>
       <c r="P8" t="n">
@@ -25010,6 +23654,9 @@
         <is>
           <t>MATCH</t>
         </is>
+      </c>
+      <c r="R8" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="9">
@@ -25017,55 +23664,55 @@
         <v>11</v>
       </c>
       <c r="B9" t="n">
-        <v>44.05</v>
+        <v>74.31399999999999</v>
       </c>
       <c r="C9" t="n">
-        <v>2.05408</v>
+        <v>1.27533</v>
       </c>
       <c r="D9" t="n">
-        <v>703.952</v>
+        <v>765.905</v>
       </c>
       <c r="E9" t="n">
-        <v>33.24118977574833</v>
+        <v>36.45430747263208</v>
       </c>
       <c r="F9" t="n">
-        <v>43.9154</v>
+        <v>74.4939</v>
       </c>
       <c r="G9" t="n">
-        <v>2.06</v>
+        <v>1.2727</v>
       </c>
       <c r="H9" t="n">
-        <v>8</v>
+        <v>57</v>
       </c>
       <c r="I9" t="n">
-        <v>8</v>
+        <v>5.705705705705705</v>
       </c>
       <c r="J9" t="n">
-        <v>0.1345999999999989</v>
+        <v>0.1799000000000035</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>1 0 20</t>
+          <t>2 0 8</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>Cu39S28</t>
+          <t>CuS</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>Spionkopite</t>
+          <t>Covellite</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>Cu39S28</t>
+          <t>CuS</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>000360380</t>
+          <t>000752233</t>
         </is>
       </c>
       <c r="P9" t="n">
@@ -25076,460 +23723,8 @@
           <t>MATCH</t>
         </is>
       </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="n">
-        <v>13</v>
-      </c>
-      <c r="B10" t="n">
-        <v>48.224</v>
-      </c>
-      <c r="C10" t="n">
-        <v>1.88557</v>
-      </c>
-      <c r="D10" t="n">
-        <v>2117.71</v>
-      </c>
-      <c r="E10" t="n">
-        <v>100</v>
-      </c>
-      <c r="F10" t="n">
-        <v>48.2657</v>
-      </c>
-      <c r="G10" t="n">
-        <v>1.884</v>
-      </c>
-      <c r="H10" t="n">
-        <v>618</v>
-      </c>
-      <c r="I10" t="n">
-        <v>61.86186186186187</v>
-      </c>
-      <c r="J10" t="n">
-        <v>0.04170000000000584</v>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>1 1 0</t>
-        </is>
-      </c>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>CuS</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>Covellite</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>CuS</t>
-        </is>
-      </c>
-      <c r="O10" t="inlineStr">
-        <is>
-          <t>000752233</t>
-        </is>
-      </c>
-      <c r="P10" t="n">
+      <c r="R9" t="n">
         <v>1</v>
-      </c>
-      <c r="Q10" t="inlineStr">
-        <is>
-          <t>MATCH</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="n">
-        <v>14</v>
-      </c>
-      <c r="B11" t="n">
-        <v>53.012</v>
-      </c>
-      <c r="C11" t="n">
-        <v>1.72599</v>
-      </c>
-      <c r="D11" t="n">
-        <v>1007.48</v>
-      </c>
-      <c r="E11" t="n">
-        <v>47.57403043853974</v>
-      </c>
-      <c r="F11" t="n">
-        <v>53.0112</v>
-      </c>
-      <c r="G11" t="n">
-        <v>1.726</v>
-      </c>
-      <c r="H11" t="n">
-        <v>256</v>
-      </c>
-      <c r="I11" t="n">
-        <v>25.62562562562562</v>
-      </c>
-      <c r="J11" t="n">
-        <v>0.0007999999999981355</v>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>1 0 8</t>
-        </is>
-      </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>CuS</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>Covellite</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>CuS</t>
-        </is>
-      </c>
-      <c r="O11" t="inlineStr">
-        <is>
-          <t>000752233</t>
-        </is>
-      </c>
-      <c r="P11" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q11" t="inlineStr">
-        <is>
-          <t>MATCH</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="n">
-        <v>18</v>
-      </c>
-      <c r="B12" t="n">
-        <v>59.376</v>
-      </c>
-      <c r="C12" t="n">
-        <v>1.55528</v>
-      </c>
-      <c r="D12" t="n">
-        <v>1194.52</v>
-      </c>
-      <c r="E12" t="n">
-        <v>56.40621237091008</v>
-      </c>
-      <c r="F12" t="n">
-        <v>59.0765</v>
-      </c>
-      <c r="G12" t="n">
-        <v>1.5624</v>
-      </c>
-      <c r="H12" t="n">
-        <v>104</v>
-      </c>
-      <c r="I12" t="n">
-        <v>10.41041041041041</v>
-      </c>
-      <c r="J12" t="n">
-        <v>0.2994999999999948</v>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>2 0 3</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>CuS</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>Covellite</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>CuS</t>
-        </is>
-      </c>
-      <c r="O12" t="inlineStr">
-        <is>
-          <t>000752233</t>
-        </is>
-      </c>
-      <c r="P12" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q12" t="inlineStr">
-        <is>
-          <t>MATCH</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="n">
-        <v>24</v>
-      </c>
-      <c r="B13" t="n">
-        <v>69.116</v>
-      </c>
-      <c r="C13" t="n">
-        <v>1.35797</v>
-      </c>
-      <c r="D13" t="n">
-        <v>739.095</v>
-      </c>
-      <c r="E13" t="n">
-        <v>34.90067100783394</v>
-      </c>
-      <c r="F13" t="n">
-        <v>68.9388</v>
-      </c>
-      <c r="G13" t="n">
-        <v>1.361</v>
-      </c>
-      <c r="H13" t="n">
-        <v>8</v>
-      </c>
-      <c r="I13" t="n">
-        <v>8</v>
-      </c>
-      <c r="J13" t="n">
-        <v>0.1771999999999991</v>
-      </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>2 0 7</t>
-        </is>
-      </c>
-      <c r="L13" t="inlineStr">
-        <is>
-          <t>Cu39S28</t>
-        </is>
-      </c>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>Spionkopite</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr">
-        <is>
-          <t>Cu39S28</t>
-        </is>
-      </c>
-      <c r="O13" t="inlineStr">
-        <is>
-          <t>000360380</t>
-        </is>
-      </c>
-      <c r="P13" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q13" t="inlineStr">
-        <is>
-          <t>MATCH</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="n">
-        <v>25</v>
-      </c>
-      <c r="B14" t="n">
-        <v>70.03700000000001</v>
-      </c>
-      <c r="C14" t="n">
-        <v>1.34235</v>
-      </c>
-      <c r="D14" t="n">
-        <v>739.048</v>
-      </c>
-      <c r="E14" t="n">
-        <v>34.89845162935435</v>
-      </c>
-      <c r="F14" t="n">
-        <v>69.749</v>
-      </c>
-      <c r="G14" t="n">
-        <v>1.3472</v>
-      </c>
-      <c r="H14" t="n">
-        <v>60</v>
-      </c>
-      <c r="I14" t="n">
-        <v>6.006006006006006</v>
-      </c>
-      <c r="J14" t="n">
-        <v>0.2880000000000109</v>
-      </c>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>1 0 11</t>
-        </is>
-      </c>
-      <c r="L14" t="inlineStr">
-        <is>
-          <t>CuS</t>
-        </is>
-      </c>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>Covellite</t>
-        </is>
-      </c>
-      <c r="N14" t="inlineStr">
-        <is>
-          <t>CuS</t>
-        </is>
-      </c>
-      <c r="O14" t="inlineStr">
-        <is>
-          <t>000752233</t>
-        </is>
-      </c>
-      <c r="P14" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q14" t="inlineStr">
-        <is>
-          <t>MATCH</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="n">
-        <v>27</v>
-      </c>
-      <c r="B15" t="n">
-        <v>71.101</v>
-      </c>
-      <c r="C15" t="n">
-        <v>1.32485</v>
-      </c>
-      <c r="D15" t="n">
-        <v>711.048</v>
-      </c>
-      <c r="E15" t="n">
-        <v>33.57626870534681</v>
-      </c>
-      <c r="F15" t="n">
-        <v>71.3383</v>
-      </c>
-      <c r="G15" t="n">
-        <v>1.321</v>
-      </c>
-      <c r="H15" t="n">
-        <v>12</v>
-      </c>
-      <c r="I15" t="n">
-        <v>12</v>
-      </c>
-      <c r="J15" t="n">
-        <v>0.2373000000000047</v>
-      </c>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>12 0 19</t>
-        </is>
-      </c>
-      <c r="L15" t="inlineStr">
-        <is>
-          <t>Cu39S28</t>
-        </is>
-      </c>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>Spionkopite</t>
-        </is>
-      </c>
-      <c r="N15" t="inlineStr">
-        <is>
-          <t>Cu39S28</t>
-        </is>
-      </c>
-      <c r="O15" t="inlineStr">
-        <is>
-          <t>000360380</t>
-        </is>
-      </c>
-      <c r="P15" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q15" t="inlineStr">
-        <is>
-          <t>MATCH</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="n">
-        <v>31</v>
-      </c>
-      <c r="B16" t="n">
-        <v>74.31399999999999</v>
-      </c>
-      <c r="C16" t="n">
-        <v>1.27533</v>
-      </c>
-      <c r="D16" t="n">
-        <v>765.905</v>
-      </c>
-      <c r="E16" t="n">
-        <v>36.16666115757115</v>
-      </c>
-      <c r="F16" t="n">
-        <v>74.4939</v>
-      </c>
-      <c r="G16" t="n">
-        <v>1.2727</v>
-      </c>
-      <c r="H16" t="n">
-        <v>57</v>
-      </c>
-      <c r="I16" t="n">
-        <v>5.705705705705705</v>
-      </c>
-      <c r="J16" t="n">
-        <v>0.1799000000000035</v>
-      </c>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>2 0 8</t>
-        </is>
-      </c>
-      <c r="L16" t="inlineStr">
-        <is>
-          <t>CuS</t>
-        </is>
-      </c>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>Covellite</t>
-        </is>
-      </c>
-      <c r="N16" t="inlineStr">
-        <is>
-          <t>CuS</t>
-        </is>
-      </c>
-      <c r="O16" t="inlineStr">
-        <is>
-          <t>000752233</t>
-        </is>
-      </c>
-      <c r="P16" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q16" t="inlineStr">
-        <is>
-          <t>MATCH</t>
-        </is>
       </c>
     </row>
   </sheetData>
@@ -25543,7 +23738,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J20"/>
+  <dimension ref="A1:J5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -25600,35 +23795,35 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="B2" t="n">
-        <v>19.945</v>
+        <v>57.555</v>
       </c>
       <c r="C2" t="n">
-        <v>4.44811</v>
+        <v>1.60009</v>
       </c>
       <c r="D2" t="n">
-        <v>365.952</v>
+        <v>814.2380000000001</v>
       </c>
       <c r="E2" t="n">
-        <v>17.28055305022878</v>
+        <v>38.75478343645884</v>
       </c>
       <c r="F2" t="n">
-        <v>20.6644</v>
+        <v>56.7051</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Cu1.9375S</t>
+          <t>Cu39S28</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>000711383</t>
+          <t>000360380</t>
         </is>
       </c>
       <c r="I2" t="n">
-        <v>0.7194000000000003</v>
+        <v>0.8498999999999981</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
@@ -25638,35 +23833,35 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="B3" t="n">
-        <v>24.242</v>
+        <v>59.397</v>
       </c>
       <c r="C3" t="n">
-        <v>3.66849</v>
+        <v>1.5548</v>
       </c>
       <c r="D3" t="n">
-        <v>461.619</v>
+        <v>1178</v>
       </c>
       <c r="E3" t="n">
-        <v>21.79802711419411</v>
+        <v>56.06853879105188</v>
       </c>
       <c r="F3" t="n">
-        <v>24.7304</v>
+        <v>59.7154</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Cu1.9375S</t>
+          <t>CuS</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>000711383</t>
+          <t>000752233</t>
         </is>
       </c>
       <c r="I3" t="n">
-        <v>0.4883999999999986</v>
+        <v>0.318400000000004</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
@@ -25679,32 +23874,32 @@
         <v>10</v>
       </c>
       <c r="B4" t="n">
-        <v>39.957</v>
+        <v>67.13200000000001</v>
       </c>
       <c r="C4" t="n">
-        <v>2.25451</v>
+        <v>1.39321</v>
       </c>
       <c r="D4" t="n">
-        <v>660.952</v>
+        <v>738.2380000000001</v>
       </c>
       <c r="E4" t="n">
-        <v>31.21069457102247</v>
+        <v>35.13745835316517</v>
       </c>
       <c r="F4" t="n">
-        <v>39.2897</v>
+        <v>67.5258</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Cu1.9375S</t>
+          <t>Cu39S28</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>000711383</t>
+          <t>000360380</t>
         </is>
       </c>
       <c r="I4" t="n">
-        <v>0.6672999999999973</v>
+        <v>0.3937999999999988</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
@@ -25717,604 +23912,34 @@
         <v>12</v>
       </c>
       <c r="B5" t="n">
-        <v>44.582</v>
+        <v>77.834</v>
       </c>
       <c r="C5" t="n">
-        <v>2.03079</v>
+        <v>1.22622</v>
       </c>
       <c r="D5" t="n">
-        <v>704</v>
+        <v>720.8099999999999</v>
       </c>
       <c r="E5" t="n">
-        <v>33.24345637504663</v>
+        <v>34.30794859590671</v>
       </c>
       <c r="F5" t="n">
-        <v>43.9154</v>
+        <v>77.37909999999999</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Cu39S28</t>
+          <t>CuCl</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>000360380</t>
+          <t>000822117</t>
         </is>
       </c>
       <c r="I5" t="n">
-        <v>0.6666000000000025</v>
+        <v>0.4549000000000092</v>
       </c>
       <c r="J5" t="inlineStr">
-        <is>
-          <t>NO MATCH</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="n">
-        <v>15</v>
-      </c>
-      <c r="B6" t="n">
-        <v>55.407</v>
-      </c>
-      <c r="C6" t="n">
-        <v>1.65694</v>
-      </c>
-      <c r="D6" t="n">
-        <v>756.476</v>
-      </c>
-      <c r="E6" t="n">
-        <v>35.72141605791161</v>
-      </c>
-      <c r="F6" t="n">
-        <v>54.4403</v>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>Cu39S28</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>000360380</t>
-        </is>
-      </c>
-      <c r="I6" t="n">
-        <v>0.9666999999999959</v>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>NO MATCH</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="n">
-        <v>16</v>
-      </c>
-      <c r="B7" t="n">
-        <v>55.754</v>
-      </c>
-      <c r="C7" t="n">
-        <v>1.64742</v>
-      </c>
-      <c r="D7" t="n">
-        <v>740.2859999999999</v>
-      </c>
-      <c r="E7" t="n">
-        <v>34.95691100292296</v>
-      </c>
-      <c r="F7" t="n">
-        <v>56.7051</v>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>Cu39S28</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>000360380</t>
-        </is>
-      </c>
-      <c r="I7" t="n">
-        <v>0.9511000000000038</v>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>NO MATCH</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="n">
-        <v>17</v>
-      </c>
-      <c r="B8" t="n">
-        <v>57.453</v>
-      </c>
-      <c r="C8" t="n">
-        <v>1.6027</v>
-      </c>
-      <c r="D8" t="n">
-        <v>842.619</v>
-      </c>
-      <c r="E8" t="n">
-        <v>39.78915904443951</v>
-      </c>
-      <c r="F8" t="n">
-        <v>56.7051</v>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>Cu39S28</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>000360380</t>
-        </is>
-      </c>
-      <c r="I8" t="n">
-        <v>0.7479000000000013</v>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>NO MATCH</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="n">
-        <v>19</v>
-      </c>
-      <c r="B9" t="n">
-        <v>61.75</v>
-      </c>
-      <c r="C9" t="n">
-        <v>1.50107</v>
-      </c>
-      <c r="D9" t="n">
-        <v>771</v>
-      </c>
-      <c r="E9" t="n">
-        <v>36.40725122892181</v>
-      </c>
-      <c r="F9" t="n">
-        <v>63.0584</v>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>Cu39S28</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>000360380</t>
-        </is>
-      </c>
-      <c r="I9" t="n">
-        <v>1.308399999999999</v>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>NO MATCH</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="n">
-        <v>20</v>
-      </c>
-      <c r="B10" t="n">
-        <v>62.118</v>
-      </c>
-      <c r="C10" t="n">
-        <v>1.49305</v>
-      </c>
-      <c r="D10" t="n">
-        <v>773.571</v>
-      </c>
-      <c r="E10" t="n">
-        <v>36.52865595383693</v>
-      </c>
-      <c r="F10" t="n">
-        <v>63.0584</v>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>Cu39S28</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>000360380</t>
-        </is>
-      </c>
-      <c r="I10" t="n">
-        <v>0.9403999999999968</v>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>NO MATCH</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="n">
-        <v>21</v>
-      </c>
-      <c r="B11" t="n">
-        <v>62.446</v>
-      </c>
-      <c r="C11" t="n">
-        <v>1.48601</v>
-      </c>
-      <c r="D11" t="n">
-        <v>769.143</v>
-      </c>
-      <c r="E11" t="n">
-        <v>36.31956216856888</v>
-      </c>
-      <c r="F11" t="n">
-        <v>63.0584</v>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>Cu39S28</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>000360380</t>
-        </is>
-      </c>
-      <c r="I11" t="n">
-        <v>0.6124000000000009</v>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>NO MATCH</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="n">
-        <v>22</v>
-      </c>
-      <c r="B12" t="n">
-        <v>63.489</v>
-      </c>
-      <c r="C12" t="n">
-        <v>1.46407</v>
-      </c>
-      <c r="D12" t="n">
-        <v>766.095</v>
-      </c>
-      <c r="E12" t="n">
-        <v>36.17563311312691</v>
-      </c>
-      <c r="F12" t="n">
-        <v>63.0584</v>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>Cu39S28</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>000360380</t>
-        </is>
-      </c>
-      <c r="I12" t="n">
-        <v>0.4305999999999983</v>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>NO MATCH</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="n">
-        <v>23</v>
-      </c>
-      <c r="B13" t="n">
-        <v>67.13200000000001</v>
-      </c>
-      <c r="C13" t="n">
-        <v>1.39321</v>
-      </c>
-      <c r="D13" t="n">
-        <v>738.2380000000001</v>
-      </c>
-      <c r="E13" t="n">
-        <v>34.86020276619556</v>
-      </c>
-      <c r="F13" t="n">
-        <v>67.5258</v>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>Cu39S28</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>000360380</t>
-        </is>
-      </c>
-      <c r="I13" t="n">
-        <v>0.3937999999999988</v>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>NO MATCH</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="n">
-        <v>26</v>
-      </c>
-      <c r="B14" t="n">
-        <v>70.85599999999999</v>
-      </c>
-      <c r="C14" t="n">
-        <v>1.32884</v>
-      </c>
-      <c r="D14" t="n">
-        <v>722.619</v>
-      </c>
-      <c r="E14" t="n">
-        <v>34.12266079869293</v>
-      </c>
-      <c r="F14" t="n">
-        <v>71.3383</v>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>Cu39S28</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>000360380</t>
-        </is>
-      </c>
-      <c r="I14" t="n">
-        <v>0.4823000000000093</v>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>NO MATCH</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="n">
-        <v>28</v>
-      </c>
-      <c r="B15" t="n">
-        <v>71.69499999999999</v>
-      </c>
-      <c r="C15" t="n">
-        <v>1.31534</v>
-      </c>
-      <c r="D15" t="n">
-        <v>715.381</v>
-      </c>
-      <c r="E15" t="n">
-        <v>33.78087651283698</v>
-      </c>
-      <c r="F15" t="n">
-        <v>71.3383</v>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>Cu39S28</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>000360380</t>
-        </is>
-      </c>
-      <c r="I15" t="n">
-        <v>0.3566999999999894</v>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>NO MATCH</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="n">
-        <v>29</v>
-      </c>
-      <c r="B16" t="n">
-        <v>71.98099999999999</v>
-      </c>
-      <c r="C16" t="n">
-        <v>1.31081</v>
-      </c>
-      <c r="D16" t="n">
-        <v>700.571</v>
-      </c>
-      <c r="E16" t="n">
-        <v>33.08153618767442</v>
-      </c>
-      <c r="F16" t="n">
-        <v>71.3383</v>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>Cu39S28</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>000360380</t>
-        </is>
-      </c>
-      <c r="I16" t="n">
-        <v>0.6426999999999907</v>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>NO MATCH</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="n">
-        <v>30</v>
-      </c>
-      <c r="B17" t="n">
-        <v>73.004</v>
-      </c>
-      <c r="C17" t="n">
-        <v>1.29494</v>
-      </c>
-      <c r="D17" t="n">
-        <v>708.2859999999999</v>
-      </c>
-      <c r="E17" t="n">
-        <v>33.44584480405721</v>
-      </c>
-      <c r="F17" t="n">
-        <v>74.4939</v>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>CuS</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>000752233</t>
-        </is>
-      </c>
-      <c r="I17" t="n">
-        <v>1.489899999999992</v>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>NO MATCH</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="n">
-        <v>32</v>
-      </c>
-      <c r="B18" t="n">
-        <v>75.64400000000001</v>
-      </c>
-      <c r="C18" t="n">
-        <v>1.25617</v>
-      </c>
-      <c r="D18" t="n">
-        <v>693.381</v>
-      </c>
-      <c r="E18" t="n">
-        <v>32.74201850111677</v>
-      </c>
-      <c r="F18" t="n">
-        <v>76.73350000000001</v>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>Cu39S28</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>000360380</t>
-        </is>
-      </c>
-      <c r="I18" t="n">
-        <v>1.089500000000001</v>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>NO MATCH</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="n">
-        <v>33</v>
-      </c>
-      <c r="B19" t="n">
-        <v>77.813</v>
-      </c>
-      <c r="C19" t="n">
-        <v>1.22649</v>
-      </c>
-      <c r="D19" t="n">
-        <v>742.8099999999999</v>
-      </c>
-      <c r="E19" t="n">
-        <v>35.0760963493585</v>
-      </c>
-      <c r="F19" t="n">
-        <v>77.37909999999999</v>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>CuCl</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>000822117</t>
-        </is>
-      </c>
-      <c r="I19" t="n">
-        <v>0.4339000000000084</v>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>NO MATCH</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="n">
-        <v>34</v>
-      </c>
-      <c r="B20" t="n">
-        <v>79</v>
-      </c>
-      <c r="C20" t="n">
-        <v>1.21102</v>
-      </c>
-      <c r="D20" t="n">
-        <v>738</v>
-      </c>
-      <c r="E20" t="n">
-        <v>34.8489642113415</v>
-      </c>
-      <c r="F20" t="n">
-        <v>79.6553</v>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>CuS</t>
-        </is>
-      </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>000752233</t>
-        </is>
-      </c>
-      <c r="I20" t="n">
-        <v>0.6552999999999969</v>
-      </c>
-      <c r="J20" t="inlineStr">
         <is>
           <t>NO MATCH</t>
         </is>
@@ -26413,25 +24038,25 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F2" t="n">
-        <v>0.1152125000000024</v>
+        <v>0.05886666666666803</v>
       </c>
       <c r="G2" t="n">
-        <v>0.2994999999999948</v>
+        <v>0.1799000000000035</v>
       </c>
       <c r="H2" t="n">
-        <v>432.4187919970157</v>
+        <v>341.6811994288434</v>
       </c>
       <c r="I2" t="n">
-        <v>23.52941176470588</v>
+        <v>50</v>
       </c>
       <c r="J2" t="n">
         <v>15</v>
       </c>
       <c r="K2" t="n">
-        <v>53.33333333333334</v>
+        <v>40</v>
       </c>
     </row>
     <row r="3">
@@ -26456,25 +24081,25 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F3" t="n">
-        <v>0.07454285714285598</v>
+        <v>0.09769999999999897</v>
       </c>
       <c r="G3" t="n">
         <v>0.2531999999999996</v>
       </c>
       <c r="H3" t="n">
-        <v>305.8943386960443</v>
+        <v>253.0023322227511</v>
       </c>
       <c r="I3" t="n">
-        <v>20.58823529411764</v>
+        <v>41.66666666666667</v>
       </c>
       <c r="J3" t="n">
         <v>116</v>
       </c>
       <c r="K3" t="n">
-        <v>6.03448275862069</v>
+        <v>4.310344827586207</v>
       </c>
     </row>
     <row r="4">
@@ -26499,25 +24124,25 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="F4" t="n">
-        <v>0.163685714285715</v>
+        <v>0.1925333333333346</v>
       </c>
       <c r="G4" t="n">
-        <v>0.2506000000000022</v>
+        <v>0.2706000000000017</v>
       </c>
       <c r="H4" t="n">
-        <v>286.3965793238923</v>
+        <v>161.0664921465969</v>
       </c>
       <c r="I4" t="n">
-        <v>20.58823529411764</v>
+        <v>25</v>
       </c>
       <c r="J4" t="n">
         <v>31</v>
       </c>
       <c r="K4" t="n">
-        <v>22.58064516129032</v>
+        <v>9.67741935483871</v>
       </c>
     </row>
   </sheetData>
